--- a/conference_articles.xlsx
+++ b/conference_articles.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>strong dominating set, Hajo´s sum, vertex-sum,</t>
+          <t>strong dominating set, Hajo´s sum, vertex-sum, operation, domatic.. MSC(2020): 05C99. 1. Introduction A dominating set of a graph G = (V,E) is a subset D of V such that every vertexinV \D isadjacenttoatleastonememberofD. Theminimumcardinality ofalldominatingsetsofGiscalledthedominationnumberofGandisdenotedby γ(G). This parameter has been extensively studied in the literature and there are hundreds of papers concerned with domination. We recommend a fundamental book [9] about domination in general. The various different domination concepts are well-studied now, however new concepts are introduced frequently and the interest is growing rapidly. A set D ⊆ V is a strong dominating set of G, if for every vertex x ∈ D = V \ D there is a vertex y ∈ D with xy ∈ E(G) and deg(x) ≤ deg(y). The strongdominationnumber γ (G)isdefinedastheminimumcardinalityofastrong st dominating set. A γ -set of G is a strong dominating set of G of minimum st cardinality γ (G). If D is a strong dominating set in a graph G, then we say st that a vertex u ∈ D is strong dominated by a vertex v ∈ D if uv ∈ E(G), and deg(u)≤deg(v). ∗ Speaker. Emailaddress: alikhani@yazd.ac.ir † Emailaddress:nima.ghanbari@uib.no 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finite dimensional algebra, Ring epimorphism,</t>
+          <t>Finite dimensional algebra, Ring epimorphism, Homological conjectures. MSC(2020): 16G10, 16G60. 1. Introduction Auslander-Reiten Conjecture is already known to be one of the most long- standing homological conjectures in the field of representation theory of finite dimensional algebras. Though it has emerged originally in this context, it is also widely studied in various settings such as commutative rings and (noncommu- tative) Noetherian algebras over commutative noetherian rings. As a matter of fact, at least for finite dimensional algebras, it is known that Auslander-Reiten conjecture has strong links to some other homological conjectures. These include the famous finitistic dimension conjecture, Nakayama conjecture, and vanishing conjecture [4]. On the other hand, there exists a natural generalization of the concept of lo- calization for commutative rings to the setting of arbitrary rings; this is named universallocalizationandwasintroducedin[6]bylocalizingwithrespecttoagiven set of morphisms between finitely generated projective modules. This type of lo- calizationtheoryhasobtainedmanyapplicationsinvariousareasofrepresentation theory of algebras, including tilting theory in particular [1]. This short note tries to discover a connection between universal localizations and the validity of Auslander-Reiten conjecture for a special type of finite dimen- sional algebras. ∗ Speaker. Emailaddress: eshraghi@kashanu.ac.ir 8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Logic algebra, neutrosophic logic, superhyper logic</t>
+          <t>Logic algebra, neutrosophic logic, superhyper logic algebra. MSC(2020): 16Y20, 13A70. 1. Introduction Florentin Smarandache introduced a new concept in neutrosophy branches as neutro-algebra as a generalization of partial algebra. Through a theorem he proved that Neutro-algebra is a generalization of partial algebra, and he gave examples of neutro-algebras that are not partial algebras. He also introduced theneutro-function(andneutro-operation). Recently,Smarandache,introduceda newconceptasageneralizationofhypergraphston-superhypergraph,plithogenic n-super hypergraph {with super-vertices (that are groups of vertices) and hyper- edges{definedonpower-setofpower-set...}thatisthemostgeneralformofgraph as today}, and n-ary hyperalgebra, n-ary neutro hyperalgebra, n-ary anti hyper- algebra respectively, which have several properties and are connected with the real world. Recently in the scope of neutro logical (hyper) algebra, Hamidi, et al. introduced the concept of neutro BCK-subalgebras [1] and single-valued neu- tro hyper BCK-subalgebras [2] as a generalization of BCK-algebras and hyper BCK-subalgebras, respectively and presented the main results in this regard. Also Florentin Smarandache a novel concept as super hyperalgebra with its super hyperoperations and super hyperaxioms, then is introduced some concepts such as super hypertopology and especially the super hyperfunction and neutrosophic super hyperfunction. Recently, Hamidi introduced the concept of super hyper BCK-algebras as a generalization of BCK-algebras and investigated some proper- ties of this novel concept [3]. The main motivation of this study is to extension of logic algebras to superhyper logic algebras based on the superhyper axioms. Indeed, we try to overspread the axiom of clasic algebras to superhyper axiom in ∗ Speaker. s.jahanpanah@pnu.ac.ir 12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gro¨bner systems, GES algorithm, GVWDisPGB</t>
+          <t>Gro¨bner systems, GES algorithm, GVWDisPGB algorithm, GES-GVW-CGS algorithm, Gaussian elimination. MSC(2020): 13P10, 15A06. 1. Introduction TheconceptofGr¨obnersystems,alongwiththeinitialalgorithmfortheircom- putation, introduced in 1992 by Weispfenning [5], revolutionized the field of para- metric polynomial ideals. Gro¨bner systems find numerous applications in various fields,includingmathematicsandothersciences. Theyhaveprovenvaluableinar- eassuchasalgebraicgeometry,parametriclinearalgebra,robotics,andautomated geometry theorem proving. Throughout this text, we consider R = K[x ,...,x ] 1 n thepolynomialringintermsofx ,...,x overafieldK. LetI =⟨f ,...,f ⟩⊂R 1 n 1 k be a polynomial ideal and ≺ be a monomial ordering on the set of all monomials of R. For any f ∈ R, the leading monomial of f, denoted by LM (f), is the ≺ greatest monomial (w.r.t. ≺) appearing in f and its coefficient is the leading co- efficient of f which denoted by LC (f). The leading term of f w.r.t. ≺ is the ≺ product LT (f) = LC (f)LM (f). The leading monomial ideal of I is defined ≺ ≺ ≺ to be LM (I) = ⟨LM (f) | f ∈ I⟩. A finite subset {g ,...,g } ⊂ I is called ≺ ≺ 1 m a Gr¨obner basis for I w.r.t. ≺ if LM (I) = ⟨LM (g ),...,LM (g )⟩. Gr¨obner ≺ ≺ 1 ≺ m systems can be considered as an extension of Gr¨obner bases for polynomial ideals over fields to polynomial ideals with parametric coefficients. With more details, letusconsiderS =K[a,x]asapolynomialringwithparametriccoefficientswhere a = a ,...,a is a sequence of parameters, x = x ,...,x is a sequence of vari- 1 m 1 n ables. Thus a monomial xα 1 1···xα n n is denoted by xα where α=(α 1 ,...,α n ). Let ∗ Speaker. Emailaddress: m.dehghanidarmian@gmail.com 16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algebra, Break-Even Point (BEP), business</t>
+          <t>Algebra, Break-Even Point (BEP), business Management, Mathematics. MSC(2020): 00Axx, 00A05, 00A06. 1. Algebra in Business Business is as dependent on algebra as any other field. In order to calculate profits and losses, business owners use algebraic operations. A business person willusealgebratodeterminewhetherapieceofequipmentdoesnotloseitsworth if it is in stock Algebra is used in business for a variety of reasons. Generally speaking, business math skills can help people and companies to make better decisions, understand problems more thoroughly, and see the long-term impact of their choices. One specific reason business math is used relates to keeping track of financial transactions [3]. The accurate recording and maintenance of financial records are essential for businesses of all sizes. Businesses use algebra to track income and expenses, prepare financial statements, and make informed decisions about where to allocate their resources [2]. Inaddition,thebusinessownerneedstocalculatethelowestpriceatwhichan item can be sold while still covering expenses. In the finance industry, exchange rates and interest rates are often represented algebraically; therefore, to carry out finances accurately, it is necessary to be familiar with algebraic operations. ∗ Speaker. Emailaddress: sariolghalam@pnu.ac.ir 22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shape Graph, general hyperring, heart.</t>
+          <t>Shape Graph, general hyperring, heart. MSC(2020): 16Y20, 13A70. 1. Introduction The idea of a graph based on zero–divisors of a commutative ring was intro- duced by Beck, where he was mainly interested in colorings. This idea continued by Anderson based on edges and vertices colorings of any given ring. The graph based on zero-devisors was redefined by Livingston and in paper of Anderson et al. that followed in 1999. Later than the concept of hyperalgebra structures as a generalization of algebra structures and extended all ideas of algebras structures to hyperalgebra structures. In special, the idea of graph based on hyperalgebras, is a new and novel idea that connected the relation between of graphs and hyper- algebras. In this paper, we extend the concept of a type algebra named groups to multigroups and non-associative rings to multirings or super rings. In this regard, we construct multigroups, supergroups, super ring and multirings on every arbi- trary nonempty set with some hyperoperations [2, 3, 4, 5]. The main motivation of this study is to extract zero–divisor graphs from hyperstructures with special conditions. So we construct finite superrings and introduces the concept of zero– divisorelementsinfinitesuperrings. Thisstudyapproachessometypesofgraphs from these super rings. Indeed, we connect the special class of hyperstructures to graphs via structures graphs based on zero–divisors and derivable zero–divisor subgraphs. Now, we added some necessarily topics related to our main ideas with respect to hyperstructures and shape graphs. Let R be a nonempty set and P∗(R) be the family of all nonempty subsets of G. Every function θ : R×R −→ P∗(R), is called a hyperoperation, where i i∈N={1,2,...,n,...}. For all x, y of R, θ (x,y) is called the hyperproduct of x, i y. An algebraic system (R,θ ,θ ,...,θ ) is called a hyperstructure, and a binary 1 2 n ∗ Speaker. m.hamidi@pnu.ac.ir 26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hilbert C∗-module, derivation, approximate functional</t>
+          <t>Hilbert C∗-module, derivation, approximate functional equation.. MSC(2020): 39B82, 39B52, 46S10. 1. Introduction ThenotionofaHilbertC∗-moduleinitiatedbyKaplansky[3]asageneraliza- tionofaHilbertspaceinwhichtheinnerproducttakesitsvaluesinaC∗-algebra. Let A be a C∗-algebra and M be a complex linear space that is a left A- module with a compatible scalar multiplication satisfying λ(ax)=(λa)x=a(λx) forallλ∈C,x∈M,a∈A. ThenMiscalledapre-HilbertA-moduleoraninner product A-module, if there exists an A-valued inner product (x,y) (cid:55)→ ⟨x,y⟩ : M×M→A such that, (i)⟨x,x⟩≥0 and the equality holds if and only if x=0, (ii)⟨αx+βy,z⟩=α⟨x,z⟩+β⟨y,z⟩, (iii)⟨ax,y⟩=a⟨x,y⟩, (iv)⟨x,y⟩∗ =⟨y,x⟩, for each x,y,z ∈ M, α,β ∈ C and a ∈ A. M is called a (left) Hilbert A-module, or a Hilbert C∗-module over the C∗-algebra A, if it is complete with respect to the norm ∥x∥=∥⟨x,x⟩∥2 1. Every C∗-algebra A is a Hilbert A-module under the A-valued inner product ⟨a,b⟩=ab∗ (a,b∈A). Every complex Hilbert space is a left Hilbert C-module; cf [2]. Let M and N be Hilbert C∗-modules over a C∗-algebra A. A mapping T : M → N is said to be A-linear, if T(ax+λy) = aT(x)+λT(y) for all x,y ∈ M, a ∈ A and λ ∈ C. A mapping T : M → N is said to be adjointable, if there existsamappingS :N →Msuchthat⟨T(x),y⟩=⟨x,S(y)⟩forallx∈D ⊆M, T y ∈ D ⊆ N. The unique mapping S is denoted by T∗ and is called the adjoint S of T. It is well known that any adjointable mapping T :M→N is A-linear and ∗ Speaker. Emailaddress: ekrami@pnu.ac.ir,khalil.ekrami@gmail.com 30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable..</t>
+          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary: 16W20; Secondary: 13C60. 1. Introduction Throughoutthis paper, R denotes anassociative ringwith identity, and mod- ules are unitary left R-modules unless stated otherwise. Following [2], an R- module M is said to be retractable whenever Hom (M,N) ̸= 0 for any nonzero R submodule N of M. An R-module M is called coretractable whenever for any proper submodule K of M, there exists a nonzero homomorphism f : M −→ M suchthatf(K)=0,thatmeansthatHom (M/K,M)̸=0(see[1]). Therefore,in R thisstudyweweremotivatedtoinvestigatemoduleM whereHom (M/N,M)̸=0 R foreveryproperfinitelygeneratedsubmoduleN ofM,whichwecallCFRmodule. 2. Co-finite-retractable modules Definition 2.1. Let M be an R-module. We call M is co-finite-retractable (simply CFR) whenever for every proper finitely generated submodule K of M, Hom (M/K,M)̸=0. R In the following, we consider when a direct sum of a family of CFR modules is CFR. Theorem 2.2. Let {N } be a family of CFR modules, and let M := ⊕N . i i∈I i i∈I If K∩N contain in a finitely generated submodule of N for every i∈I and every i i finitely generated submodule K of M, then M is a CFR module. ∗ Speaker. Emailaddress: pegahneishabory96@gmail.com 36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ring, unit-clean.</t>
+          <t>ring, unit-clean. MSC(2020): 15A23, 15B33, 16U99. 1. Introduction All our rings are associative rings with identity. U(R) denotes the set of all idempotents of R, J(R) denotes the Jacobson radical and B(R) denotes the set of central idempotents of the ring R. By Z we mean the localization of Z at a (p) prime p. By regular we mean Von Neumann regular. Nicholson [1] defined the notion of an element in a ring R to be clean if it can be expressed as a sum of an idempotent and an invertible element in R. We refer the readers to [2] for a survey of clean rings. Clearly it would be quite natural to ask what happens if for each element a in a ring R, there exists an invertible element u in R such that au is clean? We have visualized unit-clean to be a property such that for each a ∈ R there exists a unit u such that the element au is clean. In the other words an element a in R is defined to be unit-clean if there exists invertible elements u,v in R and an idempotent e in R such that au = e+v. A ring R is unit-clean if and only each of its elements are unit-clean. This definition is independent of the position of the invertibleelementu. Thismeans,ucouldbemultipliedtotheleftorrightofa. It iseasytoobservethatanelementinaringRisunit-cleanifitcanbeexpressedas a sum of a unit-regular element and an invertible element in R. Clearly, every 2- goodringisunit-clean. HowevertheconverseisnottrueasR=F isaunit-clean 2 ring which is not 2-good. ∗ Speaker. Emailaddress: n.pouyan@scu.ac.ir neda.pouyan@gmail.com 39</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Projection, Medium nil-∗-clean ring, Strongly ∗-clean</t>
+          <t>Projection, Medium nil-∗-clean ring, Strongly ∗-clean ring.. MSC(2020): 16Wl0,16U99. 1. Introduction Throughout, all rings are associative with an identity. An involution of a ring R is an operation ∗ : R → R such that (x+y)∗ = x∗ +y∗, (xy)∗ = y∗x∗ and (x∗)∗ = x for all x,y ∈ R. A ring R with involution ∗ is called a ∗-ring. For general ∗-ring theory, we refer the reader [1]. An element p in a ∗-ring R is called a projation if p = p∗ = p2. A ∗-ring R is called a medium nil-∗-clean ring if every element of R is the sum of difference of a nilpotent and a projection that commute. Such rings are the natural generalization of strongly nil-∗-clean rings and a subclass of weakly nil-∗-clean rings. The main goal of this article is to find a new class of ∗-clean rings and to check their relationship with other ∗-clean rings such as strongly weakly J-∗-clean and weakly nil-∗-clean and strongly π-∗- regular rings. We also investigate about corner subring and homomorphic image andgroupringandpolynominalringofmediurnnil-∗-cleanrings. Inthispaper,it is shown that the full matrix M (R) is not medium nil-∗-clean for any n≥2. We n prove that medium nil-∗-clean rings and abelian weakly nil-∗-clean rings coincide with each other. As usual, U(R) denotes the set of all invertible elements of R, Id(R)thesetofallidempotentsofRandN(R)thesetofallnilpotentsofR,J(R) stands the Jacobson radical of R. 2. Main results Lemma 2.1. Every medium nil-∗-clean ring is abelian. Theorem 2.2. Let R be a ∗-ring. Then, the following are equivalent: ∗ Speaker. Emailaddress: hasanzadeomiid@gmail.com 43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>element order, finite simple group, prime graph..</t>
+          <t>element order, finite simple group, prime graph.. MSC(2020): 20D05, 20D99, 20A99. 1. Introduction Given a group G, denote by π (G) the set of orders of all elements in G. It is e clear that the set π (G) is closed and partially ordered by divisibility, hence, it is e uniquely determined by the subset of its maximal elements which is indicated by µ(G). We also denote by π(n) the set of all prime divisors of a positive integer n. For a finite group G, we will write π(G) instead of π(|G|). The notation s (G) is m applied for the number of elements of order m in G, and nse(G)={s (G) | m∈ m π (G)}, the set of numbers of all elements in a group G with the same order. A e group G is called NSE characterization if for every finite group M, the equality nse(G)=nse(M) implies that G∼ =M. Uptonow,theNSEcharacterizationofmanynon-Abelianfinitesimplegroups areinvestigated,forinstance,thereferences’[1,2,3,5,6]introducesomeofthese groups. Inwhatfollowswewillconsiderthefinitenon-AbeliansimplegroupA isNSE 9 characterization. Main Theorem The non-Abelian finite simple group A is characterizable by 9 NSE. We conclude the introduction with some further notation and definitions to be used in the rest of this article. To every finite group G we associate a graph ∗ Speaker. Emailaddress: s-rahbariyan@araku.ac.ir 47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orthogonality, non-Archimedean C∗-algebra,</t>
+          <t>Orthogonality, non-Archimedean C∗-algebra, approximate functional equations, stability. MSC(2020): 39B82, 39B52, 47H10. 1. Introduction In 1897, Hensel [3] introduced a normed space which does not have the Archimedean property. By a non-Archimedean field we mean a field K equipped with a function (valuation) |·| from K into [0,∞) such that |r|=0 if and only if r = 0, |rs| = |r||s|, and satisfies a stronger condition than the triangle inequality |r+s| ≤ max{|r|,|s|} for all r,s ∈ K. Clearly |1| = |−1| = 1 and |n| ≤ 1 for all n ∈ N. A trivial example of a non-Archimedean valuation is the function |·| taking everything except for 0 into 1 and |0|=0. LetX beavectorspaceoverascalarfieldKwithanon-Archimedeanvaluation |·|. A function ∥·∥ : X → [0,∞) is a non-Archimedean norm, if it satisfies the following conditions: (i)∥x∥ = 0 if and only if x = 0, (ii)∥rx∥ = |r|∥x∥ (r ∈ K,x ∈ X), (iii) the strong triangle inequality (ultrametric); namely, ∥x+y∥ ≤ max{∥x∥,∥y∥}. Then (X,∥·∥) is called a non-Archimedean space. Due to the fact that ∥x −x ∥ ≤ max{∥x −x ∥ : m ≤ j ≤ n−1} (n &gt; m) a sequence n m j+1 j {x }isCauchyifandonlyif{x −x }convergestozeroinanon-Archimedean n n+1 n space. By a non-Archimedean Banach space we mean one in which every Cauchy sequence is convergent. A non-Archimedean Banach algebra A is a complete non- Archimedean algebra which satisfies ∥ab∥ ≤ ∥a∥∥b∥ for all a,b ∈ A. If A is a non-Archimedean Banach algebra, then an involution on A is a mapping a (cid:55)→ a∗ fromAintoAwhichsatisfies(i)(λa+b)∗ =λ¯a∗+b∗,(ii)(ab)∗ =b∗a∗,(iii)a∗∗ =a, for all a,b∈A and λ∈C. If, in addition, ∥a∗a∥=∥a∥2 for all a∈A, then A is a non-Archimedean C*-algebra. ∗ Speaker. Emailaddress: ekrami@pnu.ac.ir,khalil.ekrami@gmail.com 51</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosbach state, bounded hyper equality algebra, equality</t>
+          <t>Bosbach state, bounded hyper equality algebra, equality algebra. MSC(2020): 03G25, 06D35, 08A35. 1. Introduction The concept of hyper equality algebras is introduced and studied in [1] and authors provided many basic properties of this class of hyper algebras. Some propertiesofthesealgebrasandtheirrelationsbetweenotherhyperstructuresare given in [3] and hyper ideals on bounded hyper equality algebras are introduced in [4]. States play an important role in studying of logical structures. States on equality algebras are defined and studied by Ciungu in [2]. Some more results related to states on equality algebras are studied in [5]. Let H be a nonempty set and◦beafunctionfromH×H tothenonemptypowersetofH,P(H). Then◦is said to be a hyper operation on H. A hyper equality algebra H=⟨H;∼,∧,1⟩ is a nonempty set H endowed with a binary operation ∧, a binary hyper operation ∼ andatopelement1suchthat,forallx,y,z ∈H,thefollowingaxiomsarefulfilled: (HE1) ⟨H,∧,1⟩ is a meet-semilattice with top element 1; (HE2) x ∼ y ≪ y ∼ x; (HE3) 1 ∈ x ∼ x; (HE4) x ∈ 1 ∼ x; (HE5) x ≤ y ≤ z implies x ∼ z ≪ y ∼ z and x ∼ z ≪ x ∼ y; (HE6) x ∼ y ≪ (x∧z) ∼ (y ∧z); (HE7) x ∼ y ≪ (x ∼ z) ∼ (y ∼ z); where x ≤ y if and only if x∧y = x; A ≪ B is defined by for all x ∈ A, there exists y ∈ B such that x ≤ y. Define the following two derived operations, the implication and the equivalence operation of the hyper equality algebra ⟨H,∼,∧,1⟩ by x→y =x∼(x∧y) and x↔y =(x→y)∧(y →x). Proposition 1.1. [1, Proposition 2] Let H=⟨H;∼,∧,1⟩ be a hyper equality algebra. Then for all x,y,z ∈ H, A,B,C ⊆ H: (P1) x ≤ y and y ≤ x imply ∗ Speaker. Emailaddress: m a hashemi@pnu.ac.irali1978hashemi@gmail.com 57</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Parainjective, paraprojective, monoid, S-act.</t>
+          <t>Parainjective, paraprojective, monoid, S-act. MSC(2020): 20M30. 1. Introduction In this article S will denote a monoid and an S-act A (or A) is a unitary S S-act. Over a monoid S an S-act A is called paraprojective (parainjective) if for any epimorphism f : B −→ A (monomorphism f : A −→ B) there exists a monomorphism g : A −→ B (an epimorphism g : B −→ A ). In this paper these classesofS-actshavebeenstudied. Itisshownthatforprojective(injective)S-acts the concepts of parainjectivity and injectivty ( paraprojectivity and projectivity) are equivalent. Recall that an S-act A is called injective if for any S-act B, any subact C of B and any homomorphism f : C −→ A, there exists a homomorphism f¯: B −→ A such that f¯| =f. Also an S-act A is projective if for any S-act B and for every C S-act C, every S-homomorphism f : A −→ C can be lifted with respect to every epimorphism g : B −→ C, i.e., there exists a homomorphism h : A −→ B such thatf =gh(see[3]). Anelementθ ∈Aiscalledazeroelementifθs=θ forevery s ∈ S. Moreover the one element S-act is denoted by Θ = {θ}. For an S-act A, by E(A), we mean the injective envelope of A. We encourage the reader to see [3] for basic results and definitions relating to acts over monoids. 2. Main results Definition 2.1. Over a monoid S an S-act A is called paraprojective if for any epimorphism f :B −→A there exists a monomorphism g :A−→B. Also an ∗ Speaker. Emailaddress: m.rooeintan@yahoo.com 63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>General superring, Boolean general superring,</t>
+          <t>General superring, Boolean general superring, (normal)hyperideal, heart of general superring. MSC(2020): 16Y20, 13A70. 1. Introduction Thetheoryofmultigroups,superrings,andmultifieldswasintroducedbyMar- shall as a generalization of groups, rings, and fields in [4].The notions of multi- groups, superrings, multifields, and their corresponding reduced versions were in- troduced by Marshall in [4] and provided a convenient framework to study the reduced theory of quadratic forms and spaces of orderings. A superring is just a ring with multivalued addition and the idea of a superring is very natural. super- rings are considered in spaces of signs, also known as abstract real spectra and objects which arised naturally in the study of constructible sets in real geome- try. In what follows, we introduce the some concepts such need to our work from [1, 2, 3, 5]. LetRbeanon–emptysetandP∗(R)={S |∅̸=S ⊆R}. Everymap + : R×R −→ P∗(R) is called a hyperoperation and for all x and y of R, +(x,y) is called the hyperproduct of x and y. A binary hyperstructure (R,+) is called a (cid:83) hypergroupoidandA+B = a+b.,where∅≠ A,B ⊆R.Recallthatahy- a∈A,b∈B pergroupoid(R,+)iscalledasemihypergroupif∀x,y,z ∈R,(x+y)+z =x+(y+z) and a semihypergroup (R,+) is called a hypergroup if satisfies in the reproduc- tion axiom, i.e. ∀ x ∈ R,x + R = R + x = R. A commutative hypergroup (R,+)( ∀ x,y ∈ R,x + y = y + x) is called a canonical hypergroup, provided that (i) it has a scalar identity 0 ( ∀ x ∈ R,0+x = x+0 = {x}), (ii) every element has a unique inverse, (∀ x ∈ R, there exists a unique −x ∈ G, such that 0 ∈ x+(−x)∩(−x)+x), (iii) x ∈ y+z implies y ∈ x+(−z) and z ∈ −y+x ∗ Speaker. rdaneshpayeh@pnu.ac.ir 67</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Γ-δ-MV-algebra, ideals, Heyting algebra .</t>
+          <t>Γ-δ-MV-algebra, ideals, Heyting algebra . MSC(2020): 03B50,03G25,06D35. 1. Introduction We recall some definitions and results which will be needed. Definition 1.1. [1, 2, 5] An MV-algebra is a structure (A, ⊕, *, 0) where ⊕ is a binary operation, *, is a unary operation, and 0 is a constant such that the following axioms are satisfied for any a,b∈A : (MV1) (A, ⊕, 0) is an Abelian monoid, (MV2) (a∗)∗ =a, (MV3) 0∗⊕a=0∗, (MV4) (a∗⊕b)∗⊕b=(b∗⊕a)∗⊕a. Note 1=0∗ and the auxiliary operation ⊙ as follow: x⊙y =(x∗⊕y∗)∗. Theorem 1.2. [5] In an MV-algebra (A,⊕,∗,0) we have: (i) x⊙(y⊙z) = (x⊙y)⊙z, (ii) x⊙y =y⊙x, (iii) x⊙1=x, (iv) x∗∗ =x, (v) x⊙1∗ =1∗, (vi) (x∗⊙y)∗⊙y =(y∗⊙x)∗⊙x, that is (A,⊙,∗,1) is an MV-algebra. Definition 1.3. [1, 5] An ideal of an MV-algebra A is a nonempty subset I of A satisfying the following conditions: (I1) If x∈I , y ∈A and y ≤x, then y ∈I, (I2) If x,y ∈I, then x⊕y ∈I. ∗ Speaker. Emailaddress: frouzesh@bam.ac.ir 72</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ds, isomorphism, d-Rickart module, virtually d-Rickart</t>
+          <t>ds, isomorphism, d-Rickart module, virtually d-Rickart module.. MSC(2020): 16D10,16D40, 16D90. 1. Introduction The property of being a d-Rickart (short form for dual Rickart) module and how it is inherited by ds (abbreviation for direct summand) but not by direct sums of modules. It is also shown that d-Rickart modules satisfy the Summand Sum Property (SSP). The concept of relative d-Rickart condition is introduced to characterize a d-Rickart module. The text proves that a ring where each right module is d-Rickart is semisimple artinian, while a ring where every finitely gen- erated free module is d-Rickart is a von Neumann regular ring. It is proved that a ring where every injective right module is d-Rickart is right hereditary, and a consequence is that each injective right module is dual Baer if and only if the ring is right hereditary and right noetherian([4]). Over the past ten years, there has been a growing interest in using isomor- phisms to study modules. A recent paper by Behboodi et al. proposed a new approach to semisimple modules using the concept of virtually (semi)simple mod- uleandrings([1]). Chaturvedietal. ([2])introducediso-retractablemodulesasa extension of retractable modules. The present article aims to build on their work by examining Rickart modules and d-Rickart modules. InSection2,weexplorethedualnotionofvirtuallyRickartmodules,whichwe call virtually d-Rickart modules. We prove that every virtually d-Rickart module satisfiesGSSP,andthatanyvirtuallyd-RickartmodulewithC isd-Rickart. We 2 also provide a condition that ensures a virtually d-Rickart module is d-Rickart. For a uniserial module M, we show that if M ⊕M is virtually d-Rickart so M ∗ Speaker. Emailaddress: s.asgari03@umail.umz.ac.ir 77</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable..</t>
+          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary 16D10; secondary 16D40. 1. Introduction Throughoutthis paper, R denotes anassociative ringwith identity, and mod- ules are unitary left R-modules unless stated otherwise. Following [2], an R- module M is said to be retractable whenever Hom (M,N) ̸= 0 for any nonzero R submodule N of M. Amini and et al. investigate coretractable module, and we also obtain some new results of coretractable module. An R-module M is called coretractable whenever for any proper submodule K of M, there exists a nonzero homomorphism f : M −→ M such that f(K) = 0, that means that Hom (M/K,M) ̸= 0 (see [1]). Recall that, we said an R-module M is co-finite- R retractable(simplyCFR)wheneverforeveryfinitelygeneratedpropersubmodule K of M, Hom (M/K,M) ̸= 0. We show that, every module over a left Artinian R leftH-ringiscoretractable. Also,weshowthateverymodule M hasfinitelength R overacommutativeringRiscoretractable. Itisclear,everycoretractablemodule is CFR. We show that, every CFR module is coretractable if and only if every module is coretractable. ∗ Speaker. Emailaddress: Y.toloei@razi.ac.ir 82</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Krasner, Enumeration, Hyperring.</t>
+          <t>Krasner, Enumeration, Hyperring. MSC(2020): 16Y99. 1. Introduction HyperringsandhyperfieldswerealsointroducedandstudiedbyKrasner,Vou- giouklis, and Davvaz [3, 2]. Krasner was the first to expand hypercompositional structures by creating structures containing composition and hypercompositions, which he called Krasner Hyperrings[3]. Kinds of Krasner hyperrings and hy- perfields of order 3 was introduced in [5]. Mittas introduced a special type of completelyregularhypergroupcalledthepolysymmetricalhypergroup, whichwas furtherstudiedbyYatrasunderthenameofM-polysymmetricalhypergroup. Mit- tas and Yatras [4] extended the notion of polysymmetrical hyperrings to a special case called M-polysymmetrical hyperrings. In this article, we compute various types of hyperrings, including Krasner and polysymmetrical hyperrings, in small orders and provide a classification based on their Cayley tables. WerecallthedefinitionofM-polysymmetricalhyperring(Mp-hyperring)from [4] as follows: A set R is called an Mp-hyperring if it is equipped with a binary hyperop- eration + : R × R → P∗(R) and an binary operation · : R × R → R, where P∗(R)={Y|∅≠ Y ⊆R}, such that the following conditions hold: (1) (R,+) is an Mp-hypergroup, (2) (R,·) is a semigroup, (3) the multiplication is strongly bilaterally distributive over the addition. ∗ Speaker. Emailaddress: saeed mirvakili@pnu.ac.ir 85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hochschild cohomology, Square matrix algebra, Square</t>
+          <t>Hochschild cohomology, Square matrix algebra, Square algebra.. MSC(2020): . 1. Introduction Consideranarbitrarycommutativeringwithaunitelement,denotedasR. Let A and B be two R-algebras with units, M is a left A-module and right B-module ((A−B)-module),N isaleftB-moduleandrightA-module((B−A)-module). We (cid:18) (cid:19) A M also introduce S = as an algebra over R with the following operations: N B (cid:20) (cid:21) (cid:20) (cid:21) (cid:20) (cid:21) a m a m a +a m +m 1 1 + 2 2 = 1 2 1 2 n b n b n +n b +b 1 1 2 2 1 2 1 2 and (cid:20) (cid:21) (cid:20) (cid:21) (cid:20) (cid:21) a m a m a a +m ⊗ n a m +m b 1 1 · 2 2 = 1 2 1 B 2 1 2 1 2 n b n b n a +b n n ⊗ m +b b 1 1 2 2 1 2 1 2 1 A 2 1 2 where a ,a ∈A, b ,b ∈B, m ,m ∈M, n ,n ∈N. 1 2 1 2 1 2 1 2 If M ⊗ N =N ⊗ M =0, then we call S is a square algebra. Furthermore, B A within the context of S if N = 0 then S is called triangular algebra, and this particular algebra has been investigated by Cheung [3, 4]. Basic examples of triangular algebras are upper triangular matrix algebras and nest algebras which derivations on those considered in [5]. ∗ Speaker. Emailaddress: S.N.Salehi.O@pnu.ac.ir 90</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parametric linear algebra, Gauss-Jordan system,</t>
+          <t>Parametric linear algebra, Gauss-Jordan system, Parametric matrices. MSC(2020): 15A03, 13P10. 1. Introduction A matrix is said to be in reduced row echelon form (rref) when it is in row echelon form and its basic columns are vectors of the standard basis (i.e., vectors having one entry equal to 1 and all the other entries equal to 0). When the coefficient matrix of a linear system is in rref, it is straightforward to derive the solutions of the system from the coefficient matrix and the vector of constants. The standard algorithm used to transform a system into an equivalent system in rref is called Gauss-Jordan elimination. In this paper we are interested only in parametric matrices. Many problems in science and engineering can be modelled by parametric matrices, and have to be repeatedly solved for different values of parameters. In this direction, the Gauss-Jordan of a parametric matrix may have a wide range of applications. For example, we can solve the system of linear equations with parametric coefficients. The following example shows that the traditional approach for computing the Gauss-Jordan form of matrices may not be used for such a matrix. Example 1.1. Let  a−1 0 c−2 1  A= 2 0 −1 b−1  a b+c 0 −1 ∗ Speaker. Emailaddress: m.dehghanidarmian@gmail.com 95</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MV-algebras, Minimal prime ideal, Z◦−ideals .</t>
+          <t>MV-algebras, Minimal prime ideal, Z◦−ideals . MSC(2020): 06D35, 06B10. 1. Preliminaries In this section, we state the definitions and theorems that we use: Definition 1.1. [2] Algebra A = (A,⊕, *, 0) of type (2,1,0) is called an MV−algebra, if (1)α⊕(β⊕γ)=(α⊕β)⊕γ; (2)α⊕β =β⊕α; (3) α⊕0=α; (4) (α∗)∗ =α; (5) 0∗⊕α=0∗; (6) (α∗⊕β)∗⊕β =(β∗⊕α)∗⊕α for any α,β,γ ∈A On A, the constan 1 and the auxiliary operation ⊙ are defined as follows: 1=0∗ and α⊙β =(α∗⊕β∗)∗, for all α,β ∈A. Also, ≤ is a partial order on A α≤β ⇔α∗⊕β =1,∀α,β ∈A and it is called the natural order on A. If ≤ is an linearly ordered relative on A, then A is called an MV−chain. ∗ Speaker. Emailaddress: bedrood.m@gmail.com 101</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Filippov algebra, nilpotent n-Lie algebra .</t>
+          <t>Filippov algebra, nilpotent n-Lie algebra . MSC(2020): 117B05, 17B30. 1. Introduction The concept of n-Lie (Filippov) algebras introduced by Filippov [4], as an n- ary multilinear and skew-symmetric operation which satisfies the generalized Ja- cobi identity [[x ,...,x ],y ,...,y ]= (cid:80)n [x ,...,[x ,y ,...,y ],...,x ]]. The 1 n 2 n i=1 1 i 2 n n study of n-Lie algebras is important, since it is related to geometry and physics. Theclassificationofn-Liealgebrasrespecttodimensionisafundamentalproblem. There are many papers on the classification of n-Lie algebras. For example, Bai etal. [1]classifiedalln-Liealgebrasofdimensionn+2onthealgebraicallyclosed fields with characteristic zero. In 1986, Kasymov [7] studied some properties of nilpotent and solvable n-Lie algebras. An n-Lie algebra A is called nilpotent if As = 0 for some non-negative integer s, in which Ai+1 is defined inductively as A1 = A and Ai+1 = [Ai,A,...,A]. The n-Lie algebra A is nilpotent of class c provided that Ac+1 = 0 and Ac ̸= 0. The nilpotent n-Lie algebras of di- mension n + 3 and nilpotent n-Lie algebras of class two and dimension n + 3, n+4, n+5 and n+6 classified in [3, 2, 5, 6]. The center of A is defined by Z(A)={x∈A:[x,A,...,A]=0}. 2. Main results Inthissection,weclassify(n+4)-dimensionalnilpotentn-Liealgebrasofclass 3 and 4 with 4-dimensional derived subalgebra. We know the (n+3)-dimensional non-abeliannilpotentn-Liealgebrasforn&gt;2overanarbitraryfieldareH(n,1)⊕ F(2), A ⊕ F(1), A 1 ≤ i ≤ 5. Let A be a (n + 4)-dimensional n,n+2,1 n,n+3,i nilpotent n-Lie algebra with the derived subalgebra of dimension four with basis ∗ Speaker. Emailaddress: darabi@esfarayen.ac.ir 106</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gro¨bner bases, Cousin complex, Monomial order .</t>
+          <t>Gro¨bner bases, Cousin complex, Monomial order . MSC(2020): Primary 13P10; Secondary 13D02. 1. Introduction Oneofthecentralproblemsinalgebraicgeometryistounderstandtheproper- ties of algebraic varieties, which are geometric objects that are defined by polyno- mialequationsoverafieldofcoefficients. Oneimportanttoolinstudyingalgebraic varieties is the theory of Gr¨obner bases, which provides a way to compute alge- braic invariants of an ideal generated by a set of polynomials. A Gr¨obner basis is a special set of generators for an ideal, which has certain properties that make it useful for computation. In particular, Gr¨obner bases provide a way to solve poly- nomialequations,computethedimensionofanalgebraicvariety,andcomputethe intersection of algebraic varieties. Therefore, Gr¨obner bases have become an es- sentialtoolinmanyareasofmathematics,includingalgebraicgeometry,computer algebra, and coding theory. However, computing Gr¨obner bases can be compu- tationally expensive, especially for large ideals or in high dimensions. Therefore, researchershavedevelopedvariousalgorithmsandtechniqueslikeasBuchberger’s Algorithm, F5 Algorithm, Faug`ere’s F4 Algorithm, Janet’s Algorithm, Lazard’s Projection Algorithm to compute Gr¨obner bases efficiently. The reader can refer to[1]and[2]foralgebraicconceptsandreferto[4]and[5]tolearnthecalculations related to obtaining Grubner bases. In this paper, we introduce a new method ∗ Emailaddress: hr bamdad@pnu.ac.ir 112</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>small submodule, semisimple module, hyperedge,</t>
+          <t>small submodule, semisimple module, hyperedge, sum-hypergraph.. MSC(2020): 16D10,16D90, 05C65, 05C20. 1. Introduction Overthepastdecade, studieshaveshownthathypergraphsareusefulinsolv- ingreal-lifeproblems. Hypergraphshavebeensuccessfullyappliedinvariousfields such as network modeling, data structures, system modeling for engineering, cel- lular mobile communication systems, image processing, machine learning, data mining, soft sets, social networks, chemistry, and more. AsubmoduleN ofamoduleP issaidtobeessential(large),providedN∩L= 0 implies L=0, where L is a submodule of P. Changing intersection to sum and zerosubmoduletothewholemodule,asubmoduleK ofP issaidtobesuperfluous (small) provided K +L = P where L ≤ P implies L = P. Note that if every submodule of the module P is a large submodule, then P is called a uniform module. An analogue for a uniform module is a hollow module. The module P is called hollow, if every proper submodule is small in P. A hollow module P with a largest submodule (the sum of all proper submodules of P, which must be the radical of P) is a local module. The sum of all simple submodules of a module P is said to be the Socle of P, denoted by Soc(P). If P has no large submodules, then Soc(P) = P. In this case, we say P is semisimple. The radical of P, denoted by Rad(P) is the sum of all small submodules of P, that is equivalent to the intersection of all maximal submodules of P. ∗ Speaker. Emailaddress: hosseinibehrouz011@gmail.com 118</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UJI ring, 2-UJ ring, involution..</t>
+          <t>UJI ring, 2-UJ ring, involution.. MSC(2020): 16U99,16S99. 1. Introduction Throughout, all rings are associative with an identity. Standardly, U(R) de- notes the set of all units of R, Inv(R) is the set of all involutions of R, Id(R) is the set of all idempotents of R, J(R) stands for the Jacobson radial of R and Z(R) for the center of R [2]. A ring R is called clean if R = U(R) + Id(R). A ring R is called weakly J-clean, provided that R = J(R) ± Id(R). A ring R is said to be JU, provided the equality U(R) = 1+J(R) holds, and weakly JU or, abbteviated WJU, provided the equality U(R) = ±1+J(R) holds [3]. The objective of this article is to generalize these WJU rings. We call them UJI rings. A ring R is called UJI if, for each u ∈ U(R), there are j ∈ J(R) and i ∈ Inv(R) ∩ Z(R) suchthat u = j + i. This is obviously tantamount to U(R) = J(R)+Inv(R)∩Z(R) = (Inv(R)∩Z(R))(1+J(R)). In this paper we obtain some properties of UJI rings. 2. Main results Example 2.1. Any JU and WJU ring is UJI ring. Lemma 2.2. If R is UJI ring and 2∈J(R), then R is JU ring. Theorem 2.3. Let R be a UJI ring. Then the following hold: (1) 2∈U(R) if and only if 3∈J(R). (2) 3∈U(R) if and only if 2∈J(R). Lemma 2.4. Let R be a commutative UJI ring and 1 ∈ U(R)+U(R), Then 2∈U(R). Lemma 2.5. If R is a UJI clean ring. Then 6∈J(R). R Lemma 2.6. If R is a UJI ring. Then is a UJI ring. J(R) ∗ Speaker. Emailaddress: hasanzadeomiid@gmail.com 123</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prime submodule, Classical prime submodule, Weakly</t>
+          <t>Prime submodule, Classical prime submodule, Weakly prime submodule, Weakly prime ideal, Duo ring. MSC(2020): 16D10, 16D80, 16Dxx. 1. Introduction Throughout this article all rings are associative with identity element and all modules are unital. Several authors have extended the notion of prime ideals to modules, see, for example [3], [7]. Weakly prime submodules of modules over commutative rings were introduced by Ebrahimi Atani and Farzalipour in [4]. A proper submodule N ofM iscalledaweaklyprimesubmoduleifwhenever0̸=am∈N,wherea∈R andm∈M,theneitherm∈N oraM ⊆N. LetM bealeftR-module. Aproper submodule P of M is called prime if rRm⊆P, for some r ∈R and m∈M then m ∈ P or rM ⊆ P. Equivalently, P is prime submodule if for any ideal A of R and any submodule N of M such that AN ⊆ P, either AM ⊆ P or N ⊆ P. It is clear that each prime submodule is weakly prime. For every submodule N and K of an R-module M, we denote by (N : K) the subset {a ∈ R | aK ⊆ N} of R R, which is an ideal of R. The annihilator of K which is denoted by Ann (K) R is (0 : K). If Ann (K) = 0, then K is called a faithful submodule of M. In R R particular, if Ann (M)=0, then M is called a faithful module. We know that R R is a right (left) duo ring if every right (left) ideal of R is an ideal. It is easy to see that if R is a left duo ring, then xR⊆Rx, for each x∈R. In this paper we introduce the concept of classical prime submodule. This conceptisthegeneralizationofthenotionofweaklyprimesubmodulestomodules ∗ Speaker. Emailaddress: marziyejamali@gmail.com 126</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S˜ostak L-fuzzy topological spaces,L-uniform spaces, L-</t>
+          <t>S˜ostak L-fuzzy topological spaces,L-uniform spaces, L- Hutton uniform spaces . MSC(2020): 54A40,54E15. 1. Introduction Fuzzy topology is a type of topology defined on a lattice. The theory of fuzzy topology was initiated by Chang [1], and many authors have developed a general approach to the study of topological-type structures on fuzzy powersets. H¨ohle[2] andS˜ostak[5]introducedL-fuzzytopologicalspaces,whichgeneralizeChang[0,1]- topological spaces , and analyzed their fixed-basis foundations for L-valued fixed bases . The literature extensively covers the study of uniformity structure on L- valuedspaces,withquasi-uniformitybeingausefultoolforinvestigatingtopology, proximity, closure, and interior operators. Several different approaches exist for L-fuzzy quasi-uniformities in fuzzy sets, such as Hutton’s unification approach[3] based on powersets of the form (LX)LX , Lowen’s [4] and H¨ohle[2] entourage ap- proach based on powersets of the form LX×X . In this paper, we introduce a newdefinitionoffuzzyuniformspacebyintroducingtheconceptofagradationof uniformityonanon-emptysetX.Specifically,wepresentthenotionsofL-uniform spaces, and L-Hutton uniform spaces. We investigate the relationship between ∗ Speaker. Emailaddress: m-yaghoubi@pnu.ac.ir 131</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>weakly reversible ring, polynomial ring,</t>
+          <t>weakly reversible ring, polynomial ring, semicommutative ring. MSC(2020): 13B02,16B99. 1. Introduction In here any ring is associative and has identity. A ring R is named reversible if xy = 0 leads us yx = 0 for all x,y ∈ R. This ring and its generalizations have been discussed in many articles and very useful results have been obtained about them. We study here an extension of reversible ring named weakly reversible ring in which xy = 0 leads us rysxt is nilpotent, for all x,y ∈ R and r,s,t ∈ R. A ring that all its right ideals are ideals, is named right duo. We assert that right duo rings are weakly reversible. A ring R with the feature that xy = 0 leads us xRy = 0, for all its elements x,y, is named semicommutative ring. We know by [3, Lemma 1.4], that reversible rings are semicommutative. We admit an example which tells us that weakly reversible rings are not presently semicommutative. Further, we assert that a ring R is weakly reversible iff R[x] is weakly reversible. Finally, we peruse conditions that the power series ring and skew polynomial ring are weakly reversible ring. 1.1. Some properties of weakly reversible rings. Definition 1.1. Call ring R weakly reversible, if for every its elements x,y, xy =0 leads us rysxt is nilpotent, for all elements r,s,t∈R. Example 1.2. Given (cid:18) Z Z (cid:19) R= 2 2 . 0 Z 2 It is not hard to realize that R is weakly reversible. ∗ Speaker. Emailaddress:masoudiar@gmail.com 136</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>polygroup, pair of group, nilpotent pair of polygroup..</t>
+          <t>polygroup, pair of group, nilpotent pair of polygroup.. MSC(2020): 20N20. 1. Introduction The extension of a nilpotent group has been studied by different authors. For instance In [1] Barzegar and Erfanian introduced the α-nilpitent group. For an automorphisem α of a group G and x,y ∈ G, the α-commutator of x,y is c(x,y) = xyx−1y−α. For N ◁ G the pair (G,N) is called a pair of groups. α Pair of groups has some applications in group theory, for instance Hassanzadeh [3] introduced nilpotency of pair of groups. In 1934, Marty [4] introduced the concept of polygroups as a special hyper- group. Application of hyperstructures have been studied in many branches of mathematics. Now in this paper, we study on polygroup analogue of α-nilpotent pair and attain some of their properties. Also, we get a relation between α-nilpotent pair of polygroups and α-nilpotent pair of groups. A hyperoperation ◦ is a function from R×R into the family of non-empty subsets of R. A hypergroupoid (R,◦) is a non-empty set R with a hyperoperation (cid:83) ◦. If A and B are non-empty subsets of R, then A◦B = a◦b. We use a∈A,b∈B x◦A instead of {x}◦A and A◦x for A◦{x}. Also, (R,◦) is a semihypergroup if for any r,s,t∈R we have r◦(s◦t)=(r◦s)◦t. A semihypergroup (R,◦) is said a hypergroup if for any x∈R we have x◦R=R◦x=R . The condition that for ∗ Speaker. Emailaddress: f.mohammadzadeh@pnu.ac.ir 141</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nonlinear partial differential equations, evolution</t>
+          <t>Nonlinear partial differential equations, evolution equations, symmetries.. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Outline the problem progresses in recent years in the study and analysis of nPDEshavemadesignificantcontributionstotheunderstandingofmanyphysical system. Modelingofphysicalsystemsoftenleadstononlinearevolutionequations of the general from u =k[u], where k[u] is a locally defiv function (or a nonlinear t operator in general) of the function u and its x-derivatives. wellknownevolutionequationsdescribingphysicalphenomenacouldfoundin several domains of applied sciences, we restrict the pool of equations to classical nPDEs, such like the korteweg de vries equation and its varteties, the cylindrical kdv and the generalized kdv modeling the propagation of weakly nonlinear waves isdispersivemedia. Otherwiseawellknownvarietyofthekdvisknownforalong time, the so-called modified kdv equation, describing nonlinear a coustic waves in anharmonic lattices. Here we concontrate our intensions to a less studied unnamed variety of the mkdv equation, which differs from the mkdv equation by a first local-derivative ∗ Speaker. Emailaddress: raziemirzavand@gmail.com 146</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>colocalization, generalized local homology modules,</t>
+          <t>colocalization, generalized local homology modules, representable modules. MSC(2020): 13D45, 13E99. 1. Introduction We first recall some definitions that we will use. A Hausdorf linearly topolo- gized R-module M is said to be linearly compact if F is a family of closed cosets (i.e., cosets of closed submodules) in M which has the finite intersection property, then the cosets in F have a non-empty intersection. A Hausdorf linearly topologized R-module M is called semi-discrete if every submodule of M is closed. Thus, a discrete R-module is semi-discrete. It is clear that artinian R-modules are linearly compact with the discrete topology. So the class of semi-discrete linearly compact modules contains all artinian modules. Moreover, if (R,m) is a complete ring, then finitely generated R-modules are also linearly compact and discrete. Let I be an ideal of the ring R and M,N R-modules. The i-th generalized local homology module HI(M,N) with respect to I is defined by i HI(M,N)=limTor (M/ItM,N). i i t In the special case M =R, HI(R,N)=HI(N) is the i-th local homology module i i HI(N) of N with respect to I. i The cosupport of an R-module M, written Cosupp (M), is the set of primes R psuchthatthereexistsacocyclichomomorphicimageLofM withAnn (L)⊆p. R Note that a module is cocyclic if it is a submodule of E(R/m) for some maximal ideal m ∈ R. A prime ideal p is called coassociated to a non-zero R-module M if there is a cocyclic homomorphic image L of M with p = Ann L. The set of R ∗ Speaker. Emailaddress:m-hatamkhani@araku.ac.ir 152</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mKdV equation, Neother symmetries, direct method,</t>
+          <t>mKdV equation, Neother symmetries, direct method, conservation law. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Noether’ssecondlawstatesthatthereisaone-to-onecorrespondencebetween symmetry groups and conservation laws. The difference between these types of symmetries and geometric symmetries is that, in addition to depending on in- dependent and dependent variables, the derivatives of dependent variables also appear in them. It is important to mention that each single-parameter group is a variational problem. Whether it is derived from geometric symmetries or ob- tained from Neother symmetries, it can lead to the creation of conservation laws, andconversely,anyconservationlawcanbecorrespondedtoavariationalproblem such as these symmetries. Consider the modified Korteweg-de Vries Equation (1) u +u +u2u +u =0 t x x xxx The Lie algebra g of the this equation is spanned by the three vector fields as follow: (2) v =(x+2t)∂x+3t∂t−u∂u, v =∂t, v =∂x 1 2 3 A one-parameter higher-order local transformation can refer to a Lie-Backlund or Noether transformation that isn’t a one-parameter Lie group of point or contact transformations. LieandBacklunddidnotconsiderhigher-ordertransformations, whereas Noether did in her paper on conservation laws. ∗ Speaker. Emailaddress:m.gandomi.60@gmail.com 157</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Q-intuitionistic fuzzy subgroups, norms, conjugate,</t>
+          <t>Q-intuitionistic fuzzy subgroups, norms, conjugate, direct product, normality, homomorphisms.. MSC(2020): 08A72, 20N25, 20K30. 1. Introduction The concept of fuzzy sets was initiated by Zadeh in 1965. Since then it has become a vigorous area of research in engineering, medical science, social science, graph theory etc. Yuan and Lee [6] defined the fuzzy subgroup and fuzzy subring based on the theory of falling shadows. Solairaju and Nagarajan introduced the notion of Q- fuzzy groups in 2009. Anthony and Sherwood [1] gave the definition of fuzzy subgroup based on t-norm in 1977. As a generalization of a fuzzy set, the concept of an intuitionistic fuzzy set was introduced by Atanassov [2]. In previous works [3]-[5], by using norms, we investigated some properties of fuzzy algebraic structures. In this study, we introduced a new algebraic structure of Q- intuitionisticfuzzysubgroupsundernorms(T andC)asconjugate,directproduct, normality,order,normalized,characteristic,compositionandgeneralcharacterris- tic and discussed some important properties of them. 2. Preliminaries Thissectioncontainssomebasicdefinitionsandpreliminaryresultswhichwill be needed in the sequal. For more details we refer to [1]-[6]. ∗ Speaker. Emailaddress: Rasuli@pnu.ac.ir 162</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ring, unit-semi boolean .</t>
+          <t>ring, unit-semi boolean . MSC(2020): 15A23, 15B33, 16U99. 1. Introduction Itisassumedthroughoutthispaper, allringsareassociative, containingiden- tity element 1 (1 ̸= 0). Our phrasing and notation generally agree with [1]. For illustration, U(R) sits for the group of units in R, J(R) for the Jacobson radical inR, Nil(R)forthesetofnilpotentsinR andId(R)forthesetofidempotentsin R. Before presenting our main achievements, we will first present a brief history ofwhatisbestknowninthisfield. Anelementinaringiscalledcleanifitcanbe written as the sum of an idempotent and a unit, and an element is further named strongly clean if such idempotent and unit commute. A ring is (strongly) clean if every its element is (strongly) clean. The notion of a clean ring was instituted by Nicholson in 1977 as an illustration of a ring with idempotents, that can be liftedmoduloanyleft(right)ideal. Inthelasttenyears,manyauthorshavestud- iedclassesofringsdefinedbyreplacing”unit”and/or”idempotent”withdifferent conditionsonringelementsand/orprobablyaddingadditionalrequirementstothe above definition. For example, classes of semi-boolean, uniquely clean, strongly nil-clean rings have all been obtained on this way. Besides, it was defined in [4] the(smallest)classofsemi-booleanringsasthoseringsRforwhicheveryelement isthesumofanelementfromtheJacobsonradicalandanidempotent;theserings were also termed J-clean. This was extended in [2] to the class of rings called ∗ Speaker. Emailaddress: n.pouyan@scu.ac.ir neda.pouyan@gmail.com 168</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>polygroup, soft set, Engel polygroup..</t>
+          <t>polygroup, soft set, Engel polygroup.. MSC(2020): 20N20. 1. Introduction One way for dealing with uncertain problems in engineering, medical science and social science is soft set theory. It was proposed by Molodtsov [4]. Also, it has applications in Rieman integration, probability theory, game theory and etc (see [4]). In1934, Martyintroducedtheconceptofpolygroupsasaspecialhypergroup. In addition, polygroups have been discussed by Corsini , Borzooei , Davvaz and so on (see [1]). Some results of group theory are translated on polygroups such as nilpotent polygroup. Now, in this paper we study on Engel soft polygroup and investigate some properties of it. A hyperoperation ◦ is a mapping from H ×H into the family of non-empty subsets of H. A hypergroupoid (H,◦) is a non-empty set H with a hyperoperation (cid:83) ◦. If A and B are non-empty subsets of H, then A◦B = a◦b. Also, we a∈A,b∈B use x◦A instead of {x}◦A and A◦x for A◦{x}. The structure (H,◦) is called a semihypergroup if a◦(b◦c) = (a◦b)◦c for any a,b,c ∈ H. A semihypergroup (H,◦) is called a hypergroup if for any x∈H, x◦H =H ◦x=H. Definition 1.1. [1]Analgebraicstructure(P,·,e,−1),wheree∈P and−1 is an unitary operation on P, is called polygroup if for any x,y,z ∈P the following conditions hold: ∗ Speaker. mohamadzadeh@pnu.ac.ir 173</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>capable n-Lie algebra, nilpotent n-Lie algebra,</t>
+          <t>capable n-Lie algebra, nilpotent n-Lie algebra, Multiplier. MSC(2020): 117B05, 17B30. 1. Introduction In 1985, Filippov [6] introduced the concept of n-Lie (Filippov) algebra. The center of n-Lie algebra A is defined as Z(A) = {x∈A:[x,A,...,A]=0}. The notion of nilpotent Filippov algebra was defined by Kasymov [7]. A Filippov algebra A is nilpotent if As = 0, where s is a non-negative integer number. Note that Ai is defined as inducted by A1 = A,Ai+1 = [Ai,A,...,A]. The study of n-Lie algebras is important since it has applications in geometry and physics. Beside other problems about n-Lie algebras, classification of n-Lie algebras is a centralprobleminthisarea. ThealgebraicclassificationofFilippovalgebraisalso discussed in the literature. For example, see [6, 1, 3]. LetAbeann-LiealgebraoverafieldΛandA∼ =F/Rforafreen-Liealgebra. ThentheSchurmultiplierM(A)ofAisisomorphicto R∩F2 . Then-Liealgebra [R,F,...,F] Aiscalledacapablewhenthereexistsann-LiealgebraB suchthatA=B/Z(B). The abelian n-Lie algebra F(d) is capable if and only if d ≥ n. Also, the n- Lie algebra H(n,m)⊕F(k) is capable if and only if m = 1. (See [5] for more informations). The following lemma plays a key role in the study of the capability of n-Lie algebras. Lemma1.1. Then-LiealgebraAiscapableifandonlyifdimM(A)&gt;dimM(A)− I dim(A2∩I) for each central ideal I of A. ∗ Speaker. Emailaddress: darabi@esfarayen.ac.ir 179</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>weakly prime ideal, weakly semiprime ideal, duo ring.</t>
+          <t>weakly prime ideal, weakly semiprime ideal, duo ring. MSC(2020): 16N60, 16D25. 1. Introduction Throughout this article all rings are associative with identity element. The structure of weakly prime ideals over non-commutative rings has been studied by Y. Hirano, E. Poon and H. Tsutsui in [4]. We studied some properties of weakly prime ideals and then we define structure of weakly semiprime. Let P be a proper ideal of commutative ring R with identity 1 ̸= 0. D. D. Anderson and E. Smith [1] called P weakly prime if a,b ∈ R and 0 ̸= ab ∈ P impliesa∈P orb∈P. Following[3],anidealI inRisweaklysemiprimeifa∈R and 0̸=a2 ∈I implies a∈I. Nowwedefinetheconceptsthatwewillneed. AnproperidealI ofRiscalled semiprime if J2 ⊆ I implies J ⊆ I for any ideals J of R. A ring R is called semiprimeif0issemiprimeideal. GivenaringR, theprimeradicalandthesetof √ all nilpotent elements are denoted by 0 and Nil(R), respectively. The Jacobson radical of a ring R denoted by J(R) is the intersection of all maximal right (or left) ideals of R. We denoted M (R), the set of n×n matrices over a ring R. n Under addition and multiplication of matrices, M (R) forms a non-commutative n ring with identity. M (P) is an ideal (resp prime ideal) in M (R) if and only if P n n is an ideal (resp. prime ideal) in R. A ring is called reduced if it has no nonzero nilpotent elements; and a ring R is called right (or left) duo ring if every right (or left) ideal of R is a two-sided ideal. ∗ Speaker. Emailaddress: marziyejamali@gmail.com 185</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>closed submodule, semiprime submodule, prime</t>
+          <t>closed submodule, semiprime submodule, prime submodule. MSC(2020): 18A15, 13A02. 1. Introduction Throughout this paper R is a commutative ring with identity and M is an R-module. (α,β)-closed ideals in a commutative ring with identity have been introduced and studied in [1]. ApropersubmoduleP ofM iscalledprimeifrm∈P impliesthatr ∈(P :M) or m∈P. Also, P is called semiprime if rtm∈P implies that rm∈P. For more results on prime and semiprime submodules, see [2], [3]. Let α,β be positive integers with α&gt;β. We define a proper submodule K of M to be (α,β)-closed if rαm∈K implies that rβm∈K for r ∈R and m∈M. On the other hand, K is called (α,β)-closed submodule of M if IαL⊆K implies that IβL⊆K where I is an ideal of R and K is a submodule of M. Clearly, every (α,1)-closed submodule is semiprime. In this paper, we characterize (α,β)-closed submodules, which are a general- ization of (α,β)-closed ideals. 2. Some results ItisclearbydefinitionthatifK isan(α,β)-closedsubmoduleofanR-module M, then (K : M) is an (α,β)-closed ideal of R. But the converse is not true in R general. ConsiderZ-moduleZ×Z. Letα&gt;2. ThenthesubmoduleK =(7mZ,0) of Z×Z is not (α,β)-closed for every β &lt;α. But (K :Z Z×Z)=0 is prime and so an (α,β)-closed ideal of Z. ∗ Speaker. Emailaddress: Rezvan.Varmazyar@iau.ac.ir 190</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BCK-algebra,(strong)d-algebra,constructivefunctions.</t>
+          <t>BCK-algebra,(strong)d-algebra,constructivefunctions. MSC(2020): 06F35, 20N02. 1. Introduction In 1966, Y. Imai and K. Ise´ki [3, 4] introduced BCK and BCI-algebras as algebras connected with some logics, where the class of BCK-algebras is a proper subclass of BCI-algebras. In 1999, J. Neggers and H. S. Kim [5], as generaliza- tion of BCK-algebras, introduced the notion of d-algebras and studied among relations between d-algebras and oriented digraphs. P. J. Allen [1] constructed a multitude of d-algebras related to constructive function triples on R and on in- tegral domains. In 2010, J. S. Han et al. [2] defined several special varieties of d-algebras, such as strong d-algebras, (weakly) selective (pre-) d-algebras. In [6], A. Rezaei et al. introduced a notion of K-nonvanishing map on a field K, and obtained polynomially defined d-algebras, as well as some conditions for these to be strong d-algebras. Moreover, they investigated some relations between polyno- mially defined d-algebras with left-zero semigroups and β-algebras. The present paper is a continuation of [1] and [6], where the property of d- algebras and polynomial defined d-algebras were studied. Here we consider the notion of a triple (ϕ,φ,ψ) called a constructive function triple on R, to construct aclassofstrongd-algebras. Weobtainsomeconditionsforad-algebraonRtobe strong. 2. Preliminaries A d-algebra ([5]) is an algebra (X, ∗, ξ) of type (2,0) satisfying the following conditions: (I) α∗α=ξ, ∗ Speaker. kghadimi@pnu.ac.ir 193</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Locally Noetherian, Locally Artinian, S-acts, Monoids.</t>
+          <t>Locally Noetherian, Locally Artinian, S-acts, Monoids. MSC(2020): 20M30. 1. Introduction Animportantandinterestingdiscussionofmoduletheoryistostudytheprop- erties of noetherian and artinian modules. A module is called locally noetherian (locallyartinian)ifallitsfinitelygeneratedsubmodulesarenoetherian(artinian). Formonoids,descendingandascendingchainconditionsoncommutativemonoids with zero are discussed in [1]. Then, in the category of S-acts, the concepts of finitely (Rees) cogenerated S-acts are investigated in [3]. In particular, (Rees) noetherian and artinian S-acts are studied in [4]. An S-act is said to be (Rees) artinian (noetherian) if it satisfies descending (ascending) chain condition on its (Rees) congruences. An S-act is artinian if and only if each of its factor acts is finitelycogenerated. Usingtheresultsin[4],inSection2,weintroducethenotions of (Rees) locally artinian (noetherian) S-acts. We say that an S-act is (Rees) lo- cally artinian (noetherian) if every its finitely generated subact is (Rees) artinian (noetherian). Then, we present some general properties of such acts. Moreover, weinvestigatethebehaviorof(Rees)locallynoetherianand(Rees)locallyartinian S-acts under Rees short exact sequences. Throughout the paper, S and A are used to denote a monoid and a right S S-act, respectively. A nonempty subset B of a right S-act A is called a subact S ∗ Speaker. Emailaddress: khosravi@fasau.ac.ir 198</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algebra, productivity, business Management,</t>
+          <t>Algebra, productivity, business Management, Mathematics. MSC(2020): 00Axx, 00A05, 00A06. 1. Business and Algebra Algebra is used in business for a variety of reasons. Business math skills can help people and companies to make better decisions, understand problems more thoroughly, and see the long-term impact of their choices [6]. One specific reasonbusinessmathisusedrelatestokeepingtrackoffinancialtransactions. The accuraterecordingandmaintenanceoffinancialrecordsareessentialforbusinesses ofallsizes. Businessesusealgebratotrackincomeandexpenses,preparefinancial statements, and make informed decisions about where to allocate their resources [2]. Another reason algebra is used in business is to make calculations and predic- tions. Businesses use mathematical concepts such as probability and statistics to make decisions about pricing, production, and investment. By understanding and using these concepts, businesses can make better decisions that lead to increased profits. Algebra is also used in business to understand and analyze data. Data is collected by businesses for a variety of purposes, such as understanding customer ∗ Speaker. Emailaddress: sariolghalam@pnu.ac.ir 203</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lfuzzy topological spaces, uniformity structure, L-</t>
+          <t>Lfuzzy topological spaces, uniformity structure, L- Hutton uniform spaces,. MSC(2020): 54A40,54E15. 1. Introduction Fuzzy topology is a type of topology defined on a lattice. The theory of fuzzy topology was initiated by Chang [1], and many authors have developed a general approach to the study of topological-type structures on fuzzy powersets. H¨ohle[2] andS˜ostak[5]introducedL-fuzzytopologicalspaces,whichgeneralizeChang[0,1]- topological spaces , and analyzed their fixed-basis foundations for L-valued fixed bases . The literature extensively covers the study of uniformity structure on L- valuedspaces,withquasi-uniformitybeingausefultoolforinvestigatingtopology, proximity, closure, and interior operators. Several different approaches exist for L-fuzzy quasi-uniformities in fuzzy sets, such as Hutton’s unification approach[3] based on powersets of the form (LX)LX , Lowen’s [4] and H¨ohle[2] entourage ap- proach based on powersets of the form LX×X . This paper introduces the notions of L-Hutton uniform spaces and L-uniformities, and investigates the relationship betweenL-fuzzytopologicalspacesandL-Huttonuniformspaces. Wedemonstrate that every [0,1]-fuzzy topological space is Hutton [0,1]-quasi-uniformizable. Fi- nally, we establish the relation between Hutton L-uniformities andL-uniformities ∗ Speaker. Emailaddress: m-yaghoubi@pnu.ac.ir 207</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mKdV equation, Neother symmetries, direct method,</t>
+          <t>mKdV equation, Neother symmetries, direct method, conservation law. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Noether’ssecondlawstatesthatthereisaone-to-onecorrespondencebetween symmetry groups and conservation laws. The difference between these types of symmetries and geometric symmetries is that, in addition to depending on in- dependent and dependent variables, the derivatives of dependent variables also appear in them. It is important to mention that each single-parameter group is a variational problem. Whether it is derived from geometric symmetries or ob- tained from Neother symmetries, it can lead to the creation of conservation laws, andconversely,anyconservationlawcanbecorrespondedtoavariationalproblem such as these symmetries. Consider the modified Korteweg-de Vries Equation (1) u +u +u2u +u =0 t x x xxx The Lie algebra g of the this equation is spanned by the three vector fields as follow: (2) v =(x+2t)∂x+3t∂t−u∂u, v =∂t, v =∂x 1 2 3 A one-parameter higher-order local transformation can refer to a Lie-Backlund or Noether transformation that isn’t a one-parameter Lie group of point or contact transformations. LieandBacklunddidnotconsiderhigher-ordertransformations, whereas Noether did in her paper on conservation laws. ∗ Speaker. Emailaddress:m.gandomi.60@gmail.com 213</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>right gr-ring, power series, symmetric ring, self injective.</t>
+          <t>right gr-ring, power series, symmetric ring, self injective. MSC(2020): 16P99, 16D25. 1. Introduction Any ring here is associative and has identity element. Define a ring duo, if its one sided ideals are ideals. Reversible rings have been the subject of many researches so far. These rings R with the feature that xy =0 thus yx=0, for all x,y ∈R. Marks in [5], studied the connection between reversible, symmetric and duorings. CallaringRsymmetric,ifforeveryx,y,z ∈R,xyz =0yieldsyxz =0. The study of reversible rings continued in [4]. In the case that R is reversible, we see in [4] that R[x] is not necessarily reversible. Idempotents of reversible and pseudo-reversible rings was studied in [2]. A pseudo-reversible ring is a ring R in whichforx,y ∈R,ifxy isanonzeroidempotentelementofR,thenxy =yx. The sense of i-reversible ring which was defined in [3], is a ring in which 0̸=xy is an idempotent yields yx is an idempotent. In [3], it was shown that reversible rings are i-reversible, but i-reversible rings are not necessarily reversibles. In continuation of previous researches about reversible ring, in [6], we intro- duced a class of reversible rings called right gr-ring. This ring R with the feature that for every its right ideal I, xy ∈I infer that yx∈I, for all x,y ∈R . In here, we assert that if R is a ring such that R[[x]] is a right gr-ring, then R is also a right gr-ring. Moreover, we study situations which R[[x]] is a right gr-ring. For this aim, it is proved that if R is a von Neumann right gr-ring, then R[[x]] is a symmetric ring. Finally, if R is a von Neumann right gr-ring such that ∗ Speaker. Emailaddress:masoudiar@gmail.com 218</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>character graphs, eigenvalue, matching number, cut</t>
+          <t>character graphs, eigenvalue, matching number, cut vertex. MSC(2020): 20E45, 05C25, 05C76. 3. Introduction Consider a finite group G. By the set Irr(G) denotes irreducible characters of the group G and the corresponding its degree set is cd(G) = {ϕ(1) : ϕ ∈ Irr(G)}. Also by the set ρ(G), we mean primes that they divide at least one character degree in cd(G). A vast study has been investigated the algebraic structure of groups through the study of associated graphs. One such graph which is denoted by ∆(G), is called as the character graph of G. Note that this graph is simple, undirected and ρ(G) is its vertex set, where r,s ∈ ρ(G) are adjacent vertices in ∆(G), iff there exists ϕ(1)∈ cd(G) such that it is divisible by rs. Characterizing thegraphsthatcanserveascharactergraphshasbeenatopicofinterestformany researchers, which for more detail, we refer the reader to [1, 2] Perfect matchings, cut vertices and the size of a character graph can have a significant impact on the structure of the underlying group. Here, we focus on the effects of perfect matchings and cut vertices on the character graph of a group. Additionally, we concentrate on the structure of ∆(R×S) where R,S are non-abelian groups. ∗ Speaker. Emailaddress: hosseinzadeh@ausmt.ac.ir 225</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Insurance Fraud, Network analysis, Algorithm, Graph,</t>
+          <t>Insurance Fraud, Network analysis, Algorithm, Graph, Random process.. MSC(2020): 05C82, 91B30. 1. Introduction Fraudintheinsuranceindustryisavoluntaryacttoobtainbenefitsandillegal benefits from insurance organizations and companies. In other words, all matters that lead to the loss of functional trust and confidence among the elements of the insuranceindustryareconsideredfraudintheinsuranceindustry. Currently,fraud isoneofthemostimportantrisksthatorganizationsandinsurancecompaniesface. Cheatinginanywayisunpleasantbecausetheorganizationsuffersfinanciallosses asaresult. Fraudintheinsuranceindustryisverydiverseandhappensfrequently anddailyaroundus. Amongthemostobviousexamplesofinsurancefraud,wecan mention the creation of fake accidents to receive financial and physical damages. In general, frauds can be classified based on three important criteria: ”source of creation”,”severityoffraud”and”timeoffraud”. Fraudsaredividedintointernal and external categories according to the source of its creation. Internal fraud is a fraudcommittedbysomeoneinsidetheinsuranceindustry,whichincludeschanges ∗ Speaker. Emailaddress: hamzeh@irc.ac.ir 230</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>domination number, zero divisor graph, ideal-based zero</t>
+          <t>domination number, zero divisor graph, ideal-based zero divisor graph, annihilating ideal graph. MSC(2020): 05C75, 13H10. 1. Introduction AssociatingagraphwitharinggoesbacktopaperofBeck[1]in1988,wherehe introducedtheideaofzerodivisorgraphs. LetRbeacommutativeringwithiden- tity. ThezerodivisorgraphΓ(R)ofaringR,isanundirectedgraphwhosevertices are all of the elements of Z(R)\{0} such that there is an edge between vertices a andbifandonlyifa̸=bandab=0. Redmondgeneralizedthezerodivisorgraph notion by replacing elements whose product is zero with elements whose product lies in some ideal I of R. Let R be a commutative ring with non zero identity and I be an ideal of R. The ideal-based zero divisor graph of R, is an undirected graph, denoted by Γ (R), with vertices {x∈R\I :xy ∈I for some y ∈R\I} I where distinct vertices x and y are adjacent if and only if xy ∈ I. Therefore, if I =0 then γ (Γ(R))=γ(Γ(R)). I Also we call an ideal I of R, an annihilating ideal if there exists a non zero ideal J of R such that IJ =0. Let A(R) be the set of all annihilating ideals of R. The graph with the vertex set A(R)∗ = A(R)\{0} such that two distinct vertices I and J are adjacent if and only if IJ = 0, Is called the annihilating ideal graph AG(R),Whichwasfirstintroducedin[2]. Adominatingsetforagraphisasubset of vertices such that every vertex not in the dominating set is joined to at least one member of it by some edge. The domination number γ(G) is the number of verticesinasmallestdominatingsetforG. Wecalladominatingsetofcardinality γ(G), a γ-set. A total dominating set of a graph G is a set of vertices of G such that every vertex is adjacent to a vertex in it . The total domination number of ∗ Speaker. Emailaddress: sima.kiani@gmail.com 236</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Social network, community detection, algorithm.</t>
+          <t>Social network, community detection, algorithm. MSC(2020): 91D30, 90B18, 05C82. 1. Introduction Social, technological and information systems can often be described in terms ofnetworks.Thenetworkconsistsofasetofseparateelements(nodes)andconnec- tions between elements (links). A graph can be used to explain the network as a mathematical structure.Oneof theimportant issues insome networks isdetection community. In fact, communities are groups of network nodes that are closely related to each other and have little connection with nodes outside the commu- nity. Communities can be used to extract useful information from networks. At thefirsttime,in2004,NewmanandGirvan[2]introducedameasureforquantita- tivelymeasuringthequalityofcommunitydetectionalgorithmscalledmodularity, which is shown by Q. Modularity measure Q defined as compare fraction of edges within the cluster to expected fraction in random graph with identical degree. The modularity measure of a network can be written as: (1) Q= 1 (cid:88) (A − k i k j)δ(C ,C ) 2m i,j 2m i j i,j where A=[A ] is the adjacency matrix, k and k are the degrees of nodes i and i,j i j j respectively, m is the total edge in the network, C and C are the community i j assignments of nodes i and j respectively, and δ(C ,C ) is the Kronecker delta i j function which equals 1 if C =C and 0 otherwise. i j ∗ Speaker. Emailaddress: h.taha64@yahoo.com 239</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>clique, entropy.</t>
+          <t>clique, entropy. MSC(2020): 05C35, 94A17. 1. Introduction Entropyisacentralconceptininformationtheoryandhasbeenusedtoprove several combinatorial inequalities, as demonstrated in [3] and [4]. In this paper, we leverage entropy to establish a series of inequalities for the number of cliques of varying sizes in a graph. All random variables are assumed to be discrete and finitely supported. Let X be such a variable and denote the support of X by supp(X). The entropy of X is defined by the following formula: (cid:88) H(X)=− Pr(X =x)logPr(X =x), x∈supp(X) where the base of the logarithm is 2. Note that H(X) only depends on the distri- bution of X and not the values taken by X. For a given support, the entropy is maximized for a variable with a uniform distribution over that support, and the maximum value is the logarithm of the size of the support [1, Theorem 2.6.4]. The following theorem, which is called the Shearer’s lemma, is the essential ingredient of the proof of our main result. Some special cases of this lemma have been proved in [3] and the general case can be found in [2]. Note that [k] = {1,...,k}, and when F = {i ,...,i } and i &lt; ··· &lt; i , X denotes the 1 r 1 r F tuple (X ,...,X ). i1 ir Theorem 1.1. Consider k random variables X ,...,X and suppose that F 1 k is a collection of subsets of [k] such that every element of [k] belongs to at least d ∗ Speaker. Emailaddress: ghodrati@sru.ac.ir 245</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sombor index; Sombor energy.</t>
+          <t>Sombor index; Sombor energy. MSC(2020): 05C07, 05C09, 05C31. 1. Introduction Throughoutthispaperallgraphsallsimple. LetG=(V,E)beasimplegraph with vertex set V = {v ,v ,...,v } and edge set E = E(G), and let |V(G)| = n 1 2 n and|E(G)|=m. Wewritev v ∈E(G)iftheverticesv andv areadjacent. The i j i j degree of a vertex v is d =|N(v)| where N(v) is the open neighborhood of vertex v v. By K and K we mean the compete graph and its complement, respectively. n n The adjacency matrix A = A(G) of a graph G is defined by its entries as a =1ifv v ∈E(G)and0otherwise. Letλ ⩾λ ⩾···⩾λ betheeigenvalues ij i j 1 2 n of the adjacency matrix of G. The energy of G is defined as n (cid:88) E =E(G)= |λ |. i i=1 The concept of energy was first used by Gutman in chemistry to approximate π-electron energy. Extensive research has been done on energy of graphs. Sombor index of a graph is a new topological index that recently has defined by Gutman [2]. The Sombor index of a graph G is (cid:88) (cid:112) SO(G)= d2 +d2, u v uv∈E(G) where d isthe vertexdegree ofv. TherearesomepapersonSombor indexabout v properties of this index, see [5, 6] for instance. Similartotheadjacencymatrix, theSombormatrixofG, denotedbyS(G)= (cid:113) [s ], is defined as s = d2+d2 if v v ∈E(G) and 0 otherwise. We denote the ij ij i j i j ∗ Speaker. Emailaddress: mr oboudi@yahoo.com;mr oboudi@shirazu.ac.ir 248</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fixed point, automorphism, θ-function, dihedral group.</t>
+          <t>fixed point, automorphism, θ-function, dihedral group. MSC(2020): 20F28, 20D60. 1. Introduction Suppose that G is a finite group and Aut(G) is the automorphism group of G. Examining the relationship between the structure of a group and structure of its automorphism group is one of the topics of interest in group theory, which has been examined by many authors from different perspectives. In this regard, the fixed points of automorphisms are one of the interesting topics in this field, which have been the focus of many authors, for example, you can refer to [1] and [2]. In [1], the authors defined the θ function for each divisor d of |G|, as the number of automorphisms whose number of fixed points is equal to d and calculated the valuesofthisfunctionforsomeAbeliangroups. In[2], thetafunctionfordihedral groupoforder2q,whereq isaprimenumber,hasbeeninvestigated. Inthispaper, by calculating θ values of dihedral groups D , the values of θ function will be 2pq calculated for a larger class of dihedral groups. 2. Preliminaries Throughout this paper, G will be a finite group and Aut(G) will be its auto- morphism group. We denote the dihedral group of order 2n by D . 2n ∗ Speaker. Emailaddress: s.a.mousavi@qom.ac.ir 252</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>enhanced power graph, power graph, isomorphism..</t>
+          <t>enhanced power graph, power graph, isomorphism.. MSC(2020): 05C12, 91A43, 05C69. 1. Introduction There are many connections between graphs and groups. Generating graphs from semigroups and groups has a long history. The commuting graph, power graph, enhanced power graph, have been introduced to explore the properties of algebraic structures using graph theory. The concept of a power graph was introduced in the context of semigroup theory by Kelarev and Quinn [3]. Let G be a finite group, the undirected power graphP(G)istheundirectedgraphwithvertexsetG,wheretwoverticesa,b∈G are adjacent if and only if a ̸= b and am = b or bm = a for some positive integer →− m. Likewise,thedirectedpowergraph P(G)isthedirectedgraphwithvertexset G, where for two vertices u,v ∈G there is an arc from a to b if and only if a̸=b and b=am for some positive integer m. In this paper we study the same power graphs and enhanced power graphs. Clearly G ∼ = G implies P(G ) ∼ = P(G ). Does the converse hold? In [2], the 1 2 1 2 converse has been considered and it’s is false for finite groups in general. For example, if p is an odd prime and m &gt; 2, besides the elementary abelian group H of order pm, there are non-abelian groups G of order pm and exponent p, so H and Garenon-isomorphicbuthaveisomorphicpowergraphs. Ontheotherhand, it is shown in [2] that if both G and H are abelian then P(G) ∼ = P(H) implies G∼ =H. It is proved that if G is one of the following finite groups: (1) A simple group, (2) A cyclic group, (3) A symmetric group, (4) A dihedral group, ∗ Speaker. Emailaddress: m.mirzargar@email.com 257</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unitary Cayley graph, Domination number, Roman</t>
+          <t>Unitary Cayley graph, Domination number, Roman domination number. MSC(2020): 05C75, 13H10. 1. Introduction LetRbearingandU(R)bethesetofunitelementsofR. TheunitaryCayley graph of R, denoted G(R), is the graph obtained by setting all the elements of R to be the vertices and defining distinct vertices x and y to be adjacent if and only if x−y ∈U(R). In [1] the authors proved that the unitary Cayley graph of R is a regular graph of degree |U(R)| and If R is isomorphic to product of n rings, then G(R) is isomorphic to tensor product of their unitary Cayley graphs. A set D is called a dominating set if every vertex not in D is adjacent to one or more vertices in D. The minimum cardinality of a dominating set of G is the domination number denoted by γ(G). Roman domination is a variation of domination introduced by ReVelle [3, 4]. TheconceptofRomandominationcanbeformulatedintermsofgraphs. Wecon- sideronlysimplegraphs,namelyG,withvertexsetV(G)andedgesetE(G). The neighborhood of a vertex v ∈ V(G) is the set N(v) = {u : uv ∈ E(G)} and the closed neighborhood is N[v]=N(v)∪{v}. A Roman dominating function (RDF) of a graph G is a function f :V(G)→{0,1,2} such that whenever f(v)=0 there exists a vertex u ∈ N(v) with f(u) = 2. Let (V ,V ,V ) be the ordered partition 0 1 2 of V induced by f, where V = {v ∈ V|f(v) = i} for i = 0,1,2. Note that there i exists a 1−1 correspondence between the functions f :V →{0,1,2} and the or- dered partitions (V ,V ,V ) of V. Thus, we can write f =(V ,V ,V ). Therefore, 0 1 2 0 1 2 a RDF on graph G can be defined as a function f = (V ,V ,V ) satisfying the 0 1 2 condition that V ≺V , where ≺ means that the set V dominates the set V , i.e. 2 0 2 0 (cid:80) V ⊆ N[V ]. The weight of f is f(v). The Roman domination number 0 2 v∈V(G) γ (G) of G is the minimum weight of RDFs of G. In this paper all of the rings R ∗ Speaker. Emailaddress: sima.kiani@gmail.com 261</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dynamic monopolies, Repetitive Polling Game, majority</t>
+          <t>Dynamic monopolies, Repetitive Polling Game, majority function . MSC(2020): 05C57, 37E15. 1. Introduction Let G = (V,E) be a simple undirected graph on the vertex set {v ,...,v }. 1 n Consider the repetitive polling game on G with following procedure (see [2]): At round 0, each vertex v is colored by color x0(v) which may be black or white. At each round, each vertex (simultaneously) looks at the current colors of vertices in its closed neighborhood, and adopts the more common color (namely, the one occurring at the majority of its neighbors) as its new color. More precisely, if we denote the closed neighborhood of the vertex v by N[v] and the global state of the graph after round t by Xt = (xt(v ),...,xt(v )) (xt(v) is the color at vertex 1 n v, after round t), then at round t+1 each entry of the vector Xt+1 is computed by the the following rule: If at round t more than half of the elements of N[v] are colored with c, then at round t+1 the vertex v will be c (c∈{white,black} and xt+1(v) = c). If at round r exactly half of the elements of N[v] have white color and other half of it are black, then we say that there is a tie. In this case v is colored at round t+1 by white (xt+1(v) = white). An example for the resulting ∗ Speaker. Emailaddress:leilamusavi.math@gmail.com 264</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LDPC codes, girth, affine permutation matrix..</t>
+          <t>LDPC codes, girth, affine permutation matrix.. MSC(2020): 11H71, 11T71, 68P30. 1. Introduction Low-densityparity-check(LDPC)codes[1],asamainclassoferrorcorrecting linear codes, can be specified by their sparse parity-check matrices (PCM’s) and their associated Tanner graphs. Although the minimum-distance of LDPC codes is less than that of the best known linear codes, due to their structures, they are suitableforlow-complexityiterativedecodingmethods,suchasPearl’sbeliefprop- agation(BP)algorithm,adoptedinmanypracticalapplications. Theperformance of LDPC codes of small length may be strongly affected by their cycle properties suchasgirth. Infact,thegirth,i.e. theshortestcyclesintheTannergraph,isone important factor [2, 3, 4, 5, 6] to design LDPC codes with good error-correcting properties. Quasi-cyclic (QC) LDPC codes [6] are the most promising class of structured LDPC codes due to their ease of hardware implementation using simple shift registers and excellent performance over noisy channels when they are decoded by message-passing algorithms. The PCM’s of QC-LDPC codes are comprised of blocks of circulant matrices, classified by the researchers as type-I, type-II and type-III QC-LDPC codes, if each block is a combination of at-most one, two and three circulant permutation matrices (CPMs), respectively. On the other hand, recently,someattentionhavebeenpaidonaclassoflow-densityparity-checkcodes from affine permutation matrices, called (Type-I) APM-LDPC codes, in [2, 3, 4], ∗ Speaker. Emailaddress: zghbaba123@gmail.com 270</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(k,h)-Pell-Lucas sequence, Eigenvalue, Determinant,</t>
+          <t>(k,h)-Pell-Lucas sequence, Eigenvalue, Determinant, Spectral norm. MSC(2020): 11B83, 05A15. 1. Introduction Buenoin[1]consideredaparticularrightcirculantmatrixinvolvingFibonacci sequence and obtained the formulae for the Euclidean norm and eigenvalues of thismatrix. Bozkurt[2]computedthespectralnormsofsomematricesconnected integer sequences such as Fibonacci, Lucas, Pell and Perrin numbers. The authos in [3] studied (k,h)-Pell sequence and (k,h)-Pell-Lucas sequence and found a formulae of nth term and sum of the first n terms of these sequences. In thispaperweobtainsomeformulastocomputingtheeigenvaluesanddeterminants of circulant matrices involving these sequences. Then, we give upper and lower bounds for the spectral norm of them and will present numerical example related toeigenvalues, determinantsandEuclideannormsofparticularcirculantmatrices connected(k,h)-Pellsequenceand(k,h)-Pell-Lucassequencefork =1andh=1. The Pell sequence {P } has the recursive relation n P =2P +P , n n−1 n−2 [3], where P = 0,P = 1. Now, we consider a generalization of this sequence [3] 0 1 which is called (k,h)-Pell sequence and is denoted by Γ . This sequence has the n recursive relation (1) Γ =2kΓ +hΓ , n n−1 n−2 ∗ Speaker. Emailaddress: petroudi@pnu.ac.ir 276</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Domination, roman domination, t-restricted pebbling</t>
+          <t>Domination, roman domination, t-restricted pebbling configuration, optimal pebbling number, pebbling number.. MSC(2020): 05C99. 1. Introduction Graph pebbling is a network optimization model for the transportation of resources that are consumed in transit. Electricity, heat, or other energy may dissipateasitmovesfromonelocationtoanother, oiltankersmayuseupsomeof the oil it transports, information may be lost as it travels through its medium, or military troops may be lost while moving through a region. The central problem in this model asks whether discrete pebbles from one set of vertices can be moved to another while pebbles are lost in the process. A pebbling move across an edge ofagraphtakestwopebblesfromoneendpointandplacesonepebbleattheother endpoint; the other pebble is lost in transit as a toll. Let G = (V,E) be a simple graph of order n. A function f : V → N∪{0} is called a configuration of pebbles on the vertices of G and the quantity w(f) = (cid:80) f(u) is called the weight of f which is just the total number of pebbles u∈V assignedtovertices. Apebblingmove(step)fromavertexutooneofitsneighbors v reduces f(u) by two and increases f(v) by one. A pebbling configuration f is said to be solvable, if for every vertex v, there exists a sequence (possibly empty) ofpebblingmovesthatresultsinapebbleonv. Thepebblingnumberπ(G)equals the minimum number k such that every pebbling configuration f with w(f) = k is solvable. ∗ Speaker. Emailaddress: aghaeefatemeh29@gmail.com † Emailaddress: alikhani@yazd.ac.ir 282</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Domination, independent domination, well independent</t>
+          <t>Domination, independent domination, well independent dominated. . MSC(2020): 05C99. 1. Introduction All graphs considered in this paper are finite undirected graphs without loop nor parallel edge. Let G be such a graph. A non-empty set S ⊆V(G) is a domi- nating set if every vertex in V(G)\S is adjacent to at least one vertex in S. The minimum cardinality of all dominating sets of G is called the domination number of G and is denoted by γ(G). For a detailed treatment of domination theory, the readerisreferredto[5]. Themaximumcardinalityofaminimaldominatingsetin G is called the upper domination number of G denoted by Γ(G). The difference between these two parameters is called the domination gap of G and denote it by µ (G) = Γ(G)−γ(G). A graph G with µ (G) = 0 is called a well-dominated d d graph. Domination gap was first introduced by Finbow et al. in [2]. An independent set in a graph G is a set of pairwise non-adjacent vertices. A maximum independent set in G is a largest independent set and its size is called independence number of G and is denoted by α(G). A graph is said to be well- covered if all of its maximal independent sets have the same size. In general, a graph G with independence number α(G) is well-covered if and only if G¯ is ∗ Emailaddress: alikhani@yazd.ac.ir † Speaker. Emailaddress: nemati.nasim60@gmail.com 286</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>generalized Laplacian, 2-degree, neighbourhood Zagreb</t>
+          <t>generalized Laplacian, 2-degree, neighbourhood Zagreb index, eigenvalue. MSC(2020): 05C09, 05C92, 92E10. 1. Introduction Throughout this paper G is a simple graph with n vertices and m edges. The vertexandtheedgesetsofGaredenotedbyV(G)={v ,··· ,v }andE(G). The 1 n degree of a vertex v, denoted by d (v), is the number of vertices adjacent to v. G The2-degreeofthevertexv ∈V(G),denotedbyS (v ),isdefinedtobethesum i G i of degrees of neighbours of v . For a vertex u ∈ V(G), there are several notation i for representing the ”sum of degrees of the vertices adjacent to u ” in literature - for example, Cao and Yu et al. used the notation t(u) (and called it 2-degree), Abdo et al. used the notation d and Hagos used S(u). However, following [4] 2,u we use the notation S (u) or simply S(u) or S (due to the obvious reason, as G u S stands for sum) for future use. Note that the average-degree (also known as ∗ Speaker. Emailaddress: sharafdini@pgu.ac.ir 290</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>(k,h)-Pell-Lucas sequence, Consecutive term,</t>
+          <t>(k,h)-Pell-Lucas sequence, Consecutive term, Summation formula, Identity. MSC(2020): 11B83, 05A15. 1. Introduction Mathematicianshavebeenfascinatedbywell-knownsequencesbecauseoftheir interesting and exciting applications in the area of numerical analysis, combina- tory theory, matrix theory and computer sciences. In [1] Bueno studied (k,h)- Jacobsthal sequence of the form T =kT +2hT . n n−1 n−2 Hefoundaformulaofnthtermandsumofthefirstntermsofthissequence. Cerda Morales [2] considered a particular Jacobsthal sequence, namely, q-Jacobsthal se- quence {J } and obtained a generating matrix for the terms of sequence {J } q,n q,kn for a positive integer k. Then by the aid of this matrix, established some new identities for thissequence. The main objectiveof this paperis to investigate new results about (k,h)-Pell sequence and (k,h)-Pell Lucas sequence. The well-known Pell sequence {P } has the recursive relation n P =2P +P , n n−1 n−2 [3], where P = 0,P = 1. Now, we consider a generalization of this sequence [3] 0 1 which is called (k,h)-Pell sequence and is denoted by Γ . This sequence has the n recursive relation (1) Γ =2kΓ +hΓ , n n−1 n−2 ∗ Speaker. Emailaddress: petroudi@pnu.ac.ir 295</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seidel matrix, Seidel Laplacian matrix, Eigenvalue,</t>
+          <t>Seidel matrix, Seidel Laplacian matrix, Eigenvalue, Seidel energy.. MSC(2020): 18A32, 05C50. 1. Introduction Let G be an undirected simple connected graph order n and size m, the ad- jacency matrix A(G) = (a ) of G is an n×n symmetric matrix, where a = 1 ij ij if v and v are adjacent in G, zero otherwise. For a graph G, Seidel matrix is i j defined as S(G) = [s ] in which s = −1 if the vertices v and v are adja- ij ij i j cent, s = 1 if the vertices v and v are not adjacent and s = 0 for i = j. ij i j ij Let D(G) = diag(d ,d ,...,d ) be the diagonal degree matrix. The Laplacian 1 2 n matrix of G is defined as L(G) = D(G) − A(G). Let D (G) = diag(n − 1 − S 2d ,n−1−2d ,...,n−1−2d ) be a diagonal matrix in which d stands for 1 2 n i degree of a vertex v in G. Then, in analogy with the ordinary Laplacian matrix, i the Seidel Laplacian matrix of G is defined as S (G) = D (G)−S(G). Note L S that D (G) = D(G)−D(G¯) and S (G) = L(G)−L(G¯). Let λ ,λ ,··· ,λ and S L 1 2 n λL,λL,··· ,λL be the Seidel eigenvalues and Seidel Laplacian eigenvalues of G 1 2 n respectively. The Seidel energy E (G) of a graph G is the sum of the absolute S values of the eigenvalues of G. The Seidel Laplacian energy of G is defined as n (cid:88) n(n−1)−4m E = |λL− | SL i n i=1 ∗ Speaker. Emailaddress: askari@kashanu.ac.ir 301</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>complex networks, heterogeneity measure, upper and</t>
+          <t>complex networks, heterogeneity measure, upper and lower bound . MSC(2020): 68R10, 05C10. 1. Introduction Let G=(V,E) be a simple graph (i.e. finite, undirected graph without loops or multiple edges) on vertex set V ={v ,...,v } and edge set E ={e ,...,e } (so 1 n 1 m n=|V(G)|isitsorder, andm=|E(G)|isitssize). Forv ∈V(G), thedegreeof i v , written by d(v ) or k , is the number of edges incident with v . Let ∆= max i i i i {d : v ∈ V(G)} and δ = min {d : v ∈ V(G)}. A network is an simple graph i i i i consisting of a certain number of nodes or vertices connected by links or edges. A regular network is a graph where each vertex has the same number of neighbors; i.e. everyvertexhasthesamedegree. Anetworkisirregularifalltheverticeshave distinctdegreesexceptforonepair. Complexnetworks,whicharenetworkswhose structureisirregular,complexanddynamicallyevolvingintime,arethestructural skeleton of biological, ecological, technological, and socioeconomic systems [2, 3]. The study of such complex networks has developed into a major field of inter- disciplinary research spanning across mathematics, physics, biology and social sciences[4,5,6]. Theheterogeneitymeasureisasingleindexthatcanquantifythe diversity of connections between vertices or nodes in networks even with different ∗ Speaker. Emailaddress: taherihassan@gmail.com 304</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>perfect star packing, perfect pseudo-matching, fullerene</t>
+          <t>perfect star packing, perfect pseudo-matching, fullerene graphs. MSC(2020): 05C90, 05C70. 1. Introduction A fullerene is a carbon molecule interconnected in pentagonal and hexagonal rings. A fullerene graph is a cubic, 3-connected planar graph with 12 pentagons. The number of hexagons can be either zero or a positive integer greater than one [4]. For all even n≥20 except n=22 exists a fullerene graph on n vertices [4]. A matching of a graph G is a set M of independent edges of G, i.e., a set of edges such that no two edges share a vertex. A matching is said to be perfect if any vertex of G is incident with an edge from it. In 1891, Petersen established that every 3-regular graph with no more than two cut-edges has a perfect matching, which shows that all fullerene graphs have perfect matchings [5]. For given graphs, G and H, a perfect H-packing in G is a spanning subgraph of G whose all components are isomorphic to H. If H is the star graph K , it is 1,3 calledperfectstarpacking. Aperfectpseudo-matchinginagraphGisaspanning subgraphofGwhosecomponentsareisomorphictoK ortoK . Perfectpseudo- 1,3 2 matchingswithtwotypesofcomponentsarecalledmixed. Aninterestingproblem infullerenegraphsiscountingperfectmatchingsandtogivesomeboundsofperfect matchings. (See [1]). The Counting of perfect star packing and perfect pseudo- matchingisanewersubject. T.Doˇsli´cetal. [2]categorizedsomefullerenegraphs that have a perfect star packing and they obtained that every fullerene graph G ∗ Speaker. Emailaddress: m.taheri26@gmail.com 309</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Commuting conjugacy class graph, The generalized</t>
+          <t>Commuting conjugacy class graph, The generalized dicyclic groups.. MSC(2020): 20C15, 20D15. 1. Introduction Suppose G is a non-abelian finite group. The commuting conjugacy class graph, Γ(G), of G is a simple and undirected graph with non-central conjugacy classes of G as its vertex set and two distinct vertices C and D are adjacent if and only if there are c ∈ C and d ∈ D such that cd = dc, [3]. In the mentioned paper, the authors classified all finite groups G with this property that Γ(G) is triangle-free. The commuting conjugacy class graph was first studied by Herzog et al. [2], but they considered the nonidentity conjugacy classes of the group as a vertexset. Thenotionofthecommuting graphofafinitegroupwasintroduced byBrauerandFowler[1]inanoldpaperinwhichtheauthorsinvestigatedgroups of even orders. These authors did not use the graph theory language, but proved some elementary properties of this graph. Suppose X = {∆ ,...,∆ } are a set of undirected graphs with mutually 1 s disjointvertexsets. Thenotation∆ ∪···∪∆ isusedforagraphwiththevertex 1 s sets V(∆ )∪···∪V(∆ ) and the edge sets E(∆ )∪···∪E(∆ ). In the case that 1 s 1 s all members of X are isomorphic, we use the notation sΛ as Λ ∪···∪Λ . 1 1 s The aim of this paper is to calculate the commuting conjugacy class graph of the generalized dicyclic group Dic(A,y,x), where Dic(A,y,x)=⟨A,x|x2 =y, ax =a−1, ∀a∈A⟩ ∗ Speaker. Emailaddress: MA.Salahshour@iau.ac.ir 317</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seidel matrix; Seidel Estrada index.</t>
+          <t>Seidel matrix; Seidel Estrada index. MSC(2020): 05C31, 05C50, 15A18. 1. Introduction Throughout the paper all graphs are simple. They are finite with no loops and direction. Let G=(V(G),E(G)) be a simple graph. The order of G denotes thenumberofverticesofG. Fortwoverticesuandv bye=uv wemeantheedge e between the vertices u and v. For every vertex v ∈V(G), the degree of v is the numberofedgesincidentwithv andisdenotedbydeg (v). Ak–regulargraphisa G graph such that every vertex of that has degree k. The complement of G, denoted byG,isthesimplegraphwithvertexsetV(G)suchthattwodistinctverticesofG are adjacent if and only if they are not adjacent in G. The edgeless graph (empty graph), the complete graph, the cycle, and the path of order n, are denoted by K , K , C and P , respectively. Let t and n ,...,n be some positive integers. n n n n 1 t By K we mean the complete multipartite graph with part sizes n ,...,n . n1,...,nt 1 t In particular, the complete bipartite graph with part sizes m and n is denoted by K . The identity matrix and the matrix whose all of entries are equal to 1 are m,n denoted by I and J, respectively. A Hermitian matrix (or self-adjoint matrix) is a complex square matrix that is equal to its own conjugate transpose. The eigenvalues of Hermitian matrices are real. For every Hermitian matrix of size n, say A, we sort its eigenvalues as λ (A) ≥ λ (A) ≥ ··· ≥ λ (A). The trace and 1 2 n rank of a complex matrix B are denoted by tr(B) and rank(B), respectively. LetGbeasimplegraphwithvertexset{v ,...,v }. Theadjacency matrixof 1 n G, denoted by A(G), is the n×n matrix such that the (i,j)-entry is 1 if v and v i j are adjacent, and otherwise is 0. For more details on the adjacency matrices and their properties, see [2]. The Seidel matrix of G that is denoted by S(G)=[s ] is ij ∗ Speaker. Emailaddress: mr oboudi@yahoo.com,mr oboudi@shirazu.ac.ir 319</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prof. Alireza Ashrafi, Metric graph theory, Topological</t>
+          <t>Prof. Alireza Ashrafi, Metric graph theory, Topological indices, Chemical graph theory.. MSC(2020): 05C12, 05C35, 92E10. 1. Review of Prof. Ashrafi’s Research ProfessorAshrafihasstudiedseveralconceptsingraphtheoryduringhisscien- tific career. Also he is one the pioneers in some of the concepts are widely studied today. Symmetrytheoryingraphsofmoleculesinphysicalchemistry,group-based graphs,metricgraphtheory,biologicalgraphs,etc. Ingeneral,hisresearchcanbe divided into three main parts in the graph theory, which we will explain below. • group-based graphs, • Graph invariant, • Mathematical Chemistry. There are different ways to understand graph groups. One way is to think of them as groups associated with graphs, where each vertex and edge of the graph ∗ Speaker. Emailaddress: mjnajafiarani@gmail.com 323</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>cozero-divisor graph, dual of cozero-divisor graph.</t>
+          <t>cozero-divisor graph, dual of cozero-divisor graph. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Let R be a commutative ring and W∗(R) be the set of all non-zero non-unit elementsofR. GraphΓ(R),thecozero-divisorgraphofR,isagraphwithvertices set W∗(R), and two elements a,b∈W∗(R) are adjacent if and only if a∈/ bR and b∈/ aR. The dual of cozero-divisor graph of a commutative ring(R), is a graph with vertices set W∗(R), and two elements a,b ∈ W∗(R) are adjacent if and only if a∈bR or b∈aR. WecharacterizethedualgraphofZ ,bydecomposingofnintoprimenumber. n 2. Main results Let n be an integer number and we decompose n into prime integers, and so we characterize the dual cozero-divisor graph whit this property. Theorem 2.1. Let R = Z n and n = p 1 α1···p k αk and p i s are prime integer. Then we have above items: 1) let n=p. then we have a field and graph is an empty graph. 2) let n=p p , then Γ(R) contains two disjoint subgraph Γ(p ) and Γ(p ). 1 2 1 2 Proof. Each subgraph Γ(P ), has vertics set &lt; p &gt; and is a con- i i nectedsubgraph. Ontheotherhandwehavep p =n=0, andforeach 1 2 x ∈ W∗(R), we have x ∈/ p p R = 0, therefore tow subgraph Γ(R ) are 1 2 i not connected. Now, if p ,p ≤ 3, thus each subgraph has not any cycle and so 1 2 girth(Γ(R))=diam(Γ(R))=∞. ∗ Speaker. Emailaddress: sazare66@gmail.com 327</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Binary decision (hyper) diagram, Binary decision</t>
+          <t>Binary decision (hyper) diagram, Binary decision (hyper) tree.. MSC(2020): 05C65, 94C10, 05C05. 1. Introduction Definition 1.1. [1] Let V be a finite set, m ∈ N, and for each 1 ≤ i ≤ m, F ⊆ V is an arbitrary subset of V. Then, we call H = (V,F = {F }m ) as a i i i=1 Pseudo hypergraph that each x∈V, is a hyper vertex (for simplicity, we call it a vertex) and for each 1≤i≤m, we call F hyperedges, and for simplicity we show i it as H =(V,{F }m ). i i=1 APseudohypergraphH =(V,{F }m )iscalledahypergraphifforeach1≤i≤m, i i=1 ∅≠ F and (cid:83)m F =V. i i=1 i Definition 1.2. [3]Abinarydecisiontree(BDT)forthevariableorderx &lt; i1 x &lt; ... &lt; x , It has the attached properties: (1), all end vertices are marked i2 in with 0 or 1, (2), all other nodes are labeled by a variable and they have precisely two subtree(children), the 0-child and the 1-child. The edges leading to these children are labeled by 0 respectively by 1, (3), if the root is not a leave, then it is labeled by x ,(4) if a node is labeled by x then, its two children are leaves, i1 in (5), if a node is labeled by x and j &lt; n, then its two children are labeled by ij x . Every path of a decision tree determines an assignment of the variables ij+1 x ,x ,...,x . The Boolean function f(x ,x ,...,x ) represented by a decision i1 i2 in 1 2 n tree T is defined by as f(x ,x ,...,x ) = label of the leaf reached by the path 1 2 n corresponding to the assignment x ,x ,...,x . i1 i2 in ∗ Speaker. Emailaddress: M.Rahmati@pnu.ac.ir 331</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(m,n)-super hyper operation, (m,n)-super hyper</t>
+          <t>(m,n)-super hyper operation, (m,n)-super hyper G-subalgebra.. MSC(2020): 17A70, 17C70. 1. Introduction Definition 1.1. [1] A G-algebra is a non-empty set X with a constant 0 and a binary operation ∗ satisfying the following axioms: (I) x∗x=0, (II) x∗(x∗y)=y for all x,y ∈X. Definition 1.2. [5] Let X ̸= ∅. Then f∗ : Xm → Pn(X) is called an (m,n) ∗ (m,n)-super hyperoperation, where m ≥ 2,n ≥ 0, Pn(X) is the nth-powerset of ∗ the set X, ∅ ̸∈ Pn(X) and Xm = X×X×...×X. Also (X,f∗ ) is called an ∗ (m,n) (cid:124) (cid:123)(cid:122) (cid:125) m times (m,n)-super hyperalgebra. Let f∗ be an (m,n)-super hyperoperation on X and B ,...,B subsets of X. (m,n) 1 m We define (cid:91) f∗ (B ,...,B )= f∗ (x ,...,x ). (m,n) 1 m (m,n) 1 m xi∈Bi If B ⊆Pn(X), then we identify {B} with B. ∗ 2. Super hyper G-subalgebra In this section, we make the concept of super hyper G-subalgebras as an extension of G-subalgebras and seek some of their properties ∗ Speaker. Emailaddress: M.Rahmati@pnu.ac.ir 336</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>compact graph, vertex degree, neighborhood, cut vertex.</t>
+          <t>compact graph, vertex degree, neighborhood, cut vertex. MSC(2020): 05C07, 05C38, 05C75. 1. Introduction Webeginwithrecallingsomedefinitionsandnotationsongraphs. Throughout thispaper,agraphGisanundirectedsimplegraphwiththevertexsetV =V(G) and the edge set E =E(G). A graph is said to be connected if there exists a path between any two distinct vertices. Maximal connected subgraphs of G are called theconnected componentsofGandthenumberofthemisdenotedbyc(G). Acut vertex is a vertex whose deletion increases the number of components. Moreover, inthispaper,weusethenotationω(G)fortheclique number. Acyclewithlength n is denoted by C . Every graph with no cycle is called a forest. Moreovere, we n denote the induced subgraph on X ⊂V(G), by G[X]. A bipartite graph is a graph whose vertex set can be divided into two disjoint parts X and Y such that both of the induced subgraphs G[X] and G[Y] have no edges. Moreover, a complete bipartite graph is a bipartite graph in which every vertex of one part is joined to every vertex of the other part. If the size of one of the parts is 1, then it is said to beastargraph. LetGbeagraph. TheneighbourhoodanddegreeofavertexxofG aredenotedbyN(x)=N (x)andd(x)=d (x),respectively. Also,themaximum G G (minimum) degree of vertices of G is denoted by ∆(G) (δ). An end vertex is a vertex withh degree one. A clique of a graph is its complete subgraph and the number of vertices in the largest clique of graph G, denoted by ω(G), is called the clique number of G. The complete graph of order, denoted by K , is a graph in n whichanytwodistinctverticesareadjacent. Thediameter ofaconnectedgraphG, denotedbydiam(G), isthemaximumdistancebetweenanypairoftheverticesof ∗ Speaker. f.shaveisi@razi.ac.ir 341</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Energy of graph, domination number, perfect matching.</t>
+          <t>Energy of graph, domination number, perfect matching. . MSC(2020): 05C50, 05C69, 05C70. 1. Introduction Let G be a simple graph with n vertices, m edges and having eigenvalues λ ,...,λ . The energy of the graph G denoted by E(G) is defined as the sum of 1 n the absolute values of its eigenvalues. Hence, n (cid:80) E(G)= |λ |. i i=1 The domination number of G, denoted by γ(G), is the minimum cardinality of a dominating set of G. The total domination number of G, denoted by γ (G) is t the minimum cardinality of a total dominating set. The matching number of G, denoted by µ(G), is the size of a maximum matching. A maximum matching is a matching that contains the largest possible number of edges. If a matching covers all vertices of G, then it is called a perfect matching. 2. Main results Lemma 2.1. [4, Thm. 1.1]. Let G be a graph. Then E(G)≥2µ(G). Lemma 2.2. [3]. If G is a graph without any isolated vertex, then µ(G) ≥ γ(G). Lemma 2.3. If H is a proper subgraph of a graph G, then E(H)&lt;E(G). Lemma 2.4. [2, Thm. 3]. A connected graph G of order 2n has γ(G) = n if and only if either G = C or the vertices of G can be partitioned into two sets 4 V and V with a matching between them and satisfying G[V ]=K and G[V ] is 1 2 1 n 2 connected. ∗ Speaker. Emailaddress: sorouhani435@gmail.com 346</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Random graphs, Expectation, Zagreb indices.</t>
+          <t>Random graphs, Expectation, Zagreb indices. MSC(2020): 05C07, 05C80, 60B20. 1. Introduction LetGbeagraphwiththevertexsetV(G)andtheedgesetE(G). Weconsider simple graphs with no loops or multiple edges. The degree of a vertex v ∈ V(G) is denoted by d(v). The Zagreb index, named after the capital of Croatia, is one of the earli- est chemical topological indices to be defined. Chemical graph theory serves as a bridge between mathematics, chemistry, and graph theory, exploring the rela- tionship between molecular diagrams and numerical quantities known as graph parameters. The first Zagreb index, denoted as M (G), and the second Zagreb 1 index, denoted as M (G), were introduced by Gutman and Trinajstic in 1975 [2]. 2 ∗ Speaker. Emailaddress: sara.samaie1981@gmail.com 350</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Soft sets, soft graphs, soft coloring of soft graphs, total</t>
+          <t>Soft sets, soft graphs, soft coloring of soft graphs, total soft coloring of soft graphs.. MSC(2020): 03E75, 03E72, 05C15. 1. Introduction Graph coloring problem is one of the most studied and well known subjects in discrete and combinatorial optimization domain. There are many practical applications that can be modeled and analyzed by graph coloring problems. Soft set theory [5], firstly initiated by Molodtsov, is a new mathematical tool for dealing with uncertainties. It is shown that the soft sets have applications in severalfieldssuchasthesmoothnessoffunctions,operationresearch,gametheory, measurement and probability theory. The applications of soft sets are progressing rapidly and many researchers are focusing on real and practical problems. Many researchersstudiedapplicationsofsoftsetsinvariousalgebraicstructures. Thum- bakara and George [7] applied soft sets in graphs and presented the concept of soft graphs in the specific way. Akram and Nawas in [1] and [2] introduced the concept of soft graph in the broad spectrum and investigated some properties of this structure. Further study of the concept has been done in [3, 6]. In this paper, we introduce the notions of soft coloring and soft chromatic number of soft graph and show that these concepts are generalizations of the proper vertex, edge coloring and chromatic number of graphs. Also, the notion of soft coloring can unify the concepts of vertex and edge coloring of graphs, and coloring of hypergraphs. ∗ Speaker. Emailaddress: r.manaviyat@pnu.ac.ir 354</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Legendre multiwavelet, Galerkin method, condition</t>
+          <t>Legendre multiwavelet, Galerkin method, condition number.. MSC(2020): 65L20, 65N30, 42C40. 1. Introduction We consider the boundary value problem with Dirichlet condition (cid:40) −(p(x)u′)′ =f(x), x∈[0,1] (1) u(0)=u(1)=0. Wesupposef isacontinuousfunctionandp(x)isapositivefunctionwithcontin- uous derivative on I = [0,1]. Using the finite difference method, the problem (1) can be discretized as [2] p u −(p +p )u +p u =h2f , i=1,...,N, i−1 i−1 i−1 i+1 i i+1 i+1 i 2 2 2 2 where u =u(x ), p =p(x ), f =f(x ), x =ih, u =u =0. i i i+1 i+1 i i i 0 N+1 2 2 In summery, above equations can be written in matrix form Lu=f, where   −(p +p ) p 0 ··· 0 0 0 1 3 3 2 2 2  p −(p +p ) p ··· 0 0 0   3 2 3 2 5 2 5 2   . . . . . .  L= . . . . . . . . . . . .     0 0 0 ··· p −(p +p ) p   N−3 N−3 N−1 N−1  2 2 2 2 0 0 0 ··· 0 p −(p +p ) N−1 N−1 N+1 2 2 2 ∗ Speaker. Emailaddress: htabrizidooz@kashanu.ac.ir 361</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Generalized Jacobi polynomials, Lan-Emden equation ,</t>
+          <t>Generalized Jacobi polynomials, Lan-Emden equation , Petro-Galerkin method, Error estimate.. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction In astrophysics, the Lane–Emden equation is a dimensionless form of Pois- son’s equation for the gravitational potential of a Newtonian self-gravitating. In this article, we consider the ODE form of this equation including Riesz fractional derivatives with variable coefficients in the following form [3] ∂αu(x) k ∂βu(x) 1 (1) + + u(x)=f(x), ∂|x|α xα−β ∂|x|β xα−2 where −1 ⩽ x ⩽ 1 , 1 &lt; α ⩽ 2 and 0 &lt; β ⩽ 1 and boundary conditions are u(−1) = u(1) = 0. We give a brief introduction of fractional derivatives [1]. For α∈[k−1,k)inwhichk ∈N,theleft-sidedRiemann-Liouvillefractionalderivative of order α is defined as 1 dk (cid:90) x v(y) (2) RDαv(x)= dy, x∈[a,b], x Γ(k−α)dxk (x−y)α−k+1 a andtheright-sidedRiemann-Liouvillefractionalderivativeoforderαisdefinedas (−1)k dk (cid:90) b v(y) (3) RDαv(x)= dy, x∈[a,b]. x Γ(k−α)dxk (y−x)α−k+1 x ∗ Speaker. Emailaddress: hoorihfakhari@yahoo.com 367</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fuzzy multi-dimensional mappings; g-(linear continuous)</t>
+          <t>Fuzzy multi-dimensional mappings; g-(linear continuous) function; g-differentiability; Directional g-derivative. MSC(2020): 34A07. 1. Introduction Since Zadeh [5] began to study the basic concepts and principles of fuzzy theory,manystudieshavefocusedonthetheoreticalandpracticalaspectsoffuzzy numbers. In 1987, Kaleva [6] discussed fuzzy differentiability and considered the necessary and sufficient conditions for H-differentiability of fuzzy mappings from [a,b] into E. In 2003, Wang and Wu [2] proposed fuzzy mappings from Rn into E by using H-difference, directional derivative, differentiability, and subdifferential. However,theH-differencebetweentwofuzzynumbersoccursonlyinveryrestricted conditions[6]andtheH-differencebetweentwofuzzynumberscannotalwayscome into existence [3]. Then the gH-difference between two fuzzy numbers is defined under less restrictive conditions, although the gH-difference is not always existed. As a result, the generalized difference proposed in [1, 3], by Gomes and Barros, eliminates all the short-comes discussed in the above differences so that the g- difference of two fuzzy numbers always exists [1]. In 2013, Bede and Stefanini studiedandintroducedtheconceptofgeneralizeddifferentiabilityforfuzzy-valued functions by using the new generalization of gH-difference. We introduce the concept of g-differentiability for fuzzy multi-dimensional mappings based on the concept of g-differentiability [1], so that it exists for a larger class of fuzzy multi- dimensional mappings. In this article, characterization is appointed for Fr´echet and Gˆateaux g-differentiability; based on level-set and through differentiability of endpoints real-valued functions a characterization is also offered and explored for directional and partial g-differentiability. The sufficient condition for Fr´echet and ∗ Speaker. Emailaddress: sedaghatfar@yahoo.com 373</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dickson polynomials, neural networks, system</t>
+          <t>Dickson polynomials, neural networks, system identification. MSC(2020): 12D05, 68T07, 93B30. 1. Introduction Systemidentificationisanactivefieldofcontroltheorywithwideapplications. In this field, the inputs and outputs of underlying system is measured and the modelingiscarriedoutusingthem. Duetothedifficultiesinmodelingofnonlinear systems using the first principles, the importance of this context is obvious. Applyingtheartificialneuralnetworksisoneofthemostimportantapproaches in the identification of nonlinear systems. On the basis of polynomial sets, some neural networks have been designed in the literature [4, 1]. In this work, a neu- ral network based on the Dickson polynomials is designed, and utilized for the identification of nonlinear dynamical systems. The rest of this work is continued as follow. In Section 2, the Dickson poly- nomials are introduced. On the basis of Dickson polynomials, a neural network is designed and explained in Section 3. In Section 4, the proposed model is utilized forsystemidentification. InSection5,anexampleisexplained,andtheconclusion is stated in Section 6. ∗ Speaker. Emailaddress: g.ahmadi@pnu.ac.ir 378</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Information measure, uncertainty, entropy, fuzzy set..</t>
+          <t>Information measure, uncertainty, entropy, fuzzy set.. MSC(2020): 94A17 , 62A86 , 60A86. 1. Introduction Fuzzy theory and information theory have many applications in other fields. Fuzzy theory is useful in modeling imprecise systems and systems that require decisions to control the system. Information theory is also used in many branches suchasprobabilitytheory,statistics,financialmathematics,computerscienceand engineering. Statistical theory and fuzzy set theory have both been developed to study patterns involving uncertainty. The first one is suitable for studying pat- terns based on statistical uncertainty (due to random events) and the second one is suitable for studying patterns based on possibilistic (caused by ambiguity and impreciseness). The theory of fuzzy sets was proposed in 1965 by an Iranian sci- entist named Zadeh, but studies and researches in statistics and fuzzy probability started in the eighties. One of the important and fundamental concepts in information theory is en- tropy, which is used as a measure to compare different uncertain systems and was created by Boltzmann to evaluate the degree of disorder of a gas in a closed container. This concept was later used by Shannon in the field of information theory and penetrated the field of fuzzy sets. Information theory quantifies infor- mation, for example, the amount of information transmitted in an event from the sigma field depends on the probability of that event occurring. A mea- sure to quantify the information of an event A from the sigma field is equal to I(A) = −logP(A) and the average information over all the events from the sigma field (the expected value of uncertainty, associated with an experiment ∗ Speaker. Emailaddress: mehdishams@kashanu.ac.ir 384</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>linear regression, correlated covariance structure, time</t>
+          <t>linear regression, correlated covariance structure, time series regression, autoregressive moving average (ARMA) model. MSC(2020): 62J05,62M10, 91B84. 1. Introduction Multiple regression is a tool that allows one to model the linear relationship between a response variable and some explanatory variables [5]. The matrix form of the multiple regression model can be written as: (1) Y =Xβ+ϵ, where Y is n × 1 vector of the response variable, X is n × (k + 1) matrix of k explanatory variables, β is p×1 vector of the unknown regression coefficients (p=k+1),andϵdenotesthen×1vectorsoftheerrorterms. Itisusuallyassumed thatϵ∼ N(0,σ2I ). Iftheseassumptionsaremet,thetheordinary-least-squares n (OLS), in that it find estimate βˆ that minimize the error sum of squares SSE = (cid:80)n ϵ2, provides the best linear unbiased estimate of β. Statistical inference for i=1 i model (1) fitted to data using OLS method, needs to fulfill several assumptions about the random errors, including the assumption of the uncorrelated errors. For the situations, where the data are collected over time or space, it is common for the errors to have a correlated structure, since adjacent observations tend to be similar in both temporal and spatial dimensions. Serial correlation will not affect the unbiasedness or consistency of the OLS estimators, but it does affect theirefficiency. Withpositiveserialcorrelation,theOLSestimatesofthestandard errorswillbesmallerthanthetruestandarderrors. Thiswillleadtotheconclusion that the parameter estimates are more precise than they really are. There will be a tendency to reject the null hypothesis when it should not be rejected [1]. ∗ Speaker. Emailaddress: hamidghorbani@kashanu.ac.ir 390</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>random graph models, network structure .</t>
+          <t>random graph models, network structure . MSC(2020): 05C80, 05C90. 1. Introduction Network data or graphs, a collection of nodes with edges connecting them, appear everywhere in today life. For example, disease-transmission networks, hu- manbrainnetworks,terroristnetworks,ecologicalfoodnetworks(foodweb),social networks, financial transaction networks, academic paper coauthor ships and ci- tations, protein interaction patterns and much more, [3]. Such network data can be modeled as a stochastic graph, see [6]. The nodes of random networks are randomly distributed on the plane and randomly connected to each other using a specific rules. The aim of entering the randomness in their construction is to increase their ability to mimic the observable behavior in real systems. Under- standing the behavior and properties of real-world networks is crucial for various fields, as it can help in designing efficient communication networks, studying the spreadofdiseases,analyzingsocialinteractions,anddevelopingalgorithmsfornet- work analysis. The random graph theory is a multidisciplinary field that applies probabilisticconceptstomodelandanalyzereal-worldnetworks. Thisfieldiscon- cerned with understanding the structure, complexity, and connectivity of various networks, including social networks, biological networks, and the Internet. The ∗ Speaker. Emailaddress: hamidghorbani@kashanu.ac.ir 395</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECM-algorithm, linear mixed models, the canonical</t>
+          <t>ECM-algorithm, linear mixed models, the canonical fundamental skew normal, heavy-tail distribution.. MSC(2020): 62H12, 62F10. 1. Introduction Linear mixed models (LMM) [1] have played important role in analyzing lon- gitudinal data that this data is measured repeatedly. The introduction of LMM paved a broad way to the development of applied statistics for analyzing data in a large variety of fields, specially medicine and bio-statistic. The key feature of LMM is to use multivariate normal distribution for each sample that has been repeat tests. In the case that the sample has participated in all periodic tests, for a set of random vectors Y ,...,Y , the generic form of an LMM model can 1 n theoretically be defined by a linear combination of random effects as iid iid (1) Y =X β+Z B +ϵ , B ∼ N (0,D), ϵ ∼ N (0,Ψ), B ⊥ε , j j j j j j q j p j j whereY ∈Rp,β isag-dimensionalconstanteffectsvectorandp×gknownmatrix j X . Basedonmodel(1),p×q knownmatrixZ describesrelationbetweenY and j j j B for j =1,...,n. j When faced with frequently measures, the problem of missing data should be addressed appropriately before engaging learning algorithms. However, many researchers have proposed the maximum likelihood approach to deal with missing information. TheGaussianLinearmixedmodelslacksrobustnessagainstskewness and kurtesis and may seriously distort the estimates and results. In asymmetric ∗ Speaker. Emailaddress: saeed darijani@yahoo.com 401</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Finite mixture, canonical fundamental skew normal,</t>
+          <t>Finite mixture, canonical fundamental skew normal, outliers, missing information. MSC(2020): 62H12, 62F10. 1. Introduction Unsupervised classification have played important role in analyzing pattern recognition. The introduction of finite mixture model clear a broad way to the development of applied statistics for analyzing data in a large variety of fields, for example,factoranalysisandbio-statistic. Thekeyfeatureoffinitemixtureistouse multivariate normal distribution for each component. The finite mixture models based on normal distribution lacks robustness against skewness and kurtesis and may seriously distort the estimates and results. Missing data is an ubiquitous challenge in multivariate analysis and in finite mixture the problem of missing data cannot be neglected. Multivariate distributions with incomplete data has been considered in the paper, consisting the work by [1]. Severaldifferentasymmetricfinitemixturemodelwithusingtheclassofskew distribution have been suggested in the papers, for example, [3]. Specifically, a random variable Y is said to have a the canonical fundamental skew normal distribution, denoted by CFUSN (µ,Σ,Λ), if it can theoretically be defined by a p linear representation (1) Y =µ+ΛU +U , 0 where,µisalocationparameter,Λisap×q matrix,U isap-dimensionN (µ,Σ), 0 p U is a q-variate standard half-normal random vector, independent of U , and = 0 denotes the equality in distribution. ∗ Speaker. Emailaddress: farzane.hashemi1367@yahoo.com 407</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ordered random variables, test of fit, contingency tables.</t>
+          <t>ordered random variables, test of fit, contingency tables. MSC(2020): 62H17, 65C10. 1. Introduction Analysisofcontingencytablesisoneofthebestwaystoanswermanyquestions in the area of medicine, human, management and economics researches, etc.. [5] introduced an R or C association model and [6] presented a proportional odds modelastwomainapproachesformodelingthesedata. Whenthedataareordinal, the assignment of scores to the categories and the modelling of the empirical distribution are two well -known analysis models. Since, it is necessary to draw a suitable graph before performing statistical analysis, we have used the idea in [2] to draw new graph for ordered categorical data. This paper has the following structure. In section 2, a new chart was proposed for ordered data set in the contingency tables. Section 3 contains two examples to interpret the proposed chart. 2. The new plot Suppose that CT = {n } where i = 1,··· ,I and j = 1,··· ,J be a two-way ij contingency table, which the column variable be an ordinal variable and the rows represent different types of groups or some categorized explanatory variables. In this content, the column variable is a specified score whereas the row variable need not be a score. Let n = (cid:80)J n be a sum of ith row, p(j|i) = nij and i. j=1 ij ni. P(j|i) = (cid:80)j p(k|i) are the conditional percentage of the jth column category k=1 given the ith row and the conditional cumulative percentage function given the ith column. Similarity, n = (cid:80)I n be a sum of jth column, p(i|j) = nij .j i=1 ij n.j ∗ Speaker. Emailaddress: salmanpour@kashanu.ac.ir 413</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vibrating system, Cost minimization,</t>
+          <t>Vibrating system, Cost minimization, Hamilton-Jacobi-Bellman equation. MSC(2020): 93-08. 1. Introduction Vibrating systems are one of the most important structures in engineering that has attracted considerable attention in the past decade. Optimization of these systems has been considered by researchers from different aspects such as cost optimization, size optimization, topology optimization [1]. In this paper, we are going to consider the problem of cost optimization for a harmonic oscillator which is described by the following equation of motion: (1) My¨(t)+Dy˙(t)+Ky(t)=u(t) where y(t) shows displacement, M is mass, D is damping, K is stiffness and u(t) is the force acting on the system. Thevibratingsystem(1)isaccompaniedwithacostfunctionofthefollowingform that should be minimized: 1(cid:90) T (2) J = g(t,y(t),u(t))dt 2 0 In this paper, we are going to consider the problem of minimizing (2) subject to (1) by calculating a suitable input force u(t). In what follows, we will clarify our proposed procedure for solving this minimization problem. ∗ Speaker. Emailaddress: m ayatollahi@pnu.ac.ir 419</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Quasi-equilibrium problem, Hadamar space, Strictly</t>
+          <t>Quasi-equilibrium problem, Hadamar space, Strictly monotone mapping, Proximal point method.. MSC(2020): 65K15, 90C33, 47H09. 1. Introduction Let(X,d)beametricspace. Forx,y∈X,amappingc:[0,l]→X,wherel≥0,is calledageodesicwithendpointsx,y,ifc(0)=x,c(l)=y,andd(c(t),c(t′))=|t−t′|for all t,t′∈[0,l]. If, for every x,y∈X, a geodesic with endpoints x,y exists, then we call (X,d) a geodesic metric space. Furthermore if there exists a unique geodesic for each x,y ∈ X, then (X,d) is said to be uniquely geodesic. A subset C of a uniquely geodesic space X is said to be convex when for any two points x,y∈C, the geodesic joining x and y is contained in C. For each x,y∈X, the image of a geodesic c with endpoints x,y is called a geodesic segment joining x and y and is denoted by [x,y]. Let X be a uniquely geodesic metric space. For each x,y ∈ X andforeacht∈[0,1],thereexistsauniquepointz∈[x,y]suchthatd(x,z)=td(x,y) and d(y,z)=(1−t)d(x,y). We will use the notation (1−t)x⊕ty for denoting the unique point z satisfying the above statement. Definition 1.1. [1] A geodesic space X is called CAT(0) space if for all x,y,z∈X and t∈[0,1] it holds that d2(tx⊕(1−t)y,z)≤td2(x,z)+(1−t)d2(y,z)−t(1−t)d2(x,y). A complete CAT(0) space is called an Hadamard space. ∗ Speaker. Emailaddress: r.lotfikar@ilam.ac.ir 424</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prey-predator model, Cross-diffusion, Hopf bifurcation,</t>
+          <t>Prey-predator model, Cross-diffusion, Hopf bifurcation, Turing instability. MSC(2020): 92B05, 92D25. 1. Introduction In a prey-predator system, a group defense is a strategy used by the prey to protect themselves from predators instead of escape[7]. The group defense behavior of species in the predator-prey system is modeled by a nonmonotonic functional response [1, 6]. As examples of functional responses describing the group defense mechanism we can mention Holling-type IV [5], simplified Monod- Haldane [6], Ivlev-type, and Ivlev-like [2]. Also, the functional response mu (1) g(u)= , p&gt;1, up+c discussed in [3], describes the group defense behavior in prey species. In[4],Patraetal. introducedaprey-predatorsystemwiththefunctionalresponse (1). The authors studied the local asymptotic stability of the interior equilibrium point and the Hopf bifurcation. ∗ Speaker. Emailaddress: y.jalilian@razi.ac.ir 429</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wireless Sensor Network, WSN, network coding,</t>
+          <t>Wireless Sensor Network, WSN, network coding, multicast,optimization problem.. MSC(2020): 18A32, 05C50. 1. Introduction Thenetworkencodingtechniqueworkssothatnetworknodesstoretheirinput packets for a period in memory to combine with other packets and create a new encoded package. Regardless all the benefits and advantages of using network encoding technology, the time constraint for wireless sensor network nodes is a disadvantage for this technique. In this paper, the limited time of sensor nodes in ∗ Speaker. Emailaddress: askari@kashanu.ac.ir 434</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>distributed convex optimization, consensus, gradient</t>
+          <t>distributed convex optimization, consensus, gradient descent method. MSC(2020): 46N10, 93D05, 93D50. 1. Introduction Multi-agentsystemshave attractedinterest fromresearchers overthe lastfew yearsbecauseagentscanagreeonavalueusinginteractionsbetweenthem. Reach- inganagreementonavalueusingcommunicationbetweenagentsiscalledconsen- sus[5]. Duetothewidespreaduseofmulti-agentsystems, thedesignandanalysis of distributed algorithms have become an important research topic. Distributed algorithms use only local calculations and the information exchange of each agent with its neighbors to achieve the specified goals. The consensus-based algorithm is the most widely used distributed algorithm. Distributed consensus-based al- gorithms are extensively applied to solve the distributed optimization problem. The purpose of the distributed optimization problem is to calculate the optimal solution of the cost function by using distributed algorithms. The distributed convex optimization problem has been frequently solved by gradient-based methods [2]-[4]. In [4], an algorithm has been suggested for the distributed convex optimization problem, and it has been considered the commu- nicationnetworktobeundirected. Inaddition,ithasbeenprovedtheexponential convergence of the suggested algorithm by applying the Lyapunov theory. According to the above-mentioned explanations, in this article, the proposed algorithm is designed by combining the gradient method with the consensus algo- rithm of the multi-agent system. A theorem for the convergence of the proposed ∗ Speaker. Emailaddress: ehsan.nzm74@gmail.com 439</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>stochastic gradient descent, decay step size, convergence</t>
+          <t>stochastic gradient descent, decay step size, convergence rate.. MSC(2020): 90C06, 90C15, 90C26. 1. Introduction Stochastic gradient descent (SGD) is a popular optimization algorithm for training machine learning models. It efficiently optimizes high-dimensional ob- jective functions by updating model parameters using gradients computed from subsets of training samples. The effectiveness of SGD depends on selecting the right step size, or learning rate. Afixedstepsizecanleadtoslowconvergenceorovershooting,whileanoverly adaptive step size can introduce instability. Researchers have explored adaptive strategies for adjusting the step size during training. One common approach is using decay step sizes, which gradually reduce the step size over time [1, 2]. This helpsbalanceexplorationandexploitation,enablingquickexplorationinitiallyand fine-tuning later for convergence. The cosine step length is widely used among decay step lengths due to its favorable performance in terms of accuracy and loss function [2]. However, it has a drawback in the initial iterations where it does not yield satisfactory results ∗ Speaker. Emailsoheilshamaee@kashanu.ac.ir 445</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Blind Watermarking, Official Letters, Letter Body</t>
+          <t>Blind Watermarking, Official Letters, Letter Body Detection, Cryptography. MSC(2020): 11T71. 1. Introduction Watermarking is a crucial technique for establishing copyright ownership and authenticity of digital files. Since 1990, digital image watermarking has been in use. However, in 1993, it was introduced as electronic watermarking by Tirkel et al.[1]. Withadvancementsintechnology,moderntechniquessuchasdeeplearning are now commonly used for watermarking [2]. Several studies have investigated watermarking techniques for documents in different languages such as Chinese [3], English [4], etc. In this article, we will focus on the watermarking of official documents in organizations, irrespective of the language used. In [5], a blind watermarking algorithm for images is presented. In this paper, weintroduceablindalgorithmspecificallydesignedforconcealingpersonnelcodes and administrative information associated with official document circulation. Theremainderofthepaperisorganizedasfollows. Insection2,wepresentthe watermarking and extraction algorithms. In section 3, we evaluate the effective- ness of the presented algorithms by examining the results of their implementation on a sample image. Finally, section 4 concludes the paper by highlighting its achievements. 2. Watermarking Algorithm In this section, we present a blind watermarking algorithm for embedding a watermark into a document and an algorithm for extracting the watermark. We ∗ Speaker. Emailaddress: asaeedi@kashanu.ac.ir 451</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inverse eigenvalue problem, Bordered diagonal matrix,</t>
+          <t>Inverse eigenvalue problem, Bordered diagonal matrix, Leading principal submatrix. MSC(2020): 15xx-15A29. 1. Introduction Inverse eigenvalue problems arise in several applications, including system and control theory, neural networks, physics, vibration analysis, and so on [2, 3]. Withrespecttothespectralinformationarisefromtheproblemathandandwhich kind of matrix we are looking for, there are various methods in inverse eigenvalue problems. Here we consider the problem of constructing a symmetric bordered diagonal matrix of the following form from special spectral data:   a b b ··· b 1 1 2 n−1  b 1 ma 1 0 ··· 0    (1) A= b 2 0 ma 1 ··· 0  , a ∈R , b &gt;0 , m∈R.    . . . . . . . . . ... . . .    1 j b 0 0 ··· ma n−1 1 This class of matrices appear in certain symmetric inverse eigenvalue and inverse Sturm Liouville problems, for instance, in the movement equation with some per- turbations in regulation systems in control theory [1, 4, 5] Throughout this paper, we denote the j×j leading principal submatrix of A by A , the characteristic polynomial of A by ϕ (λ) and the eigenvalues of A by j j j j λ(j) ≤ λ(j) ≤ ··· ≤ λ(j) for j = 1,...,n. This work is motivated by the results 1 2 j ∗ Speaker. Emailaddress: s-mashayekhi@araku.ac.ir 457</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Robust set-valued optimization problem, Asymptotic</t>
+          <t>Robust set-valued optimization problem, Asymptotic function. MSC(2020): 49J10, 49K10, 90C26. ∗ Speaker. Emailaddress: z.soltani@kashanu.ac.ir 464</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minimax Theorem, Asymptotic function.</t>
+          <t>Minimax Theorem, Asymptotic function. MSC(2020): 49J10, 49K10, 90C26. ∗ Speaker. Emailaddress: z.soltani@kashanu.ac.ir 466</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Enhanced power graph, power graph, nilpotent groups,</t>
+          <t>Enhanced power graph, power graph, nilpotent groups, forbidden subgraphs.. MSC(2020): 05C25. References 1. G. Aalipour, S. Akbari, P. J. Cameron, R. Nikandish, and F. Shaveisi. On the structure of the power graph and the enhanced power graph of a group. Electron. J. Combin. 24 (3) (2017)16-18. 2. S.Biswas,P.J.Cameron,A.Das,andH.K.Dey.Ondifferenceofenhancedpowergraphand power graph of a finite group,(2022) arXiv:2206.12422. ∗ JitenderKumar. Emailaddress: jitenderarora09@gmail.com 468</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Shifted Vieta-Lucas polynomials, Caputo derivative,</t>
+          <t>Shifted Vieta-Lucas polynomials, Caputo derivative, Fractional-order Ricatti differential equations, Operational matices. MSC(2020): 65L60, 65L05, 33C45. ∗ Speaker. Emailaddress: zabihi@kashanu.ac.ir 470</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Shifted Legendre polynomials, Legendre wavelets, Water</t>
+          <t>Shifted Legendre polynomials, Legendre wavelets, Water pollution, Pollution of system of lakes.. MSC(2020): 65L05, 33C45. ∗ Speaker. Emailaddress: zabihi@kashanu.ac.ir 472</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gyrogroup, Cayley graph, Algorithm.</t>
+          <t>Gyrogroup, Cayley graph, Algorithm. MSC(2020): 20N05, 05C40, 05C85. References 1. L.Bussaban,A.Kaewkhao,S.Suantai,Cayleygraphsofgyrogroups,QuasigroupsandRelated Systems,27(2019)25-32. 2. R. Maungchang, P. Khachorncharoenkul, K. Prathom,T. Suksumran, On transitivity and connectedness of Cayley graphs of gyrogroups,Heliyon,7(2021)e07049. ∗ Speaker. Emailaddress: neda.moradi@grade.kashanu.ac.ir 474</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Non-local ring, genus and crosscap of a graph, graph</t>
+          <t>Non-local ring, genus and crosscap of a graph, graph classes. MSC(2020): 05C25. References 1. M. Saha, A. Das, E. Y. C¸elikel, and C. Abdio˘glu, Prime ideal sum graph of a commutative ring,J.AlgebraAppl.22(2023)no.6,2350121. 2. Z.S.Pucanovi´candZ.Z.Petrovi´c,Toroidalityofintersectiongraphsofidealsofcommutative rings,GraphsCombin.30(2014)no.3,707–716. 3. Z. S. Pucanovi´c, M. Radovanovi´c, and A. L. Eri´c, On the genus of the intersection graph of ideals of a commutative ring,J.AlgebraAppl.13(2014)no.5,1350155. 4. V.Ramanathan,On projective intersection graph of ideals of commutative rings,J.Algebra Appl.20(2021)no.2,2150017. ∗ Speaker. Emailaddress: maithilpraveen@gmail.com 477</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Graph, Eigenvalues, Spectrum.</t>
+          <t>Graph, Eigenvalues, Spectrum. MSC(2020): 18A32, 18F20, 05C65 . References 1. Y. Hou and W.-C. Shiu, The spectrum of the edge corona of two graphs, Electronic Journal ofLinearAlgebra,20(2010),586–594. 2. M. Javarsineh and G.H. Fath-Tabar, The Main Eigenvalues of the Undirected Power Graph of a Group,JournalofAlgebraicStructuresandTheirApplications,4(1)(2017)19-32. 3. I.Gopalapillai,Thespectrumofneighborhoodcoronaofgraphs,KragujevacJ.Math,35(2011) 493–500. ∗ Speaker. Emailaddress: khani@shaiau.ac.ir 479</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Class preserving automorphism group, central</t>
+          <t>Class preserving automorphism group, central automorphism group, normal automorphism group, generalized dihedral group. MSC(2020): 20D99, 20F99. References 1. V. Bardakov, A. Vesnin and M.K. Yadav, Class preserving automorphisms of unitian- gular groups, International Journal of Algebra and Computation, 22 (3) (2012) 1250023, https://doi.org/10.1142/S02181967125002. 2. The GAP Team, Group, GAP - Groups, Algorithms, and Programming, 2012, http://www.gap-system.org. 3. M.K.Yadav,Classpreservingautomorphismsoffinitep-groups,JournaloftheLondonMath- ematicalSociety,Ser.2,75(3)(2007)755–772,https://doi.org/10.1112/jlms/jdm025. 4. M.K. Yadav, Class preserving automorphisms of finite p-groups II, Israel Journal of Mathe- matics,209(2015)355–396,10.1007/s11856-015-1222-4. ∗ Speaker. Emailaddress: momoeysfn@gmail.com 481</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable..</t>
+          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary: 16W20; Secondary: 13C60.. References 1. F.W. Anderson, K.R. Fuller, Rings and categories of modules, (Vol. 13) Springer Science &amp; BusinessMedia,2012. 2. B.Amini,M.ErshadandH.Sharif,Coretractable modules,JournaloftheAustralianMathe- maticalSociety,86(3)(2009)289-304. 3. S.Asgari,A.HaghanyandY.Tolooei,T-semisimplemodulesandT-semisimplerings,Com- municationsinAlgebra,41(5)(2013)1882-1902. 4. P. Neishabouri, Y. Tolooei, S. Bagheri, On modules in which every finitely generated sub- module is a kernel of an endomorphism,CommunicationsinAlgebra,51(2)(2023)841-858. 5. A.A.Tuganbaev,Ringsclosetoregular,(Vol.545)SpringerScience&amp;BusinessMedia,2013. 6. A. Ghorbani, Co-epi-retractable modules and co-pri rings, Communications in Algebra, 38 (10)(2010)3589-3596. 7. R.Wisbauer,Foundations of module and ring theory,Routledge,2018. ∗Speaker. Emailaddress: pegahneishabori96@gmail.com 483</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Class preserving automorphism group, central</t>
+          <t>Class preserving automorphism group, central automorphism group, normal automorphism group, generalized dicyclic group. MSC(2020): 20D99, 20F99. References 1. V. Bardakov, A. Vesnin and M.K. Yadav, Class preserving automorphisms of unitian- gular groups, International Journal of Algebra and Computation, 22 (3) (2012) 1250023, https://doi.org/10.1142/S02181967125002. 2. TheGAP Team, Group, GAP -Groups, Algorithms, and Programming,Version4.5.5,2012, http://www.gap-system.org. 3. M.K. Yadav, Class preserving automorphisms of finite p-groups, Journal of the London Mathematical Society, Ser. 2, 75 (3) (2007) 755–772; available at https://doi.org/10.1112/jlms/jdm025. 4. M.K.Yadav,Class preserving automorphisms of finite p-groups II,Israel Journal of Mathe- matics,209(2015)355–396,10.1007/s11856-015-1222-4. ∗ Speaker. Emailaddress: bardia.jahangiri@yahoo.com 485</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Neural Networks, Systems Biology, Modules of Genes.</t>
+          <t>Neural Networks, Systems Biology, Modules of Genes. MSC(2020): 62P10, 68T07, 92C42. ∗ Speaker. Emailaddress: mahdevar@kashanu.ac.ir 487</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable..</t>
+          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary 16D10; secondary 16D40. . References 1. F.W. Anderson, K.R.Fuller, Rings and categories of modules, (Vol. 13) Springer Science &amp; BusinessMedia,2012. 2. B.Amini,M.ErshadandH.Sharif,Coretractable modules,JournaloftheAustralianMathe- maticalSociety,86(3)(2009)289-304. 3. S.Asgari,A.Haghany,Y.Tolooei,T-semisimple modules and T-semisimple rings. Commu- nications in Algebra,41(5)(2013)1882-1902. 4. P.Neishabouri,Y.Tolooei,S.Bagheri,Onmodulesinwhicheveryfinitelygeneratedsubmod- ule is a kernel of an endomorphism,CommunicationsinAlgebra,51(2)(2023)841-858. 5. A. Ghorbani, Co-epi-retractable modules and co-pri rings, Communications in Algebra, 38 (10)(2010)3589-3596. ∗Speaker. Emailaddress: Y.toloei@razi.ac.ir 489</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>lexicographic product, connectivity, super connectivity.</t>
+          <t>lexicographic product, connectivity, super connectivity. MSC(2020): 05C40. ∗ Speaker. Emailaddress: zeinabghasemi39@gmail.com 491</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">

--- a/conference_articles.xlsx
+++ b/conference_articles.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>strong dominating set, Hajo´s sum, vertex-sum, operation, domatic.. MSC(2020): 05C99. 1. Introduction A dominating set of a graph G = (V,E) is a subset D of V such that every vertexinV \D isadjacenttoatleastonememberofD. Theminimumcardinality ofalldominatingsetsofGiscalledthedominationnumberofGandisdenotedby γ(G). This parameter has been extensively studied in the literature and there are hundreds of papers concerned with domination. We recommend a fundamental book [9] about domination in general. The various different domination concepts are well-studied now, however new concepts are introduced frequently and the interest is growing rapidly. A set D ⊆ V is a strong dominating set of G, if for every vertex x ∈ D = V \ D there is a vertex y ∈ D with xy ∈ E(G) and deg(x) ≤ deg(y). The strongdominationnumber γ (G)isdefinedastheminimumcardinalityofastrong st dominating set. A γ -set of G is a strong dominating set of G of minimum st cardinality γ (G). If D is a strong dominating set in a graph G, then we say st that a vertex u ∈ D is strong dominated by a vertex v ∈ D if uv ∈ E(G), and deg(u)≤deg(v). ∗ Speaker. Emailaddress: alikhani@yazd.ac.ir † Emailaddress:nima.ghanbari@uib.no 2</t>
+          <t>strong dominating set, Hajo´s sum, vertex-sum, operation, domatic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finite dimensional algebra, Ring epimorphism, Homological conjectures. MSC(2020): 16G10, 16G60. 1. Introduction Auslander-Reiten Conjecture is already known to be one of the most long- standing homological conjectures in the field of representation theory of finite dimensional algebras. Though it has emerged originally in this context, it is also widely studied in various settings such as commutative rings and (noncommu- tative) Noetherian algebras over commutative noetherian rings. As a matter of fact, at least for finite dimensional algebras, it is known that Auslander-Reiten conjecture has strong links to some other homological conjectures. These include the famous finitistic dimension conjecture, Nakayama conjecture, and vanishing conjecture [4]. On the other hand, there exists a natural generalization of the concept of lo- calization for commutative rings to the setting of arbitrary rings; this is named universallocalizationandwasintroducedin[6]bylocalizingwithrespecttoagiven set of morphisms between finitely generated projective modules. This type of lo- calizationtheoryhasobtainedmanyapplicationsinvariousareasofrepresentation theory of algebras, including tilting theory in particular [1]. This short note tries to discover a connection between universal localizations and the validity of Auslander-Reiten conjecture for a special type of finite dimen- sional algebras. ∗ Speaker. Emailaddress: eshraghi@kashanu.ac.ir 8</t>
+          <t>Finite dimensional algebra, Ring epimorphism, Homological conjectures</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Logic algebra, neutrosophic logic, superhyper logic algebra. MSC(2020): 16Y20, 13A70. 1. Introduction Florentin Smarandache introduced a new concept in neutrosophy branches as neutro-algebra as a generalization of partial algebra. Through a theorem he proved that Neutro-algebra is a generalization of partial algebra, and he gave examples of neutro-algebras that are not partial algebras. He also introduced theneutro-function(andneutro-operation). Recently,Smarandache,introduceda newconceptasageneralizationofhypergraphston-superhypergraph,plithogenic n-super hypergraph {with super-vertices (that are groups of vertices) and hyper- edges{definedonpower-setofpower-set...}thatisthemostgeneralformofgraph as today}, and n-ary hyperalgebra, n-ary neutro hyperalgebra, n-ary anti hyper- algebra respectively, which have several properties and are connected with the real world. Recently in the scope of neutro logical (hyper) algebra, Hamidi, et al. introduced the concept of neutro BCK-subalgebras [1] and single-valued neu- tro hyper BCK-subalgebras [2] as a generalization of BCK-algebras and hyper BCK-subalgebras, respectively and presented the main results in this regard. Also Florentin Smarandache a novel concept as super hyperalgebra with its super hyperoperations and super hyperaxioms, then is introduced some concepts such as super hypertopology and especially the super hyperfunction and neutrosophic super hyperfunction. Recently, Hamidi introduced the concept of super hyper BCK-algebras as a generalization of BCK-algebras and investigated some proper- ties of this novel concept [3]. The main motivation of this study is to extension of logic algebras to superhyper logic algebras based on the superhyper axioms. Indeed, we try to overspread the axiom of clasic algebras to superhyper axiom in ∗ Speaker. s.jahanpanah@pnu.ac.ir 12</t>
+          <t>Logic algebra, neutrosophic logic, superhyper logic algebra</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gro¨bner systems, GES algorithm, GVWDisPGB algorithm, GES-GVW-CGS algorithm, Gaussian elimination. MSC(2020): 13P10, 15A06. 1. Introduction TheconceptofGr¨obnersystems,alongwiththeinitialalgorithmfortheircom- putation, introduced in 1992 by Weispfenning [5], revolutionized the field of para- metric polynomial ideals. Gro¨bner systems find numerous applications in various fields,includingmathematicsandothersciences. Theyhaveprovenvaluableinar- eassuchasalgebraicgeometry,parametriclinearalgebra,robotics,andautomated geometry theorem proving. Throughout this text, we consider R = K[x ,...,x ] 1 n thepolynomialringintermsofx ,...,x overafieldK. LetI =⟨f ,...,f ⟩⊂R 1 n 1 k be a polynomial ideal and ≺ be a monomial ordering on the set of all monomials of R. For any f ∈ R, the leading monomial of f, denoted by LM (f), is the ≺ greatest monomial (w.r.t. ≺) appearing in f and its coefficient is the leading co- efficient of f which denoted by LC (f). The leading term of f w.r.t. ≺ is the ≺ product LT (f) = LC (f)LM (f). The leading monomial ideal of I is defined ≺ ≺ ≺ to be LM (I) = ⟨LM (f) | f ∈ I⟩. A finite subset {g ,...,g } ⊂ I is called ≺ ≺ 1 m a Gr¨obner basis for I w.r.t. ≺ if LM (I) = ⟨LM (g ),...,LM (g )⟩. Gr¨obner ≺ ≺ 1 ≺ m systems can be considered as an extension of Gr¨obner bases for polynomial ideals over fields to polynomial ideals with parametric coefficients. With more details, letusconsiderS =K[a,x]asapolynomialringwithparametriccoefficientswhere a = a ,...,a is a sequence of parameters, x = x ,...,x is a sequence of vari- 1 m 1 n ables. Thus a monomial xα 1 1···xα n n is denoted by xα where α=(α 1 ,...,α n ). Let ∗ Speaker. Emailaddress: m.dehghanidarmian@gmail.com 16</t>
+          <t>Gro¨bner systems, GES algorithm, GVWDisPGB algorithm, GES-GVW-CGS algorithm, Gaussian elimination</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algebra, Break-Even Point (BEP), business Management, Mathematics. MSC(2020): 00Axx, 00A05, 00A06. 1. Algebra in Business Business is as dependent on algebra as any other field. In order to calculate profits and losses, business owners use algebraic operations. A business person willusealgebratodeterminewhetherapieceofequipmentdoesnotloseitsworth if it is in stock Algebra is used in business for a variety of reasons. Generally speaking, business math skills can help people and companies to make better decisions, understand problems more thoroughly, and see the long-term impact of their choices. One specific reason business math is used relates to keeping track of financial transactions [3]. The accurate recording and maintenance of financial records are essential for businesses of all sizes. Businesses use algebra to track income and expenses, prepare financial statements, and make informed decisions about where to allocate their resources [2]. Inaddition,thebusinessownerneedstocalculatethelowestpriceatwhichan item can be sold while still covering expenses. In the finance industry, exchange rates and interest rates are often represented algebraically; therefore, to carry out finances accurately, it is necessary to be familiar with algebraic operations. ∗ Speaker. Emailaddress: sariolghalam@pnu.ac.ir 22</t>
+          <t>Algebra, Break-Even Point (BEP), business Management, Mathematics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shape Graph, general hyperring, heart. MSC(2020): 16Y20, 13A70. 1. Introduction The idea of a graph based on zero–divisors of a commutative ring was intro- duced by Beck, where he was mainly interested in colorings. This idea continued by Anderson based on edges and vertices colorings of any given ring. The graph based on zero-devisors was redefined by Livingston and in paper of Anderson et al. that followed in 1999. Later than the concept of hyperalgebra structures as a generalization of algebra structures and extended all ideas of algebras structures to hyperalgebra structures. In special, the idea of graph based on hyperalgebras, is a new and novel idea that connected the relation between of graphs and hyper- algebras. In this paper, we extend the concept of a type algebra named groups to multigroups and non-associative rings to multirings or super rings. In this regard, we construct multigroups, supergroups, super ring and multirings on every arbi- trary nonempty set with some hyperoperations [2, 3, 4, 5]. The main motivation of this study is to extract zero–divisor graphs from hyperstructures with special conditions. So we construct finite superrings and introduces the concept of zero– divisorelementsinfinitesuperrings. Thisstudyapproachessometypesofgraphs from these super rings. Indeed, we connect the special class of hyperstructures to graphs via structures graphs based on zero–divisors and derivable zero–divisor subgraphs. Now, we added some necessarily topics related to our main ideas with respect to hyperstructures and shape graphs. Let R be a nonempty set and P∗(R) be the family of all nonempty subsets of G. Every function θ : R×R −→ P∗(R), is called a hyperoperation, where i i∈N={1,2,...,n,...}. For all x, y of R, θ (x,y) is called the hyperproduct of x, i y. An algebraic system (R,θ ,θ ,...,θ ) is called a hyperstructure, and a binary 1 2 n ∗ Speaker. m.hamidi@pnu.ac.ir 26</t>
+          <t>Shape Graph, general hyperring, heart</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hilbert C∗-module, derivation, approximate functional equation.. MSC(2020): 39B82, 39B52, 46S10. 1. Introduction ThenotionofaHilbertC∗-moduleinitiatedbyKaplansky[3]asageneraliza- tionofaHilbertspaceinwhichtheinnerproducttakesitsvaluesinaC∗-algebra. Let A be a C∗-algebra and M be a complex linear space that is a left A- module with a compatible scalar multiplication satisfying λ(ax)=(λa)x=a(λx) forallλ∈C,x∈M,a∈A. ThenMiscalledapre-HilbertA-moduleoraninner product A-module, if there exists an A-valued inner product (x,y) (cid:55)→ ⟨x,y⟩ : M×M→A such that, (i)⟨x,x⟩≥0 and the equality holds if and only if x=0, (ii)⟨αx+βy,z⟩=α⟨x,z⟩+β⟨y,z⟩, (iii)⟨ax,y⟩=a⟨x,y⟩, (iv)⟨x,y⟩∗ =⟨y,x⟩, for each x,y,z ∈ M, α,β ∈ C and a ∈ A. M is called a (left) Hilbert A-module, or a Hilbert C∗-module over the C∗-algebra A, if it is complete with respect to the norm ∥x∥=∥⟨x,x⟩∥2 1. Every C∗-algebra A is a Hilbert A-module under the A-valued inner product ⟨a,b⟩=ab∗ (a,b∈A). Every complex Hilbert space is a left Hilbert C-module; cf [2]. Let M and N be Hilbert C∗-modules over a C∗-algebra A. A mapping T : M → N is said to be A-linear, if T(ax+λy) = aT(x)+λT(y) for all x,y ∈ M, a ∈ A and λ ∈ C. A mapping T : M → N is said to be adjointable, if there existsamappingS :N →Msuchthat⟨T(x),y⟩=⟨x,S(y)⟩forallx∈D ⊆M, T y ∈ D ⊆ N. The unique mapping S is denoted by T∗ and is called the adjoint S of T. It is well known that any adjointable mapping T :M→N is A-linear and ∗ Speaker. Emailaddress: ekrami@pnu.ac.ir,khalil.ekrami@gmail.com 30</t>
+          <t>Hilbert C∗-module, derivation, approximate functional equation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary: 16W20; Secondary: 13C60. 1. Introduction Throughoutthis paper, R denotes anassociative ringwith identity, and mod- ules are unitary left R-modules unless stated otherwise. Following [2], an R- module M is said to be retractable whenever Hom (M,N) ̸= 0 for any nonzero R submodule N of M. An R-module M is called coretractable whenever for any proper submodule K of M, there exists a nonzero homomorphism f : M −→ M suchthatf(K)=0,thatmeansthatHom (M/K,M)̸=0(see[1]). Therefore,in R thisstudyweweremotivatedtoinvestigatemoduleM whereHom (M/N,M)̸=0 R foreveryproperfinitelygeneratedsubmoduleN ofM,whichwecallCFRmodule. 2. Co-finite-retractable modules Definition 2.1. Let M be an R-module. We call M is co-finite-retractable (simply CFR) whenever for every proper finitely generated submodule K of M, Hom (M/K,M)̸=0. R In the following, we consider when a direct sum of a family of CFR modules is CFR. Theorem 2.2. Let {N } be a family of CFR modules, and let M := ⊕N . i i∈I i i∈I If K∩N contain in a finitely generated submodule of N for every i∈I and every i i finitely generated submodule K of M, then M is a CFR module. ∗ Speaker. Emailaddress: pegahneishabory96@gmail.com 36</t>
+          <t>Co-finite-retractable, Co-retractable</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ring, unit-clean. MSC(2020): 15A23, 15B33, 16U99. 1. Introduction All our rings are associative rings with identity. U(R) denotes the set of all idempotents of R, J(R) denotes the Jacobson radical and B(R) denotes the set of central idempotents of the ring R. By Z we mean the localization of Z at a (p) prime p. By regular we mean Von Neumann regular. Nicholson [1] defined the notion of an element in a ring R to be clean if it can be expressed as a sum of an idempotent and an invertible element in R. We refer the readers to [2] for a survey of clean rings. Clearly it would be quite natural to ask what happens if for each element a in a ring R, there exists an invertible element u in R such that au is clean? We have visualized unit-clean to be a property such that for each a ∈ R there exists a unit u such that the element au is clean. In the other words an element a in R is defined to be unit-clean if there exists invertible elements u,v in R and an idempotent e in R such that au = e+v. A ring R is unit-clean if and only each of its elements are unit-clean. This definition is independent of the position of the invertibleelementu. Thismeans,ucouldbemultipliedtotheleftorrightofa. It iseasytoobservethatanelementinaringRisunit-cleanifitcanbeexpressedas a sum of a unit-regular element and an invertible element in R. Clearly, every 2- goodringisunit-clean. HowevertheconverseisnottrueasR=F isaunit-clean 2 ring which is not 2-good. ∗ Speaker. Emailaddress: n.pouyan@scu.ac.ir neda.pouyan@gmail.com 39</t>
+          <t>ring, unit-clean</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Projection, Medium nil-∗-clean ring, Strongly ∗-clean ring.. MSC(2020): 16Wl0,16U99. 1. Introduction Throughout, all rings are associative with an identity. An involution of a ring R is an operation ∗ : R → R such that (x+y)∗ = x∗ +y∗, (xy)∗ = y∗x∗ and (x∗)∗ = x for all x,y ∈ R. A ring R with involution ∗ is called a ∗-ring. For general ∗-ring theory, we refer the reader [1]. An element p in a ∗-ring R is called a projation if p = p∗ = p2. A ∗-ring R is called a medium nil-∗-clean ring if every element of R is the sum of difference of a nilpotent and a projection that commute. Such rings are the natural generalization of strongly nil-∗-clean rings and a subclass of weakly nil-∗-clean rings. The main goal of this article is to find a new class of ∗-clean rings and to check their relationship with other ∗-clean rings such as strongly weakly J-∗-clean and weakly nil-∗-clean and strongly π-∗- regular rings. We also investigate about corner subring and homomorphic image andgroupringandpolynominalringofmediurnnil-∗-cleanrings. Inthispaper,it is shown that the full matrix M (R) is not medium nil-∗-clean for any n≥2. We n prove that medium nil-∗-clean rings and abelian weakly nil-∗-clean rings coincide with each other. As usual, U(R) denotes the set of all invertible elements of R, Id(R)thesetofallidempotentsofRandN(R)thesetofallnilpotentsofR,J(R) stands the Jacobson radical of R. 2. Main results Lemma 2.1. Every medium nil-∗-clean ring is abelian. Theorem 2.2. Let R be a ∗-ring. Then, the following are equivalent: ∗ Speaker. Emailaddress: hasanzadeomiid@gmail.com 43</t>
+          <t>Projection, Medium nil-∗-clean ring, Strongly ∗-clean ring</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>element order, finite simple group, prime graph.. MSC(2020): 20D05, 20D99, 20A99. 1. Introduction Given a group G, denote by π (G) the set of orders of all elements in G. It is e clear that the set π (G) is closed and partially ordered by divisibility, hence, it is e uniquely determined by the subset of its maximal elements which is indicated by µ(G). We also denote by π(n) the set of all prime divisors of a positive integer n. For a finite group G, we will write π(G) instead of π(|G|). The notation s (G) is m applied for the number of elements of order m in G, and nse(G)={s (G) | m∈ m π (G)}, the set of numbers of all elements in a group G with the same order. A e group G is called NSE characterization if for every finite group M, the equality nse(G)=nse(M) implies that G∼ =M. Uptonow,theNSEcharacterizationofmanynon-Abelianfinitesimplegroups areinvestigated,forinstance,thereferences’[1,2,3,5,6]introducesomeofthese groups. Inwhatfollowswewillconsiderthefinitenon-AbeliansimplegroupA isNSE 9 characterization. Main Theorem The non-Abelian finite simple group A is characterizable by 9 NSE. We conclude the introduction with some further notation and definitions to be used in the rest of this article. To every finite group G we associate a graph ∗ Speaker. Emailaddress: s-rahbariyan@araku.ac.ir 47</t>
+          <t>element order, finite simple group, prime graph</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orthogonality, non-Archimedean C∗-algebra, approximate functional equations, stability. MSC(2020): 39B82, 39B52, 47H10. 1. Introduction In 1897, Hensel [3] introduced a normed space which does not have the Archimedean property. By a non-Archimedean field we mean a field K equipped with a function (valuation) |·| from K into [0,∞) such that |r|=0 if and only if r = 0, |rs| = |r||s|, and satisfies a stronger condition than the triangle inequality |r+s| ≤ max{|r|,|s|} for all r,s ∈ K. Clearly |1| = |−1| = 1 and |n| ≤ 1 for all n ∈ N. A trivial example of a non-Archimedean valuation is the function |·| taking everything except for 0 into 1 and |0|=0. LetX beavectorspaceoverascalarfieldKwithanon-Archimedeanvaluation |·|. A function ∥·∥ : X → [0,∞) is a non-Archimedean norm, if it satisfies the following conditions: (i)∥x∥ = 0 if and only if x = 0, (ii)∥rx∥ = |r|∥x∥ (r ∈ K,x ∈ X), (iii) the strong triangle inequality (ultrametric); namely, ∥x+y∥ ≤ max{∥x∥,∥y∥}. Then (X,∥·∥) is called a non-Archimedean space. Due to the fact that ∥x −x ∥ ≤ max{∥x −x ∥ : m ≤ j ≤ n−1} (n &gt; m) a sequence n m j+1 j {x }isCauchyifandonlyif{x −x }convergestozeroinanon-Archimedean n n+1 n space. By a non-Archimedean Banach space we mean one in which every Cauchy sequence is convergent. A non-Archimedean Banach algebra A is a complete non- Archimedean algebra which satisfies ∥ab∥ ≤ ∥a∥∥b∥ for all a,b ∈ A. If A is a non-Archimedean Banach algebra, then an involution on A is a mapping a (cid:55)→ a∗ fromAintoAwhichsatisfies(i)(λa+b)∗ =λ¯a∗+b∗,(ii)(ab)∗ =b∗a∗,(iii)a∗∗ =a, for all a,b∈A and λ∈C. If, in addition, ∥a∗a∥=∥a∥2 for all a∈A, then A is a non-Archimedean C*-algebra. ∗ Speaker. Emailaddress: ekrami@pnu.ac.ir,khalil.ekrami@gmail.com 51</t>
+          <t>Orthogonality, non-Archimedean C∗-algebra, approximate functional equations, stability</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosbach state, bounded hyper equality algebra, equality algebra. MSC(2020): 03G25, 06D35, 08A35. 1. Introduction The concept of hyper equality algebras is introduced and studied in [1] and authors provided many basic properties of this class of hyper algebras. Some propertiesofthesealgebrasandtheirrelationsbetweenotherhyperstructuresare given in [3] and hyper ideals on bounded hyper equality algebras are introduced in [4]. States play an important role in studying of logical structures. States on equality algebras are defined and studied by Ciungu in [2]. Some more results related to states on equality algebras are studied in [5]. Let H be a nonempty set and◦beafunctionfromH×H tothenonemptypowersetofH,P(H). Then◦is said to be a hyper operation on H. A hyper equality algebra H=⟨H;∼,∧,1⟩ is a nonempty set H endowed with a binary operation ∧, a binary hyper operation ∼ andatopelement1suchthat,forallx,y,z ∈H,thefollowingaxiomsarefulfilled: (HE1) ⟨H,∧,1⟩ is a meet-semilattice with top element 1; (HE2) x ∼ y ≪ y ∼ x; (HE3) 1 ∈ x ∼ x; (HE4) x ∈ 1 ∼ x; (HE5) x ≤ y ≤ z implies x ∼ z ≪ y ∼ z and x ∼ z ≪ x ∼ y; (HE6) x ∼ y ≪ (x∧z) ∼ (y ∧z); (HE7) x ∼ y ≪ (x ∼ z) ∼ (y ∼ z); where x ≤ y if and only if x∧y = x; A ≪ B is defined by for all x ∈ A, there exists y ∈ B such that x ≤ y. Define the following two derived operations, the implication and the equivalence operation of the hyper equality algebra ⟨H,∼,∧,1⟩ by x→y =x∼(x∧y) and x↔y =(x→y)∧(y →x). Proposition 1.1. [1, Proposition 2] Let H=⟨H;∼,∧,1⟩ be a hyper equality algebra. Then for all x,y,z ∈ H, A,B,C ⊆ H: (P1) x ≤ y and y ≤ x imply ∗ Speaker. Emailaddress: m a hashemi@pnu.ac.irali1978hashemi@gmail.com 57</t>
+          <t>Bosbach state, bounded hyper equality algebra, equality algebra</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Parainjective, paraprojective, monoid, S-act. MSC(2020): 20M30. 1. Introduction In this article S will denote a monoid and an S-act A (or A) is a unitary S S-act. Over a monoid S an S-act A is called paraprojective (parainjective) if for any epimorphism f : B −→ A (monomorphism f : A −→ B) there exists a monomorphism g : A −→ B (an epimorphism g : B −→ A ). In this paper these classesofS-actshavebeenstudied. Itisshownthatforprojective(injective)S-acts the concepts of parainjectivity and injectivty ( paraprojectivity and projectivity) are equivalent. Recall that an S-act A is called injective if for any S-act B, any subact C of B and any homomorphism f : C −→ A, there exists a homomorphism f¯: B −→ A such that f¯| =f. Also an S-act A is projective if for any S-act B and for every C S-act C, every S-homomorphism f : A −→ C can be lifted with respect to every epimorphism g : B −→ C, i.e., there exists a homomorphism h : A −→ B such thatf =gh(see[3]). Anelementθ ∈Aiscalledazeroelementifθs=θ forevery s ∈ S. Moreover the one element S-act is denoted by Θ = {θ}. For an S-act A, by E(A), we mean the injective envelope of A. We encourage the reader to see [3] for basic results and definitions relating to acts over monoids. 2. Main results Definition 2.1. Over a monoid S an S-act A is called paraprojective if for any epimorphism f :B −→A there exists a monomorphism g :A−→B. Also an ∗ Speaker. Emailaddress: m.rooeintan@yahoo.com 63</t>
+          <t>Parainjective, paraprojective, monoid, S-act</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>General superring, Boolean general superring, (normal)hyperideal, heart of general superring. MSC(2020): 16Y20, 13A70. 1. Introduction Thetheoryofmultigroups,superrings,andmultifieldswasintroducedbyMar- shall as a generalization of groups, rings, and fields in [4].The notions of multi- groups, superrings, multifields, and their corresponding reduced versions were in- troduced by Marshall in [4] and provided a convenient framework to study the reduced theory of quadratic forms and spaces of orderings. A superring is just a ring with multivalued addition and the idea of a superring is very natural. super- rings are considered in spaces of signs, also known as abstract real spectra and objects which arised naturally in the study of constructible sets in real geome- try. In what follows, we introduce the some concepts such need to our work from [1, 2, 3, 5]. LetRbeanon–emptysetandP∗(R)={S |∅̸=S ⊆R}. Everymap + : R×R −→ P∗(R) is called a hyperoperation and for all x and y of R, +(x,y) is called the hyperproduct of x and y. A binary hyperstructure (R,+) is called a (cid:83) hypergroupoidandA+B = a+b.,where∅≠ A,B ⊆R.Recallthatahy- a∈A,b∈B pergroupoid(R,+)iscalledasemihypergroupif∀x,y,z ∈R,(x+y)+z =x+(y+z) and a semihypergroup (R,+) is called a hypergroup if satisfies in the reproduc- tion axiom, i.e. ∀ x ∈ R,x + R = R + x = R. A commutative hypergroup (R,+)( ∀ x,y ∈ R,x + y = y + x) is called a canonical hypergroup, provided that (i) it has a scalar identity 0 ( ∀ x ∈ R,0+x = x+0 = {x}), (ii) every element has a unique inverse, (∀ x ∈ R, there exists a unique −x ∈ G, such that 0 ∈ x+(−x)∩(−x)+x), (iii) x ∈ y+z implies y ∈ x+(−z) and z ∈ −y+x ∗ Speaker. rdaneshpayeh@pnu.ac.ir 67</t>
+          <t>General superring, Boolean general superring, (normal)hyperideal, heart of general superring</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Γ-δ-MV-algebra, ideals, Heyting algebra . MSC(2020): 03B50,03G25,06D35. 1. Introduction We recall some definitions and results which will be needed. Definition 1.1. [1, 2, 5] An MV-algebra is a structure (A, ⊕, *, 0) where ⊕ is a binary operation, *, is a unary operation, and 0 is a constant such that the following axioms are satisfied for any a,b∈A : (MV1) (A, ⊕, 0) is an Abelian monoid, (MV2) (a∗)∗ =a, (MV3) 0∗⊕a=0∗, (MV4) (a∗⊕b)∗⊕b=(b∗⊕a)∗⊕a. Note 1=0∗ and the auxiliary operation ⊙ as follow: x⊙y =(x∗⊕y∗)∗. Theorem 1.2. [5] In an MV-algebra (A,⊕,∗,0) we have: (i) x⊙(y⊙z) = (x⊙y)⊙z, (ii) x⊙y =y⊙x, (iii) x⊙1=x, (iv) x∗∗ =x, (v) x⊙1∗ =1∗, (vi) (x∗⊙y)∗⊙y =(y∗⊙x)∗⊙x, that is (A,⊙,∗,1) is an MV-algebra. Definition 1.3. [1, 5] An ideal of an MV-algebra A is a nonempty subset I of A satisfying the following conditions: (I1) If x∈I , y ∈A and y ≤x, then y ∈I, (I2) If x,y ∈I, then x⊕y ∈I. ∗ Speaker. Emailaddress: frouzesh@bam.ac.ir 72</t>
+          <t>Γ-δ-MV-algebra, ideals, Heyting algebra</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ds, isomorphism, d-Rickart module, virtually d-Rickart module.. MSC(2020): 16D10,16D40, 16D90. 1. Introduction The property of being a d-Rickart (short form for dual Rickart) module and how it is inherited by ds (abbreviation for direct summand) but not by direct sums of modules. It is also shown that d-Rickart modules satisfy the Summand Sum Property (SSP). The concept of relative d-Rickart condition is introduced to characterize a d-Rickart module. The text proves that a ring where each right module is d-Rickart is semisimple artinian, while a ring where every finitely gen- erated free module is d-Rickart is a von Neumann regular ring. It is proved that a ring where every injective right module is d-Rickart is right hereditary, and a consequence is that each injective right module is dual Baer if and only if the ring is right hereditary and right noetherian([4]). Over the past ten years, there has been a growing interest in using isomor- phisms to study modules. A recent paper by Behboodi et al. proposed a new approach to semisimple modules using the concept of virtually (semi)simple mod- uleandrings([1]). Chaturvedietal. ([2])introducediso-retractablemodulesasa extension of retractable modules. The present article aims to build on their work by examining Rickart modules and d-Rickart modules. InSection2,weexplorethedualnotionofvirtuallyRickartmodules,whichwe call virtually d-Rickart modules. We prove that every virtually d-Rickart module satisfiesGSSP,andthatanyvirtuallyd-RickartmodulewithC isd-Rickart. We 2 also provide a condition that ensures a virtually d-Rickart module is d-Rickart. For a uniserial module M, we show that if M ⊕M is virtually d-Rickart so M ∗ Speaker. Emailaddress: s.asgari03@umail.umz.ac.ir 77</t>
+          <t>ds, isomorphism, d-Rickart module, virtually d-Rickart module</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary 16D10; secondary 16D40. 1. Introduction Throughoutthis paper, R denotes anassociative ringwith identity, and mod- ules are unitary left R-modules unless stated otherwise. Following [2], an R- module M is said to be retractable whenever Hom (M,N) ̸= 0 for any nonzero R submodule N of M. Amini and et al. investigate coretractable module, and we also obtain some new results of coretractable module. An R-module M is called coretractable whenever for any proper submodule K of M, there exists a nonzero homomorphism f : M −→ M such that f(K) = 0, that means that Hom (M/K,M) ̸= 0 (see [1]). Recall that, we said an R-module M is co-finite- R retractable(simplyCFR)wheneverforeveryfinitelygeneratedpropersubmodule K of M, Hom (M/K,M) ̸= 0. We show that, every module over a left Artinian R leftH-ringiscoretractable. Also,weshowthateverymodule M hasfinitelength R overacommutativeringRiscoretractable. Itisclear,everycoretractablemodule is CFR. We show that, every CFR module is coretractable if and only if every module is coretractable. ∗ Speaker. Emailaddress: Y.toloei@razi.ac.ir 82</t>
+          <t>Co-finite-retractable, Co-retractable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Krasner, Enumeration, Hyperring. MSC(2020): 16Y99. 1. Introduction HyperringsandhyperfieldswerealsointroducedandstudiedbyKrasner,Vou- giouklis, and Davvaz [3, 2]. Krasner was the first to expand hypercompositional structures by creating structures containing composition and hypercompositions, which he called Krasner Hyperrings[3]. Kinds of Krasner hyperrings and hy- perfields of order 3 was introduced in [5]. Mittas introduced a special type of completelyregularhypergroupcalledthepolysymmetricalhypergroup, whichwas furtherstudiedbyYatrasunderthenameofM-polysymmetricalhypergroup. Mit- tas and Yatras [4] extended the notion of polysymmetrical hyperrings to a special case called M-polysymmetrical hyperrings. In this article, we compute various types of hyperrings, including Krasner and polysymmetrical hyperrings, in small orders and provide a classification based on their Cayley tables. WerecallthedefinitionofM-polysymmetricalhyperring(Mp-hyperring)from [4] as follows: A set R is called an Mp-hyperring if it is equipped with a binary hyperop- eration + : R × R → P∗(R) and an binary operation · : R × R → R, where P∗(R)={Y|∅≠ Y ⊆R}, such that the following conditions hold: (1) (R,+) is an Mp-hypergroup, (2) (R,·) is a semigroup, (3) the multiplication is strongly bilaterally distributive over the addition. ∗ Speaker. Emailaddress: saeed mirvakili@pnu.ac.ir 85</t>
+          <t>Krasner, Enumeration, Hyperring</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hochschild cohomology, Square matrix algebra, Square algebra.. MSC(2020): . 1. Introduction Consideranarbitrarycommutativeringwithaunitelement,denotedasR. Let A and B be two R-algebras with units, M is a left A-module and right B-module ((A−B)-module),N isaleftB-moduleandrightA-module((B−A)-module). We (cid:18) (cid:19) A M also introduce S = as an algebra over R with the following operations: N B (cid:20) (cid:21) (cid:20) (cid:21) (cid:20) (cid:21) a m a m a +a m +m 1 1 + 2 2 = 1 2 1 2 n b n b n +n b +b 1 1 2 2 1 2 1 2 and (cid:20) (cid:21) (cid:20) (cid:21) (cid:20) (cid:21) a m a m a a +m ⊗ n a m +m b 1 1 · 2 2 = 1 2 1 B 2 1 2 1 2 n b n b n a +b n n ⊗ m +b b 1 1 2 2 1 2 1 2 1 A 2 1 2 where a ,a ∈A, b ,b ∈B, m ,m ∈M, n ,n ∈N. 1 2 1 2 1 2 1 2 If M ⊗ N =N ⊗ M =0, then we call S is a square algebra. Furthermore, B A within the context of S if N = 0 then S is called triangular algebra, and this particular algebra has been investigated by Cheung [3, 4]. Basic examples of triangular algebras are upper triangular matrix algebras and nest algebras which derivations on those considered in [5]. ∗ Speaker. Emailaddress: S.N.Salehi.O@pnu.ac.ir 90</t>
+          <t>Hochschild cohomology, Square matrix algebra, Square algebra</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parametric linear algebra, Gauss-Jordan system, Parametric matrices. MSC(2020): 15A03, 13P10. 1. Introduction A matrix is said to be in reduced row echelon form (rref) when it is in row echelon form and its basic columns are vectors of the standard basis (i.e., vectors having one entry equal to 1 and all the other entries equal to 0). When the coefficient matrix of a linear system is in rref, it is straightforward to derive the solutions of the system from the coefficient matrix and the vector of constants. The standard algorithm used to transform a system into an equivalent system in rref is called Gauss-Jordan elimination. In this paper we are interested only in parametric matrices. Many problems in science and engineering can be modelled by parametric matrices, and have to be repeatedly solved for different values of parameters. In this direction, the Gauss-Jordan of a parametric matrix may have a wide range of applications. For example, we can solve the system of linear equations with parametric coefficients. The following example shows that the traditional approach for computing the Gauss-Jordan form of matrices may not be used for such a matrix. Example 1.1. Let  a−1 0 c−2 1  A= 2 0 −1 b−1  a b+c 0 −1 ∗ Speaker. Emailaddress: m.dehghanidarmian@gmail.com 95</t>
+          <t>Parametric linear algebra, Gauss-Jordan system, Parametric matrices</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MV-algebras, Minimal prime ideal, Z◦−ideals . MSC(2020): 06D35, 06B10. 1. Preliminaries In this section, we state the definitions and theorems that we use: Definition 1.1. [2] Algebra A = (A,⊕, *, 0) of type (2,1,0) is called an MV−algebra, if (1)α⊕(β⊕γ)=(α⊕β)⊕γ; (2)α⊕β =β⊕α; (3) α⊕0=α; (4) (α∗)∗ =α; (5) 0∗⊕α=0∗; (6) (α∗⊕β)∗⊕β =(β∗⊕α)∗⊕α for any α,β,γ ∈A On A, the constan 1 and the auxiliary operation ⊙ are defined as follows: 1=0∗ and α⊙β =(α∗⊕β∗)∗, for all α,β ∈A. Also, ≤ is a partial order on A α≤β ⇔α∗⊕β =1,∀α,β ∈A and it is called the natural order on A. If ≤ is an linearly ordered relative on A, then A is called an MV−chain. ∗ Speaker. Emailaddress: bedrood.m@gmail.com 101</t>
+          <t>MV-algebras, Minimal prime ideal, Z◦−ideals</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Filippov algebra, nilpotent n-Lie algebra . MSC(2020): 117B05, 17B30. 1. Introduction The concept of n-Lie (Filippov) algebras introduced by Filippov [4], as an n- ary multilinear and skew-symmetric operation which satisfies the generalized Ja- cobi identity [[x ,...,x ],y ,...,y ]= (cid:80)n [x ,...,[x ,y ,...,y ],...,x ]]. The 1 n 2 n i=1 1 i 2 n n study of n-Lie algebras is important, since it is related to geometry and physics. Theclassificationofn-Liealgebrasrespecttodimensionisafundamentalproblem. There are many papers on the classification of n-Lie algebras. For example, Bai etal. [1]classifiedalln-Liealgebrasofdimensionn+2onthealgebraicallyclosed fields with characteristic zero. In 1986, Kasymov [7] studied some properties of nilpotent and solvable n-Lie algebras. An n-Lie algebra A is called nilpotent if As = 0 for some non-negative integer s, in which Ai+1 is defined inductively as A1 = A and Ai+1 = [Ai,A,...,A]. The n-Lie algebra A is nilpotent of class c provided that Ac+1 = 0 and Ac ̸= 0. The nilpotent n-Lie algebras of di- mension n + 3 and nilpotent n-Lie algebras of class two and dimension n + 3, n+4, n+5 and n+6 classified in [3, 2, 5, 6]. The center of A is defined by Z(A)={x∈A:[x,A,...,A]=0}. 2. Main results Inthissection,weclassify(n+4)-dimensionalnilpotentn-Liealgebrasofclass 3 and 4 with 4-dimensional derived subalgebra. We know the (n+3)-dimensional non-abeliannilpotentn-Liealgebrasforn&gt;2overanarbitraryfieldareH(n,1)⊕ F(2), A ⊕ F(1), A 1 ≤ i ≤ 5. Let A be a (n + 4)-dimensional n,n+2,1 n,n+3,i nilpotent n-Lie algebra with the derived subalgebra of dimension four with basis ∗ Speaker. Emailaddress: darabi@esfarayen.ac.ir 106</t>
+          <t>Filippov algebra, nilpotent n-Lie algebra</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gro¨bner bases, Cousin complex, Monomial order . MSC(2020): Primary 13P10; Secondary 13D02. 1. Introduction Oneofthecentralproblemsinalgebraicgeometryistounderstandtheproper- ties of algebraic varieties, which are geometric objects that are defined by polyno- mialequationsoverafieldofcoefficients. Oneimportanttoolinstudyingalgebraic varieties is the theory of Gr¨obner bases, which provides a way to compute alge- braic invariants of an ideal generated by a set of polynomials. A Gr¨obner basis is a special set of generators for an ideal, which has certain properties that make it useful for computation. In particular, Gr¨obner bases provide a way to solve poly- nomialequations,computethedimensionofanalgebraicvariety,andcomputethe intersection of algebraic varieties. Therefore, Gr¨obner bases have become an es- sentialtoolinmanyareasofmathematics,includingalgebraicgeometry,computer algebra, and coding theory. However, computing Gr¨obner bases can be compu- tationally expensive, especially for large ideals or in high dimensions. Therefore, researchershavedevelopedvariousalgorithmsandtechniqueslikeasBuchberger’s Algorithm, F5 Algorithm, Faug`ere’s F4 Algorithm, Janet’s Algorithm, Lazard’s Projection Algorithm to compute Gr¨obner bases efficiently. The reader can refer to[1]and[2]foralgebraicconceptsandreferto[4]and[5]tolearnthecalculations related to obtaining Grubner bases. In this paper, we introduce a new method ∗ Emailaddress: hr bamdad@pnu.ac.ir 112</t>
+          <t>Gro¨bner bases, Cousin complex, Monomial order</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>small submodule, semisimple module, hyperedge, sum-hypergraph.. MSC(2020): 16D10,16D90, 05C65, 05C20. 1. Introduction Overthepastdecade, studieshaveshownthathypergraphsareusefulinsolv- ingreal-lifeproblems. Hypergraphshavebeensuccessfullyappliedinvariousfields such as network modeling, data structures, system modeling for engineering, cel- lular mobile communication systems, image processing, machine learning, data mining, soft sets, social networks, chemistry, and more. AsubmoduleN ofamoduleP issaidtobeessential(large),providedN∩L= 0 implies L=0, where L is a submodule of P. Changing intersection to sum and zerosubmoduletothewholemodule,asubmoduleK ofP issaidtobesuperfluous (small) provided K +L = P where L ≤ P implies L = P. Note that if every submodule of the module P is a large submodule, then P is called a uniform module. An analogue for a uniform module is a hollow module. The module P is called hollow, if every proper submodule is small in P. A hollow module P with a largest submodule (the sum of all proper submodules of P, which must be the radical of P) is a local module. The sum of all simple submodules of a module P is said to be the Socle of P, denoted by Soc(P). If P has no large submodules, then Soc(P) = P. In this case, we say P is semisimple. The radical of P, denoted by Rad(P) is the sum of all small submodules of P, that is equivalent to the intersection of all maximal submodules of P. ∗ Speaker. Emailaddress: hosseinibehrouz011@gmail.com 118</t>
+          <t>small submodule, semisimple module, hyperedge, sum-hypergraph</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UJI ring, 2-UJ ring, involution.. MSC(2020): 16U99,16S99. 1. Introduction Throughout, all rings are associative with an identity. Standardly, U(R) de- notes the set of all units of R, Inv(R) is the set of all involutions of R, Id(R) is the set of all idempotents of R, J(R) stands for the Jacobson radial of R and Z(R) for the center of R [2]. A ring R is called clean if R = U(R) + Id(R). A ring R is called weakly J-clean, provided that R = J(R) ± Id(R). A ring R is said to be JU, provided the equality U(R) = 1+J(R) holds, and weakly JU or, abbteviated WJU, provided the equality U(R) = ±1+J(R) holds [3]. The objective of this article is to generalize these WJU rings. We call them UJI rings. A ring R is called UJI if, for each u ∈ U(R), there are j ∈ J(R) and i ∈ Inv(R) ∩ Z(R) suchthat u = j + i. This is obviously tantamount to U(R) = J(R)+Inv(R)∩Z(R) = (Inv(R)∩Z(R))(1+J(R)). In this paper we obtain some properties of UJI rings. 2. Main results Example 2.1. Any JU and WJU ring is UJI ring. Lemma 2.2. If R is UJI ring and 2∈J(R), then R is JU ring. Theorem 2.3. Let R be a UJI ring. Then the following hold: (1) 2∈U(R) if and only if 3∈J(R). (2) 3∈U(R) if and only if 2∈J(R). Lemma 2.4. Let R be a commutative UJI ring and 1 ∈ U(R)+U(R), Then 2∈U(R). Lemma 2.5. If R is a UJI clean ring. Then 6∈J(R). R Lemma 2.6. If R is a UJI ring. Then is a UJI ring. J(R) ∗ Speaker. Emailaddress: hasanzadeomiid@gmail.com 123</t>
+          <t>UJI ring, 2-UJ ring, involution</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prime submodule, Classical prime submodule, Weakly prime submodule, Weakly prime ideal, Duo ring. MSC(2020): 16D10, 16D80, 16Dxx. 1. Introduction Throughout this article all rings are associative with identity element and all modules are unital. Several authors have extended the notion of prime ideals to modules, see, for example [3], [7]. Weakly prime submodules of modules over commutative rings were introduced by Ebrahimi Atani and Farzalipour in [4]. A proper submodule N ofM iscalledaweaklyprimesubmoduleifwhenever0̸=am∈N,wherea∈R andm∈M,theneitherm∈N oraM ⊆N. LetM bealeftR-module. Aproper submodule P of M is called prime if rRm⊆P, for some r ∈R and m∈M then m ∈ P or rM ⊆ P. Equivalently, P is prime submodule if for any ideal A of R and any submodule N of M such that AN ⊆ P, either AM ⊆ P or N ⊆ P. It is clear that each prime submodule is weakly prime. For every submodule N and K of an R-module M, we denote by (N : K) the subset {a ∈ R | aK ⊆ N} of R R, which is an ideal of R. The annihilator of K which is denoted by Ann (K) R is (0 : K). If Ann (K) = 0, then K is called a faithful submodule of M. In R R particular, if Ann (M)=0, then M is called a faithful module. We know that R R is a right (left) duo ring if every right (left) ideal of R is an ideal. It is easy to see that if R is a left duo ring, then xR⊆Rx, for each x∈R. In this paper we introduce the concept of classical prime submodule. This conceptisthegeneralizationofthenotionofweaklyprimesubmodulestomodules ∗ Speaker. Emailaddress: marziyejamali@gmail.com 126</t>
+          <t>Prime submodule, Classical prime submodule, Weakly prime submodule, Weakly prime ideal, Duo ring</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S˜ostak L-fuzzy topological spaces,L-uniform spaces, L- Hutton uniform spaces . MSC(2020): 54A40,54E15. 1. Introduction Fuzzy topology is a type of topology defined on a lattice. The theory of fuzzy topology was initiated by Chang [1], and many authors have developed a general approach to the study of topological-type structures on fuzzy powersets. H¨ohle[2] andS˜ostak[5]introducedL-fuzzytopologicalspaces,whichgeneralizeChang[0,1]- topological spaces , and analyzed their fixed-basis foundations for L-valued fixed bases . The literature extensively covers the study of uniformity structure on L- valuedspaces,withquasi-uniformitybeingausefultoolforinvestigatingtopology, proximity, closure, and interior operators. Several different approaches exist for L-fuzzy quasi-uniformities in fuzzy sets, such as Hutton’s unification approach[3] based on powersets of the form (LX)LX , Lowen’s [4] and H¨ohle[2] entourage ap- proach based on powersets of the form LX×X . In this paper, we introduce a newdefinitionoffuzzyuniformspacebyintroducingtheconceptofagradationof uniformityonanon-emptysetX.Specifically,wepresentthenotionsofL-uniform spaces, and L-Hutton uniform spaces. We investigate the relationship between ∗ Speaker. Emailaddress: m-yaghoubi@pnu.ac.ir 131</t>
+          <t>S˜ostak L-fuzzy topological spaces,L-uniform spaces, L- Hutton uniform spaces</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>weakly reversible ring, polynomial ring, semicommutative ring. MSC(2020): 13B02,16B99. 1. Introduction In here any ring is associative and has identity. A ring R is named reversible if xy = 0 leads us yx = 0 for all x,y ∈ R. This ring and its generalizations have been discussed in many articles and very useful results have been obtained about them. We study here an extension of reversible ring named weakly reversible ring in which xy = 0 leads us rysxt is nilpotent, for all x,y ∈ R and r,s,t ∈ R. A ring that all its right ideals are ideals, is named right duo. We assert that right duo rings are weakly reversible. A ring R with the feature that xy = 0 leads us xRy = 0, for all its elements x,y, is named semicommutative ring. We know by [3, Lemma 1.4], that reversible rings are semicommutative. We admit an example which tells us that weakly reversible rings are not presently semicommutative. Further, we assert that a ring R is weakly reversible iff R[x] is weakly reversible. Finally, we peruse conditions that the power series ring and skew polynomial ring are weakly reversible ring. 1.1. Some properties of weakly reversible rings. Definition 1.1. Call ring R weakly reversible, if for every its elements x,y, xy =0 leads us rysxt is nilpotent, for all elements r,s,t∈R. Example 1.2. Given (cid:18) Z Z (cid:19) R= 2 2 . 0 Z 2 It is not hard to realize that R is weakly reversible. ∗ Speaker. Emailaddress:masoudiar@gmail.com 136</t>
+          <t>weakly reversible ring, polynomial ring, semicommutative ring</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>polygroup, pair of group, nilpotent pair of polygroup.. MSC(2020): 20N20. 1. Introduction The extension of a nilpotent group has been studied by different authors. For instance In [1] Barzegar and Erfanian introduced the α-nilpitent group. For an automorphisem α of a group G and x,y ∈ G, the α-commutator of x,y is c(x,y) = xyx−1y−α. For N ◁ G the pair (G,N) is called a pair of groups. α Pair of groups has some applications in group theory, for instance Hassanzadeh [3] introduced nilpotency of pair of groups. In 1934, Marty [4] introduced the concept of polygroups as a special hyper- group. Application of hyperstructures have been studied in many branches of mathematics. Now in this paper, we study on polygroup analogue of α-nilpotent pair and attain some of their properties. Also, we get a relation between α-nilpotent pair of polygroups and α-nilpotent pair of groups. A hyperoperation ◦ is a function from R×R into the family of non-empty subsets of R. A hypergroupoid (R,◦) is a non-empty set R with a hyperoperation (cid:83) ◦. If A and B are non-empty subsets of R, then A◦B = a◦b. We use a∈A,b∈B x◦A instead of {x}◦A and A◦x for A◦{x}. Also, (R,◦) is a semihypergroup if for any r,s,t∈R we have r◦(s◦t)=(r◦s)◦t. A semihypergroup (R,◦) is said a hypergroup if for any x∈R we have x◦R=R◦x=R . The condition that for ∗ Speaker. Emailaddress: f.mohammadzadeh@pnu.ac.ir 141</t>
+          <t>polygroup, pair of group, nilpotent pair of polygroup</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nonlinear partial differential equations, evolution equations, symmetries.. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Outline the problem progresses in recent years in the study and analysis of nPDEshavemadesignificantcontributionstotheunderstandingofmanyphysical system. Modelingofphysicalsystemsoftenleadstononlinearevolutionequations of the general from u =k[u], where k[u] is a locally defiv function (or a nonlinear t operator in general) of the function u and its x-derivatives. wellknownevolutionequationsdescribingphysicalphenomenacouldfoundin several domains of applied sciences, we restrict the pool of equations to classical nPDEs, such like the korteweg de vries equation and its varteties, the cylindrical kdv and the generalized kdv modeling the propagation of weakly nonlinear waves isdispersivemedia. Otherwiseawellknownvarietyofthekdvisknownforalong time, the so-called modified kdv equation, describing nonlinear a coustic waves in anharmonic lattices. Here we concontrate our intensions to a less studied unnamed variety of the mkdv equation, which differs from the mkdv equation by a first local-derivative ∗ Speaker. Emailaddress: raziemirzavand@gmail.com 146</t>
+          <t>Nonlinear partial differential equations, evolution equations, symmetries</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>colocalization, generalized local homology modules, representable modules. MSC(2020): 13D45, 13E99. 1. Introduction We first recall some definitions that we will use. A Hausdorf linearly topolo- gized R-module M is said to be linearly compact if F is a family of closed cosets (i.e., cosets of closed submodules) in M which has the finite intersection property, then the cosets in F have a non-empty intersection. A Hausdorf linearly topologized R-module M is called semi-discrete if every submodule of M is closed. Thus, a discrete R-module is semi-discrete. It is clear that artinian R-modules are linearly compact with the discrete topology. So the class of semi-discrete linearly compact modules contains all artinian modules. Moreover, if (R,m) is a complete ring, then finitely generated R-modules are also linearly compact and discrete. Let I be an ideal of the ring R and M,N R-modules. The i-th generalized local homology module HI(M,N) with respect to I is defined by i HI(M,N)=limTor (M/ItM,N). i i t In the special case M =R, HI(R,N)=HI(N) is the i-th local homology module i i HI(N) of N with respect to I. i The cosupport of an R-module M, written Cosupp (M), is the set of primes R psuchthatthereexistsacocyclichomomorphicimageLofM withAnn (L)⊆p. R Note that a module is cocyclic if it is a submodule of E(R/m) for some maximal ideal m ∈ R. A prime ideal p is called coassociated to a non-zero R-module M if there is a cocyclic homomorphic image L of M with p = Ann L. The set of R ∗ Speaker. Emailaddress:m-hatamkhani@araku.ac.ir 152</t>
+          <t>colocalization, generalized local homology modules, representable modules</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mKdV equation, Neother symmetries, direct method, conservation law. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Noether’ssecondlawstatesthatthereisaone-to-onecorrespondencebetween symmetry groups and conservation laws. The difference between these types of symmetries and geometric symmetries is that, in addition to depending on in- dependent and dependent variables, the derivatives of dependent variables also appear in them. It is important to mention that each single-parameter group is a variational problem. Whether it is derived from geometric symmetries or ob- tained from Neother symmetries, it can lead to the creation of conservation laws, andconversely,anyconservationlawcanbecorrespondedtoavariationalproblem such as these symmetries. Consider the modified Korteweg-de Vries Equation (1) u +u +u2u +u =0 t x x xxx The Lie algebra g of the this equation is spanned by the three vector fields as follow: (2) v =(x+2t)∂x+3t∂t−u∂u, v =∂t, v =∂x 1 2 3 A one-parameter higher-order local transformation can refer to a Lie-Backlund or Noether transformation that isn’t a one-parameter Lie group of point or contact transformations. LieandBacklunddidnotconsiderhigher-ordertransformations, whereas Noether did in her paper on conservation laws. ∗ Speaker. Emailaddress:m.gandomi.60@gmail.com 157</t>
+          <t>mKdV equation, Neother symmetries, direct method, conservation law</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Q-intuitionistic fuzzy subgroups, norms, conjugate, direct product, normality, homomorphisms.. MSC(2020): 08A72, 20N25, 20K30. 1. Introduction The concept of fuzzy sets was initiated by Zadeh in 1965. Since then it has become a vigorous area of research in engineering, medical science, social science, graph theory etc. Yuan and Lee [6] defined the fuzzy subgroup and fuzzy subring based on the theory of falling shadows. Solairaju and Nagarajan introduced the notion of Q- fuzzy groups in 2009. Anthony and Sherwood [1] gave the definition of fuzzy subgroup based on t-norm in 1977. As a generalization of a fuzzy set, the concept of an intuitionistic fuzzy set was introduced by Atanassov [2]. In previous works [3]-[5], by using norms, we investigated some properties of fuzzy algebraic structures. In this study, we introduced a new algebraic structure of Q- intuitionisticfuzzysubgroupsundernorms(T andC)asconjugate,directproduct, normality,order,normalized,characteristic,compositionandgeneralcharacterris- tic and discussed some important properties of them. 2. Preliminaries Thissectioncontainssomebasicdefinitionsandpreliminaryresultswhichwill be needed in the sequal. For more details we refer to [1]-[6]. ∗ Speaker. Emailaddress: Rasuli@pnu.ac.ir 162</t>
+          <t>Q-intuitionistic fuzzy subgroups, norms, conjugate, direct product, normality, homomorphisms</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ring, unit-semi boolean . MSC(2020): 15A23, 15B33, 16U99. 1. Introduction Itisassumedthroughoutthispaper, allringsareassociative, containingiden- tity element 1 (1 ̸= 0). Our phrasing and notation generally agree with [1]. For illustration, U(R) sits for the group of units in R, J(R) for the Jacobson radical inR, Nil(R)forthesetofnilpotentsinR andId(R)forthesetofidempotentsin R. Before presenting our main achievements, we will first present a brief history ofwhatisbestknowninthisfield. Anelementinaringiscalledcleanifitcanbe written as the sum of an idempotent and a unit, and an element is further named strongly clean if such idempotent and unit commute. A ring is (strongly) clean if every its element is (strongly) clean. The notion of a clean ring was instituted by Nicholson in 1977 as an illustration of a ring with idempotents, that can be liftedmoduloanyleft(right)ideal. Inthelasttenyears,manyauthorshavestud- iedclassesofringsdefinedbyreplacing”unit”and/or”idempotent”withdifferent conditionsonringelementsand/orprobablyaddingadditionalrequirementstothe above definition. For example, classes of semi-boolean, uniquely clean, strongly nil-clean rings have all been obtained on this way. Besides, it was defined in [4] the(smallest)classofsemi-booleanringsasthoseringsRforwhicheveryelement isthesumofanelementfromtheJacobsonradicalandanidempotent;theserings were also termed J-clean. This was extended in [2] to the class of rings called ∗ Speaker. Emailaddress: n.pouyan@scu.ac.ir neda.pouyan@gmail.com 168</t>
+          <t>ring, unit-semi boolean</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>polygroup, soft set, Engel polygroup.. MSC(2020): 20N20. 1. Introduction One way for dealing with uncertain problems in engineering, medical science and social science is soft set theory. It was proposed by Molodtsov [4]. Also, it has applications in Rieman integration, probability theory, game theory and etc (see [4]). In1934, Martyintroducedtheconceptofpolygroupsasaspecialhypergroup. In addition, polygroups have been discussed by Corsini , Borzooei , Davvaz and so on (see [1]). Some results of group theory are translated on polygroups such as nilpotent polygroup. Now, in this paper we study on Engel soft polygroup and investigate some properties of it. A hyperoperation ◦ is a mapping from H ×H into the family of non-empty subsets of H. A hypergroupoid (H,◦) is a non-empty set H with a hyperoperation (cid:83) ◦. If A and B are non-empty subsets of H, then A◦B = a◦b. Also, we a∈A,b∈B use x◦A instead of {x}◦A and A◦x for A◦{x}. The structure (H,◦) is called a semihypergroup if a◦(b◦c) = (a◦b)◦c for any a,b,c ∈ H. A semihypergroup (H,◦) is called a hypergroup if for any x∈H, x◦H =H ◦x=H. Definition 1.1. [1]Analgebraicstructure(P,·,e,−1),wheree∈P and−1 is an unitary operation on P, is called polygroup if for any x,y,z ∈P the following conditions hold: ∗ Speaker. mohamadzadeh@pnu.ac.ir 173</t>
+          <t>polygroup, soft set, Engel polygroup</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>capable n-Lie algebra, nilpotent n-Lie algebra, Multiplier. MSC(2020): 117B05, 17B30. 1. Introduction In 1985, Filippov [6] introduced the concept of n-Lie (Filippov) algebra. The center of n-Lie algebra A is defined as Z(A) = {x∈A:[x,A,...,A]=0}. The notion of nilpotent Filippov algebra was defined by Kasymov [7]. A Filippov algebra A is nilpotent if As = 0, where s is a non-negative integer number. Note that Ai is defined as inducted by A1 = A,Ai+1 = [Ai,A,...,A]. The study of n-Lie algebras is important since it has applications in geometry and physics. Beside other problems about n-Lie algebras, classification of n-Lie algebras is a centralprobleminthisarea. ThealgebraicclassificationofFilippovalgebraisalso discussed in the literature. For example, see [6, 1, 3]. LetAbeann-LiealgebraoverafieldΛandA∼ =F/Rforafreen-Liealgebra. ThentheSchurmultiplierM(A)ofAisisomorphicto R∩F2 . Then-Liealgebra [R,F,...,F] Aiscalledacapablewhenthereexistsann-LiealgebraB suchthatA=B/Z(B). The abelian n-Lie algebra F(d) is capable if and only if d ≥ n. Also, the n- Lie algebra H(n,m)⊕F(k) is capable if and only if m = 1. (See [5] for more informations). The following lemma plays a key role in the study of the capability of n-Lie algebras. Lemma1.1. Then-LiealgebraAiscapableifandonlyifdimM(A)&gt;dimM(A)− I dim(A2∩I) for each central ideal I of A. ∗ Speaker. Emailaddress: darabi@esfarayen.ac.ir 179</t>
+          <t>capable n-Lie algebra, nilpotent n-Lie algebra, Multiplier</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>weakly prime ideal, weakly semiprime ideal, duo ring. MSC(2020): 16N60, 16D25. 1. Introduction Throughout this article all rings are associative with identity element. The structure of weakly prime ideals over non-commutative rings has been studied by Y. Hirano, E. Poon and H. Tsutsui in [4]. We studied some properties of weakly prime ideals and then we define structure of weakly semiprime. Let P be a proper ideal of commutative ring R with identity 1 ̸= 0. D. D. Anderson and E. Smith [1] called P weakly prime if a,b ∈ R and 0 ̸= ab ∈ P impliesa∈P orb∈P. Following[3],anidealI inRisweaklysemiprimeifa∈R and 0̸=a2 ∈I implies a∈I. Nowwedefinetheconceptsthatwewillneed. AnproperidealI ofRiscalled semiprime if J2 ⊆ I implies J ⊆ I for any ideals J of R. A ring R is called semiprimeif0issemiprimeideal. GivenaringR, theprimeradicalandthesetof √ all nilpotent elements are denoted by 0 and Nil(R), respectively. The Jacobson radical of a ring R denoted by J(R) is the intersection of all maximal right (or left) ideals of R. We denoted M (R), the set of n×n matrices over a ring R. n Under addition and multiplication of matrices, M (R) forms a non-commutative n ring with identity. M (P) is an ideal (resp prime ideal) in M (R) if and only if P n n is an ideal (resp. prime ideal) in R. A ring is called reduced if it has no nonzero nilpotent elements; and a ring R is called right (or left) duo ring if every right (or left) ideal of R is a two-sided ideal. ∗ Speaker. Emailaddress: marziyejamali@gmail.com 185</t>
+          <t>weakly prime ideal, weakly semiprime ideal, duo ring</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>closed submodule, semiprime submodule, prime submodule. MSC(2020): 18A15, 13A02. 1. Introduction Throughout this paper R is a commutative ring with identity and M is an R-module. (α,β)-closed ideals in a commutative ring with identity have been introduced and studied in [1]. ApropersubmoduleP ofM iscalledprimeifrm∈P impliesthatr ∈(P :M) or m∈P. Also, P is called semiprime if rtm∈P implies that rm∈P. For more results on prime and semiprime submodules, see [2], [3]. Let α,β be positive integers with α&gt;β. We define a proper submodule K of M to be (α,β)-closed if rαm∈K implies that rβm∈K for r ∈R and m∈M. On the other hand, K is called (α,β)-closed submodule of M if IαL⊆K implies that IβL⊆K where I is an ideal of R and K is a submodule of M. Clearly, every (α,1)-closed submodule is semiprime. In this paper, we characterize (α,β)-closed submodules, which are a general- ization of (α,β)-closed ideals. 2. Some results ItisclearbydefinitionthatifK isan(α,β)-closedsubmoduleofanR-module M, then (K : M) is an (α,β)-closed ideal of R. But the converse is not true in R general. ConsiderZ-moduleZ×Z. Letα&gt;2. ThenthesubmoduleK =(7mZ,0) of Z×Z is not (α,β)-closed for every β &lt;α. But (K :Z Z×Z)=0 is prime and so an (α,β)-closed ideal of Z. ∗ Speaker. Emailaddress: Rezvan.Varmazyar@iau.ac.ir 190</t>
+          <t>closed submodule, semiprime submodule, prime submodule</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BCK-algebra,(strong)d-algebra,constructivefunctions. MSC(2020): 06F35, 20N02. 1. Introduction In 1966, Y. Imai and K. Ise´ki [3, 4] introduced BCK and BCI-algebras as algebras connected with some logics, where the class of BCK-algebras is a proper subclass of BCI-algebras. In 1999, J. Neggers and H. S. Kim [5], as generaliza- tion of BCK-algebras, introduced the notion of d-algebras and studied among relations between d-algebras and oriented digraphs. P. J. Allen [1] constructed a multitude of d-algebras related to constructive function triples on R and on in- tegral domains. In 2010, J. S. Han et al. [2] defined several special varieties of d-algebras, such as strong d-algebras, (weakly) selective (pre-) d-algebras. In [6], A. Rezaei et al. introduced a notion of K-nonvanishing map on a field K, and obtained polynomially defined d-algebras, as well as some conditions for these to be strong d-algebras. Moreover, they investigated some relations between polyno- mially defined d-algebras with left-zero semigroups and β-algebras. The present paper is a continuation of [1] and [6], where the property of d- algebras and polynomial defined d-algebras were studied. Here we consider the notion of a triple (ϕ,φ,ψ) called a constructive function triple on R, to construct aclassofstrongd-algebras. Weobtainsomeconditionsforad-algebraonRtobe strong. 2. Preliminaries A d-algebra ([5]) is an algebra (X, ∗, ξ) of type (2,0) satisfying the following conditions: (I) α∗α=ξ, ∗ Speaker. kghadimi@pnu.ac.ir 193</t>
+          <t>BCK-algebra,(strong)d-algebra,constructivefunctions</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Locally Noetherian, Locally Artinian, S-acts, Monoids. MSC(2020): 20M30. 1. Introduction Animportantandinterestingdiscussionofmoduletheoryistostudytheprop- erties of noetherian and artinian modules. A module is called locally noetherian (locallyartinian)ifallitsfinitelygeneratedsubmodulesarenoetherian(artinian). Formonoids,descendingandascendingchainconditionsoncommutativemonoids with zero are discussed in [1]. Then, in the category of S-acts, the concepts of finitely (Rees) cogenerated S-acts are investigated in [3]. In particular, (Rees) noetherian and artinian S-acts are studied in [4]. An S-act is said to be (Rees) artinian (noetherian) if it satisfies descending (ascending) chain condition on its (Rees) congruences. An S-act is artinian if and only if each of its factor acts is finitelycogenerated. Usingtheresultsin[4],inSection2,weintroducethenotions of (Rees) locally artinian (noetherian) S-acts. We say that an S-act is (Rees) lo- cally artinian (noetherian) if every its finitely generated subact is (Rees) artinian (noetherian). Then, we present some general properties of such acts. Moreover, weinvestigatethebehaviorof(Rees)locallynoetherianand(Rees)locallyartinian S-acts under Rees short exact sequences. Throughout the paper, S and A are used to denote a monoid and a right S S-act, respectively. A nonempty subset B of a right S-act A is called a subact S ∗ Speaker. Emailaddress: khosravi@fasau.ac.ir 198</t>
+          <t>Locally Noetherian, Locally Artinian, S-acts, Monoids</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algebra, productivity, business Management, Mathematics. MSC(2020): 00Axx, 00A05, 00A06. 1. Business and Algebra Algebra is used in business for a variety of reasons. Business math skills can help people and companies to make better decisions, understand problems more thoroughly, and see the long-term impact of their choices [6]. One specific reasonbusinessmathisusedrelatestokeepingtrackoffinancialtransactions. The accuraterecordingandmaintenanceoffinancialrecordsareessentialforbusinesses ofallsizes. Businessesusealgebratotrackincomeandexpenses,preparefinancial statements, and make informed decisions about where to allocate their resources [2]. Another reason algebra is used in business is to make calculations and predic- tions. Businesses use mathematical concepts such as probability and statistics to make decisions about pricing, production, and investment. By understanding and using these concepts, businesses can make better decisions that lead to increased profits. Algebra is also used in business to understand and analyze data. Data is collected by businesses for a variety of purposes, such as understanding customer ∗ Speaker. Emailaddress: sariolghalam@pnu.ac.ir 203</t>
+          <t>Algebra, productivity, business Management, Mathematics</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lfuzzy topological spaces, uniformity structure, L- Hutton uniform spaces,. MSC(2020): 54A40,54E15. 1. Introduction Fuzzy topology is a type of topology defined on a lattice. The theory of fuzzy topology was initiated by Chang [1], and many authors have developed a general approach to the study of topological-type structures on fuzzy powersets. H¨ohle[2] andS˜ostak[5]introducedL-fuzzytopologicalspaces,whichgeneralizeChang[0,1]- topological spaces , and analyzed their fixed-basis foundations for L-valued fixed bases . The literature extensively covers the study of uniformity structure on L- valuedspaces,withquasi-uniformitybeingausefultoolforinvestigatingtopology, proximity, closure, and interior operators. Several different approaches exist for L-fuzzy quasi-uniformities in fuzzy sets, such as Hutton’s unification approach[3] based on powersets of the form (LX)LX , Lowen’s [4] and H¨ohle[2] entourage ap- proach based on powersets of the form LX×X . This paper introduces the notions of L-Hutton uniform spaces and L-uniformities, and investigates the relationship betweenL-fuzzytopologicalspacesandL-Huttonuniformspaces. Wedemonstrate that every [0,1]-fuzzy topological space is Hutton [0,1]-quasi-uniformizable. Fi- nally, we establish the relation between Hutton L-uniformities andL-uniformities ∗ Speaker. Emailaddress: m-yaghoubi@pnu.ac.ir 207</t>
+          <t>Lfuzzy topological spaces, uniformity structure, L- Hutton uniform spaces</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mKdV equation, Neother symmetries, direct method, conservation law. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Noether’ssecondlawstatesthatthereisaone-to-onecorrespondencebetween symmetry groups and conservation laws. The difference between these types of symmetries and geometric symmetries is that, in addition to depending on in- dependent and dependent variables, the derivatives of dependent variables also appear in them. It is important to mention that each single-parameter group is a variational problem. Whether it is derived from geometric symmetries or ob- tained from Neother symmetries, it can lead to the creation of conservation laws, andconversely,anyconservationlawcanbecorrespondedtoavariationalproblem such as these symmetries. Consider the modified Korteweg-de Vries Equation (1) u +u +u2u +u =0 t x x xxx The Lie algebra g of the this equation is spanned by the three vector fields as follow: (2) v =(x+2t)∂x+3t∂t−u∂u, v =∂t, v =∂x 1 2 3 A one-parameter higher-order local transformation can refer to a Lie-Backlund or Noether transformation that isn’t a one-parameter Lie group of point or contact transformations. LieandBacklunddidnotconsiderhigher-ordertransformations, whereas Noether did in her paper on conservation laws. ∗ Speaker. Emailaddress:m.gandomi.60@gmail.com 213</t>
+          <t>mKdV equation, Neother symmetries, direct method, conservation law</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>right gr-ring, power series, symmetric ring, self injective. MSC(2020): 16P99, 16D25. 1. Introduction Any ring here is associative and has identity element. Define a ring duo, if its one sided ideals are ideals. Reversible rings have been the subject of many researches so far. These rings R with the feature that xy =0 thus yx=0, for all x,y ∈R. Marks in [5], studied the connection between reversible, symmetric and duorings. CallaringRsymmetric,ifforeveryx,y,z ∈R,xyz =0yieldsyxz =0. The study of reversible rings continued in [4]. In the case that R is reversible, we see in [4] that R[x] is not necessarily reversible. Idempotents of reversible and pseudo-reversible rings was studied in [2]. A pseudo-reversible ring is a ring R in whichforx,y ∈R,ifxy isanonzeroidempotentelementofR,thenxy =yx. The sense of i-reversible ring which was defined in [3], is a ring in which 0̸=xy is an idempotent yields yx is an idempotent. In [3], it was shown that reversible rings are i-reversible, but i-reversible rings are not necessarily reversibles. In continuation of previous researches about reversible ring, in [6], we intro- duced a class of reversible rings called right gr-ring. This ring R with the feature that for every its right ideal I, xy ∈I infer that yx∈I, for all x,y ∈R . In here, we assert that if R is a ring such that R[[x]] is a right gr-ring, then R is also a right gr-ring. Moreover, we study situations which R[[x]] is a right gr-ring. For this aim, it is proved that if R is a von Neumann right gr-ring, then R[[x]] is a symmetric ring. Finally, if R is a von Neumann right gr-ring such that ∗ Speaker. Emailaddress:masoudiar@gmail.com 218</t>
+          <t>right gr-ring, power series, symmetric ring, self injective</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>character graphs, eigenvalue, matching number, cut vertex. MSC(2020): 20E45, 05C25, 05C76. 3. Introduction Consider a finite group G. By the set Irr(G) denotes irreducible characters of the group G and the corresponding its degree set is cd(G) = {ϕ(1) : ϕ ∈ Irr(G)}. Also by the set ρ(G), we mean primes that they divide at least one character degree in cd(G). A vast study has been investigated the algebraic structure of groups through the study of associated graphs. One such graph which is denoted by ∆(G), is called as the character graph of G. Note that this graph is simple, undirected and ρ(G) is its vertex set, where r,s ∈ ρ(G) are adjacent vertices in ∆(G), iff there exists ϕ(1)∈ cd(G) such that it is divisible by rs. Characterizing thegraphsthatcanserveascharactergraphshasbeenatopicofinterestformany researchers, which for more detail, we refer the reader to [1, 2] Perfect matchings, cut vertices and the size of a character graph can have a significant impact on the structure of the underlying group. Here, we focus on the effects of perfect matchings and cut vertices on the character graph of a group. Additionally, we concentrate on the structure of ∆(R×S) where R,S are non-abelian groups. ∗ Speaker. Emailaddress: hosseinzadeh@ausmt.ac.ir 225</t>
+          <t>character graphs, eigenvalue, matching number, cut vertex</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Insurance Fraud, Network analysis, Algorithm, Graph, Random process.. MSC(2020): 05C82, 91B30. 1. Introduction Fraudintheinsuranceindustryisavoluntaryacttoobtainbenefitsandillegal benefits from insurance organizations and companies. In other words, all matters that lead to the loss of functional trust and confidence among the elements of the insuranceindustryareconsideredfraudintheinsuranceindustry. Currently,fraud isoneofthemostimportantrisksthatorganizationsandinsurancecompaniesface. Cheatinginanywayisunpleasantbecausetheorganizationsuffersfinanciallosses asaresult. Fraudintheinsuranceindustryisverydiverseandhappensfrequently anddailyaroundus. Amongthemostobviousexamplesofinsurancefraud,wecan mention the creation of fake accidents to receive financial and physical damages. In general, frauds can be classified based on three important criteria: ”source of creation”,”severityoffraud”and”timeoffraud”. Fraudsaredividedintointernal and external categories according to the source of its creation. Internal fraud is a fraudcommittedbysomeoneinsidetheinsuranceindustry,whichincludeschanges ∗ Speaker. Emailaddress: hamzeh@irc.ac.ir 230</t>
+          <t>Insurance Fraud, Network analysis, Algorithm, Graph, Random process</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>domination number, zero divisor graph, ideal-based zero divisor graph, annihilating ideal graph. MSC(2020): 05C75, 13H10. 1. Introduction AssociatingagraphwitharinggoesbacktopaperofBeck[1]in1988,wherehe introducedtheideaofzerodivisorgraphs. LetRbeacommutativeringwithiden- tity. ThezerodivisorgraphΓ(R)ofaringR,isanundirectedgraphwhosevertices are all of the elements of Z(R)\{0} such that there is an edge between vertices a andbifandonlyifa̸=bandab=0. Redmondgeneralizedthezerodivisorgraph notion by replacing elements whose product is zero with elements whose product lies in some ideal I of R. Let R be a commutative ring with non zero identity and I be an ideal of R. The ideal-based zero divisor graph of R, is an undirected graph, denoted by Γ (R), with vertices {x∈R\I :xy ∈I for some y ∈R\I} I where distinct vertices x and y are adjacent if and only if xy ∈ I. Therefore, if I =0 then γ (Γ(R))=γ(Γ(R)). I Also we call an ideal I of R, an annihilating ideal if there exists a non zero ideal J of R such that IJ =0. Let A(R) be the set of all annihilating ideals of R. The graph with the vertex set A(R)∗ = A(R)\{0} such that two distinct vertices I and J are adjacent if and only if IJ = 0, Is called the annihilating ideal graph AG(R),Whichwasfirstintroducedin[2]. Adominatingsetforagraphisasubset of vertices such that every vertex not in the dominating set is joined to at least one member of it by some edge. The domination number γ(G) is the number of verticesinasmallestdominatingsetforG. Wecalladominatingsetofcardinality γ(G), a γ-set. A total dominating set of a graph G is a set of vertices of G such that every vertex is adjacent to a vertex in it . The total domination number of ∗ Speaker. Emailaddress: sima.kiani@gmail.com 236</t>
+          <t>domination number, zero divisor graph, ideal-based zero divisor graph, annihilating ideal graph</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Social network, community detection, algorithm. MSC(2020): 91D30, 90B18, 05C82. 1. Introduction Social, technological and information systems can often be described in terms ofnetworks.Thenetworkconsistsofasetofseparateelements(nodes)andconnec- tions between elements (links). A graph can be used to explain the network as a mathematical structure.Oneof theimportant issues insome networks isdetection community. In fact, communities are groups of network nodes that are closely related to each other and have little connection with nodes outside the commu- nity. Communities can be used to extract useful information from networks. At thefirsttime,in2004,NewmanandGirvan[2]introducedameasureforquantita- tivelymeasuringthequalityofcommunitydetectionalgorithmscalledmodularity, which is shown by Q. Modularity measure Q defined as compare fraction of edges within the cluster to expected fraction in random graph with identical degree. The modularity measure of a network can be written as: (1) Q= 1 (cid:88) (A − k i k j)δ(C ,C ) 2m i,j 2m i j i,j where A=[A ] is the adjacency matrix, k and k are the degrees of nodes i and i,j i j j respectively, m is the total edge in the network, C and C are the community i j assignments of nodes i and j respectively, and δ(C ,C ) is the Kronecker delta i j function which equals 1 if C =C and 0 otherwise. i j ∗ Speaker. Emailaddress: h.taha64@yahoo.com 239</t>
+          <t>Social network, community detection, algorithm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>clique, entropy. MSC(2020): 05C35, 94A17. 1. Introduction Entropyisacentralconceptininformationtheoryandhasbeenusedtoprove several combinatorial inequalities, as demonstrated in [3] and [4]. In this paper, we leverage entropy to establish a series of inequalities for the number of cliques of varying sizes in a graph. All random variables are assumed to be discrete and finitely supported. Let X be such a variable and denote the support of X by supp(X). The entropy of X is defined by the following formula: (cid:88) H(X)=− Pr(X =x)logPr(X =x), x∈supp(X) where the base of the logarithm is 2. Note that H(X) only depends on the distri- bution of X and not the values taken by X. For a given support, the entropy is maximized for a variable with a uniform distribution over that support, and the maximum value is the logarithm of the size of the support [1, Theorem 2.6.4]. The following theorem, which is called the Shearer’s lemma, is the essential ingredient of the proof of our main result. Some special cases of this lemma have been proved in [3] and the general case can be found in [2]. Note that [k] = {1,...,k}, and when F = {i ,...,i } and i &lt; ··· &lt; i , X denotes the 1 r 1 r F tuple (X ,...,X ). i1 ir Theorem 1.1. Consider k random variables X ,...,X and suppose that F 1 k is a collection of subsets of [k] such that every element of [k] belongs to at least d ∗ Speaker. Emailaddress: ghodrati@sru.ac.ir 245</t>
+          <t>clique, entropy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sombor index; Sombor energy. MSC(2020): 05C07, 05C09, 05C31. 1. Introduction Throughoutthispaperallgraphsallsimple. LetG=(V,E)beasimplegraph with vertex set V = {v ,v ,...,v } and edge set E = E(G), and let |V(G)| = n 1 2 n and|E(G)|=m. Wewritev v ∈E(G)iftheverticesv andv areadjacent. The i j i j degree of a vertex v is d =|N(v)| where N(v) is the open neighborhood of vertex v v. By K and K we mean the compete graph and its complement, respectively. n n The adjacency matrix A = A(G) of a graph G is defined by its entries as a =1ifv v ∈E(G)and0otherwise. Letλ ⩾λ ⩾···⩾λ betheeigenvalues ij i j 1 2 n of the adjacency matrix of G. The energy of G is defined as n (cid:88) E =E(G)= |λ |. i i=1 The concept of energy was first used by Gutman in chemistry to approximate π-electron energy. Extensive research has been done on energy of graphs. Sombor index of a graph is a new topological index that recently has defined by Gutman [2]. The Sombor index of a graph G is (cid:88) (cid:112) SO(G)= d2 +d2, u v uv∈E(G) where d isthe vertexdegree ofv. TherearesomepapersonSombor indexabout v properties of this index, see [5, 6] for instance. Similartotheadjacencymatrix, theSombormatrixofG, denotedbyS(G)= (cid:113) [s ], is defined as s = d2+d2 if v v ∈E(G) and 0 otherwise. We denote the ij ij i j i j ∗ Speaker. Emailaddress: mr oboudi@yahoo.com;mr oboudi@shirazu.ac.ir 248</t>
+          <t>Sombor index; Sombor energy</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fixed point, automorphism, θ-function, dihedral group. MSC(2020): 20F28, 20D60. 1. Introduction Suppose that G is a finite group and Aut(G) is the automorphism group of G. Examining the relationship between the structure of a group and structure of its automorphism group is one of the topics of interest in group theory, which has been examined by many authors from different perspectives. In this regard, the fixed points of automorphisms are one of the interesting topics in this field, which have been the focus of many authors, for example, you can refer to [1] and [2]. In [1], the authors defined the θ function for each divisor d of |G|, as the number of automorphisms whose number of fixed points is equal to d and calculated the valuesofthisfunctionforsomeAbeliangroups. In[2], thetafunctionfordihedral groupoforder2q,whereq isaprimenumber,hasbeeninvestigated. Inthispaper, by calculating θ values of dihedral groups D , the values of θ function will be 2pq calculated for a larger class of dihedral groups. 2. Preliminaries Throughout this paper, G will be a finite group and Aut(G) will be its auto- morphism group. We denote the dihedral group of order 2n by D . 2n ∗ Speaker. Emailaddress: s.a.mousavi@qom.ac.ir 252</t>
+          <t>fixed point, automorphism, θ-function, dihedral group</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>enhanced power graph, power graph, isomorphism.. MSC(2020): 05C12, 91A43, 05C69. 1. Introduction There are many connections between graphs and groups. Generating graphs from semigroups and groups has a long history. The commuting graph, power graph, enhanced power graph, have been introduced to explore the properties of algebraic structures using graph theory. The concept of a power graph was introduced in the context of semigroup theory by Kelarev and Quinn [3]. Let G be a finite group, the undirected power graphP(G)istheundirectedgraphwithvertexsetG,wheretwoverticesa,b∈G are adjacent if and only if a ̸= b and am = b or bm = a for some positive integer →− m. Likewise,thedirectedpowergraph P(G)isthedirectedgraphwithvertexset G, where for two vertices u,v ∈G there is an arc from a to b if and only if a̸=b and b=am for some positive integer m. In this paper we study the same power graphs and enhanced power graphs. Clearly G ∼ = G implies P(G ) ∼ = P(G ). Does the converse hold? In [2], the 1 2 1 2 converse has been considered and it’s is false for finite groups in general. For example, if p is an odd prime and m &gt; 2, besides the elementary abelian group H of order pm, there are non-abelian groups G of order pm and exponent p, so H and Garenon-isomorphicbuthaveisomorphicpowergraphs. Ontheotherhand, it is shown in [2] that if both G and H are abelian then P(G) ∼ = P(H) implies G∼ =H. It is proved that if G is one of the following finite groups: (1) A simple group, (2) A cyclic group, (3) A symmetric group, (4) A dihedral group, ∗ Speaker. Emailaddress: m.mirzargar@email.com 257</t>
+          <t>enhanced power graph, power graph, isomorphism</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unitary Cayley graph, Domination number, Roman domination number. MSC(2020): 05C75, 13H10. 1. Introduction LetRbearingandU(R)bethesetofunitelementsofR. TheunitaryCayley graph of R, denoted G(R), is the graph obtained by setting all the elements of R to be the vertices and defining distinct vertices x and y to be adjacent if and only if x−y ∈U(R). In [1] the authors proved that the unitary Cayley graph of R is a regular graph of degree |U(R)| and If R is isomorphic to product of n rings, then G(R) is isomorphic to tensor product of their unitary Cayley graphs. A set D is called a dominating set if every vertex not in D is adjacent to one or more vertices in D. The minimum cardinality of a dominating set of G is the domination number denoted by γ(G). Roman domination is a variation of domination introduced by ReVelle [3, 4]. TheconceptofRomandominationcanbeformulatedintermsofgraphs. Wecon- sideronlysimplegraphs,namelyG,withvertexsetV(G)andedgesetE(G). The neighborhood of a vertex v ∈ V(G) is the set N(v) = {u : uv ∈ E(G)} and the closed neighborhood is N[v]=N(v)∪{v}. A Roman dominating function (RDF) of a graph G is a function f :V(G)→{0,1,2} such that whenever f(v)=0 there exists a vertex u ∈ N(v) with f(u) = 2. Let (V ,V ,V ) be the ordered partition 0 1 2 of V induced by f, where V = {v ∈ V|f(v) = i} for i = 0,1,2. Note that there i exists a 1−1 correspondence between the functions f :V →{0,1,2} and the or- dered partitions (V ,V ,V ) of V. Thus, we can write f =(V ,V ,V ). Therefore, 0 1 2 0 1 2 a RDF on graph G can be defined as a function f = (V ,V ,V ) satisfying the 0 1 2 condition that V ≺V , where ≺ means that the set V dominates the set V , i.e. 2 0 2 0 (cid:80) V ⊆ N[V ]. The weight of f is f(v). The Roman domination number 0 2 v∈V(G) γ (G) of G is the minimum weight of RDFs of G. In this paper all of the rings R ∗ Speaker. Emailaddress: sima.kiani@gmail.com 261</t>
+          <t>Unitary Cayley graph, Domination number, Roman domination number</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dynamic monopolies, Repetitive Polling Game, majority function . MSC(2020): 05C57, 37E15. 1. Introduction Let G = (V,E) be a simple undirected graph on the vertex set {v ,...,v }. 1 n Consider the repetitive polling game on G with following procedure (see [2]): At round 0, each vertex v is colored by color x0(v) which may be black or white. At each round, each vertex (simultaneously) looks at the current colors of vertices in its closed neighborhood, and adopts the more common color (namely, the one occurring at the majority of its neighbors) as its new color. More precisely, if we denote the closed neighborhood of the vertex v by N[v] and the global state of the graph after round t by Xt = (xt(v ),...,xt(v )) (xt(v) is the color at vertex 1 n v, after round t), then at round t+1 each entry of the vector Xt+1 is computed by the the following rule: If at round t more than half of the elements of N[v] are colored with c, then at round t+1 the vertex v will be c (c∈{white,black} and xt+1(v) = c). If at round r exactly half of the elements of N[v] have white color and other half of it are black, then we say that there is a tie. In this case v is colored at round t+1 by white (xt+1(v) = white). An example for the resulting ∗ Speaker. Emailaddress:leilamusavi.math@gmail.com 264</t>
+          <t>Dynamic monopolies, Repetitive Polling Game, majority function</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LDPC codes, girth, affine permutation matrix.. MSC(2020): 11H71, 11T71, 68P30. 1. Introduction Low-densityparity-check(LDPC)codes[1],asamainclassoferrorcorrecting linear codes, can be specified by their sparse parity-check matrices (PCM’s) and their associated Tanner graphs. Although the minimum-distance of LDPC codes is less than that of the best known linear codes, due to their structures, they are suitableforlow-complexityiterativedecodingmethods,suchasPearl’sbeliefprop- agation(BP)algorithm,adoptedinmanypracticalapplications. Theperformance of LDPC codes of small length may be strongly affected by their cycle properties suchasgirth. Infact,thegirth,i.e. theshortestcyclesintheTannergraph,isone important factor [2, 3, 4, 5, 6] to design LDPC codes with good error-correcting properties. Quasi-cyclic (QC) LDPC codes [6] are the most promising class of structured LDPC codes due to their ease of hardware implementation using simple shift registers and excellent performance over noisy channels when they are decoded by message-passing algorithms. The PCM’s of QC-LDPC codes are comprised of blocks of circulant matrices, classified by the researchers as type-I, type-II and type-III QC-LDPC codes, if each block is a combination of at-most one, two and three circulant permutation matrices (CPMs), respectively. On the other hand, recently,someattentionhavebeenpaidonaclassoflow-densityparity-checkcodes from affine permutation matrices, called (Type-I) APM-LDPC codes, in [2, 3, 4], ∗ Speaker. Emailaddress: zghbaba123@gmail.com 270</t>
+          <t>LDPC codes, girth, affine permutation matrix</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(k,h)-Pell-Lucas sequence, Eigenvalue, Determinant, Spectral norm. MSC(2020): 11B83, 05A15. 1. Introduction Buenoin[1]consideredaparticularrightcirculantmatrixinvolvingFibonacci sequence and obtained the formulae for the Euclidean norm and eigenvalues of thismatrix. Bozkurt[2]computedthespectralnormsofsomematricesconnected integer sequences such as Fibonacci, Lucas, Pell and Perrin numbers. The authos in [3] studied (k,h)-Pell sequence and (k,h)-Pell-Lucas sequence and found a formulae of nth term and sum of the first n terms of these sequences. In thispaperweobtainsomeformulastocomputingtheeigenvaluesanddeterminants of circulant matrices involving these sequences. Then, we give upper and lower bounds for the spectral norm of them and will present numerical example related toeigenvalues, determinantsandEuclideannormsofparticularcirculantmatrices connected(k,h)-Pellsequenceand(k,h)-Pell-Lucassequencefork =1andh=1. The Pell sequence {P } has the recursive relation n P =2P +P , n n−1 n−2 [3], where P = 0,P = 1. Now, we consider a generalization of this sequence [3] 0 1 which is called (k,h)-Pell sequence and is denoted by Γ . This sequence has the n recursive relation (1) Γ =2kΓ +hΓ , n n−1 n−2 ∗ Speaker. Emailaddress: petroudi@pnu.ac.ir 276</t>
+          <t>(k,h)-Pell-Lucas sequence, Eigenvalue, Determinant, Spectral norm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Domination, roman domination, t-restricted pebbling configuration, optimal pebbling number, pebbling number.. MSC(2020): 05C99. 1. Introduction Graph pebbling is a network optimization model for the transportation of resources that are consumed in transit. Electricity, heat, or other energy may dissipateasitmovesfromonelocationtoanother, oiltankersmayuseupsomeof the oil it transports, information may be lost as it travels through its medium, or military troops may be lost while moving through a region. The central problem in this model asks whether discrete pebbles from one set of vertices can be moved to another while pebbles are lost in the process. A pebbling move across an edge ofagraphtakestwopebblesfromoneendpointandplacesonepebbleattheother endpoint; the other pebble is lost in transit as a toll. Let G = (V,E) be a simple graph of order n. A function f : V → N∪{0} is called a configuration of pebbles on the vertices of G and the quantity w(f) = (cid:80) f(u) is called the weight of f which is just the total number of pebbles u∈V assignedtovertices. Apebblingmove(step)fromavertexutooneofitsneighbors v reduces f(u) by two and increases f(v) by one. A pebbling configuration f is said to be solvable, if for every vertex v, there exists a sequence (possibly empty) ofpebblingmovesthatresultsinapebbleonv. Thepebblingnumberπ(G)equals the minimum number k such that every pebbling configuration f with w(f) = k is solvable. ∗ Speaker. Emailaddress: aghaeefatemeh29@gmail.com † Emailaddress: alikhani@yazd.ac.ir 282</t>
+          <t>Domination, roman domination, t-restricted pebbling configuration, optimal pebbling number, pebbling number</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Domination, independent domination, well independent dominated. . MSC(2020): 05C99. 1. Introduction All graphs considered in this paper are finite undirected graphs without loop nor parallel edge. Let G be such a graph. A non-empty set S ⊆V(G) is a domi- nating set if every vertex in V(G)\S is adjacent to at least one vertex in S. The minimum cardinality of all dominating sets of G is called the domination number of G and is denoted by γ(G). For a detailed treatment of domination theory, the readerisreferredto[5]. Themaximumcardinalityofaminimaldominatingsetin G is called the upper domination number of G denoted by Γ(G). The difference between these two parameters is called the domination gap of G and denote it by µ (G) = Γ(G)−γ(G). A graph G with µ (G) = 0 is called a well-dominated d d graph. Domination gap was first introduced by Finbow et al. in [2]. An independent set in a graph G is a set of pairwise non-adjacent vertices. A maximum independent set in G is a largest independent set and its size is called independence number of G and is denoted by α(G). A graph is said to be well- covered if all of its maximal independent sets have the same size. In general, a graph G with independence number α(G) is well-covered if and only if G¯ is ∗ Emailaddress: alikhani@yazd.ac.ir † Speaker. Emailaddress: nemati.nasim60@gmail.com 286</t>
+          <t>Domination, independent domination, well independent dominated</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>generalized Laplacian, 2-degree, neighbourhood Zagreb index, eigenvalue. MSC(2020): 05C09, 05C92, 92E10. 1. Introduction Throughout this paper G is a simple graph with n vertices and m edges. The vertexandtheedgesetsofGaredenotedbyV(G)={v ,··· ,v }andE(G). The 1 n degree of a vertex v, denoted by d (v), is the number of vertices adjacent to v. G The2-degreeofthevertexv ∈V(G),denotedbyS (v ),isdefinedtobethesum i G i of degrees of neighbours of v . For a vertex u ∈ V(G), there are several notation i for representing the ”sum of degrees of the vertices adjacent to u ” in literature - for example, Cao and Yu et al. used the notation t(u) (and called it 2-degree), Abdo et al. used the notation d and Hagos used S(u). However, following [4] 2,u we use the notation S (u) or simply S(u) or S (due to the obvious reason, as G u S stands for sum) for future use. Note that the average-degree (also known as ∗ Speaker. Emailaddress: sharafdini@pgu.ac.ir 290</t>
+          <t>generalized Laplacian, 2-degree, neighbourhood Zagreb index, eigenvalue</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>(k,h)-Pell-Lucas sequence, Consecutive term, Summation formula, Identity. MSC(2020): 11B83, 05A15. 1. Introduction Mathematicianshavebeenfascinatedbywell-knownsequencesbecauseoftheir interesting and exciting applications in the area of numerical analysis, combina- tory theory, matrix theory and computer sciences. In [1] Bueno studied (k,h)- Jacobsthal sequence of the form T =kT +2hT . n n−1 n−2 Hefoundaformulaofnthtermandsumofthefirstntermsofthissequence. Cerda Morales [2] considered a particular Jacobsthal sequence, namely, q-Jacobsthal se- quence {J } and obtained a generating matrix for the terms of sequence {J } q,n q,kn for a positive integer k. Then by the aid of this matrix, established some new identities for thissequence. The main objectiveof this paperis to investigate new results about (k,h)-Pell sequence and (k,h)-Pell Lucas sequence. The well-known Pell sequence {P } has the recursive relation n P =2P +P , n n−1 n−2 [3], where P = 0,P = 1. Now, we consider a generalization of this sequence [3] 0 1 which is called (k,h)-Pell sequence and is denoted by Γ . This sequence has the n recursive relation (1) Γ =2kΓ +hΓ , n n−1 n−2 ∗ Speaker. Emailaddress: petroudi@pnu.ac.ir 295</t>
+          <t>(k,h)-Pell-Lucas sequence, Consecutive term, Summation formula, Identity</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seidel matrix, Seidel Laplacian matrix, Eigenvalue, Seidel energy.. MSC(2020): 18A32, 05C50. 1. Introduction Let G be an undirected simple connected graph order n and size m, the ad- jacency matrix A(G) = (a ) of G is an n×n symmetric matrix, where a = 1 ij ij if v and v are adjacent in G, zero otherwise. For a graph G, Seidel matrix is i j defined as S(G) = [s ] in which s = −1 if the vertices v and v are adja- ij ij i j cent, s = 1 if the vertices v and v are not adjacent and s = 0 for i = j. ij i j ij Let D(G) = diag(d ,d ,...,d ) be the diagonal degree matrix. The Laplacian 1 2 n matrix of G is defined as L(G) = D(G) − A(G). Let D (G) = diag(n − 1 − S 2d ,n−1−2d ,...,n−1−2d ) be a diagonal matrix in which d stands for 1 2 n i degree of a vertex v in G. Then, in analogy with the ordinary Laplacian matrix, i the Seidel Laplacian matrix of G is defined as S (G) = D (G)−S(G). Note L S that D (G) = D(G)−D(G¯) and S (G) = L(G)−L(G¯). Let λ ,λ ,··· ,λ and S L 1 2 n λL,λL,··· ,λL be the Seidel eigenvalues and Seidel Laplacian eigenvalues of G 1 2 n respectively. The Seidel energy E (G) of a graph G is the sum of the absolute S values of the eigenvalues of G. The Seidel Laplacian energy of G is defined as n (cid:88) n(n−1)−4m E = |λL− | SL i n i=1 ∗ Speaker. Emailaddress: askari@kashanu.ac.ir 301</t>
+          <t>Seidel matrix, Seidel Laplacian matrix, Eigenvalue, Seidel energy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>complex networks, heterogeneity measure, upper and lower bound . MSC(2020): 68R10, 05C10. 1. Introduction Let G=(V,E) be a simple graph (i.e. finite, undirected graph without loops or multiple edges) on vertex set V ={v ,...,v } and edge set E ={e ,...,e } (so 1 n 1 m n=|V(G)|isitsorder, andm=|E(G)|isitssize). Forv ∈V(G), thedegreeof i v , written by d(v ) or k , is the number of edges incident with v . Let ∆= max i i i i {d : v ∈ V(G)} and δ = min {d : v ∈ V(G)}. A network is an simple graph i i i i consisting of a certain number of nodes or vertices connected by links or edges. A regular network is a graph where each vertex has the same number of neighbors; i.e. everyvertexhasthesamedegree. Anetworkisirregularifalltheverticeshave distinctdegreesexceptforonepair. Complexnetworks,whicharenetworkswhose structureisirregular,complexanddynamicallyevolvingintime,arethestructural skeleton of biological, ecological, technological, and socioeconomic systems [2, 3]. The study of such complex networks has developed into a major field of inter- disciplinary research spanning across mathematics, physics, biology and social sciences[4,5,6]. Theheterogeneitymeasureisasingleindexthatcanquantifythe diversity of connections between vertices or nodes in networks even with different ∗ Speaker. Emailaddress: taherihassan@gmail.com 304</t>
+          <t>complex networks, heterogeneity measure, upper and lower bound</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>perfect star packing, perfect pseudo-matching, fullerene graphs. MSC(2020): 05C90, 05C70. 1. Introduction A fullerene is a carbon molecule interconnected in pentagonal and hexagonal rings. A fullerene graph is a cubic, 3-connected planar graph with 12 pentagons. The number of hexagons can be either zero or a positive integer greater than one [4]. For all even n≥20 except n=22 exists a fullerene graph on n vertices [4]. A matching of a graph G is a set M of independent edges of G, i.e., a set of edges such that no two edges share a vertex. A matching is said to be perfect if any vertex of G is incident with an edge from it. In 1891, Petersen established that every 3-regular graph with no more than two cut-edges has a perfect matching, which shows that all fullerene graphs have perfect matchings [5]. For given graphs, G and H, a perfect H-packing in G is a spanning subgraph of G whose all components are isomorphic to H. If H is the star graph K , it is 1,3 calledperfectstarpacking. Aperfectpseudo-matchinginagraphGisaspanning subgraphofGwhosecomponentsareisomorphictoK ortoK . Perfectpseudo- 1,3 2 matchingswithtwotypesofcomponentsarecalledmixed. Aninterestingproblem infullerenegraphsiscountingperfectmatchingsandtogivesomeboundsofperfect matchings. (See [1]). The Counting of perfect star packing and perfect pseudo- matchingisanewersubject. T.Doˇsli´cetal. [2]categorizedsomefullerenegraphs that have a perfect star packing and they obtained that every fullerene graph G ∗ Speaker. Emailaddress: m.taheri26@gmail.com 309</t>
+          <t>perfect star packing, perfect pseudo-matching, fullerene graphs</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Commuting conjugacy class graph, The generalized dicyclic groups.. MSC(2020): 20C15, 20D15. 1. Introduction Suppose G is a non-abelian finite group. The commuting conjugacy class graph, Γ(G), of G is a simple and undirected graph with non-central conjugacy classes of G as its vertex set and two distinct vertices C and D are adjacent if and only if there are c ∈ C and d ∈ D such that cd = dc, [3]. In the mentioned paper, the authors classified all finite groups G with this property that Γ(G) is triangle-free. The commuting conjugacy class graph was first studied by Herzog et al. [2], but they considered the nonidentity conjugacy classes of the group as a vertexset. Thenotionofthecommuting graphofafinitegroupwasintroduced byBrauerandFowler[1]inanoldpaperinwhichtheauthorsinvestigatedgroups of even orders. These authors did not use the graph theory language, but proved some elementary properties of this graph. Suppose X = {∆ ,...,∆ } are a set of undirected graphs with mutually 1 s disjointvertexsets. Thenotation∆ ∪···∪∆ isusedforagraphwiththevertex 1 s sets V(∆ )∪···∪V(∆ ) and the edge sets E(∆ )∪···∪E(∆ ). In the case that 1 s 1 s all members of X are isomorphic, we use the notation sΛ as Λ ∪···∪Λ . 1 1 s The aim of this paper is to calculate the commuting conjugacy class graph of the generalized dicyclic group Dic(A,y,x), where Dic(A,y,x)=⟨A,x|x2 =y, ax =a−1, ∀a∈A⟩ ∗ Speaker. Emailaddress: MA.Salahshour@iau.ac.ir 317</t>
+          <t>Commuting conjugacy class graph, The generalized dicyclic groups</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seidel matrix; Seidel Estrada index. MSC(2020): 05C31, 05C50, 15A18. 1. Introduction Throughout the paper all graphs are simple. They are finite with no loops and direction. Let G=(V(G),E(G)) be a simple graph. The order of G denotes thenumberofverticesofG. Fortwoverticesuandv bye=uv wemeantheedge e between the vertices u and v. For every vertex v ∈V(G), the degree of v is the numberofedgesincidentwithv andisdenotedbydeg (v). Ak–regulargraphisa G graph such that every vertex of that has degree k. The complement of G, denoted byG,isthesimplegraphwithvertexsetV(G)suchthattwodistinctverticesofG are adjacent if and only if they are not adjacent in G. The edgeless graph (empty graph), the complete graph, the cycle, and the path of order n, are denoted by K , K , C and P , respectively. Let t and n ,...,n be some positive integers. n n n n 1 t By K we mean the complete multipartite graph with part sizes n ,...,n . n1,...,nt 1 t In particular, the complete bipartite graph with part sizes m and n is denoted by K . The identity matrix and the matrix whose all of entries are equal to 1 are m,n denoted by I and J, respectively. A Hermitian matrix (or self-adjoint matrix) is a complex square matrix that is equal to its own conjugate transpose. The eigenvalues of Hermitian matrices are real. For every Hermitian matrix of size n, say A, we sort its eigenvalues as λ (A) ≥ λ (A) ≥ ··· ≥ λ (A). The trace and 1 2 n rank of a complex matrix B are denoted by tr(B) and rank(B), respectively. LetGbeasimplegraphwithvertexset{v ,...,v }. Theadjacency matrixof 1 n G, denoted by A(G), is the n×n matrix such that the (i,j)-entry is 1 if v and v i j are adjacent, and otherwise is 0. For more details on the adjacency matrices and their properties, see [2]. The Seidel matrix of G that is denoted by S(G)=[s ] is ij ∗ Speaker. Emailaddress: mr oboudi@yahoo.com,mr oboudi@shirazu.ac.ir 319</t>
+          <t>Seidel matrix; Seidel Estrada index</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prof. Alireza Ashrafi, Metric graph theory, Topological indices, Chemical graph theory.. MSC(2020): 05C12, 05C35, 92E10. 1. Review of Prof. Ashrafi’s Research ProfessorAshrafihasstudiedseveralconceptsingraphtheoryduringhisscien- tific career. Also he is one the pioneers in some of the concepts are widely studied today. Symmetrytheoryingraphsofmoleculesinphysicalchemistry,group-based graphs,metricgraphtheory,biologicalgraphs,etc. Ingeneral,hisresearchcanbe divided into three main parts in the graph theory, which we will explain below. • group-based graphs, • Graph invariant, • Mathematical Chemistry. There are different ways to understand graph groups. One way is to think of them as groups associated with graphs, where each vertex and edge of the graph ∗ Speaker. Emailaddress: mjnajafiarani@gmail.com 323</t>
+          <t>Prof. Alireza Ashrafi, Metric graph theory, Topological indices, Chemical graph theory</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>cozero-divisor graph, dual of cozero-divisor graph. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction Let R be a commutative ring and W∗(R) be the set of all non-zero non-unit elementsofR. GraphΓ(R),thecozero-divisorgraphofR,isagraphwithvertices set W∗(R), and two elements a,b∈W∗(R) are adjacent if and only if a∈/ bR and b∈/ aR. The dual of cozero-divisor graph of a commutative ring(R), is a graph with vertices set W∗(R), and two elements a,b ∈ W∗(R) are adjacent if and only if a∈bR or b∈aR. WecharacterizethedualgraphofZ ,bydecomposingofnintoprimenumber. n 2. Main results Let n be an integer number and we decompose n into prime integers, and so we characterize the dual cozero-divisor graph whit this property. Theorem 2.1. Let R = Z n and n = p 1 α1···p k αk and p i s are prime integer. Then we have above items: 1) let n=p. then we have a field and graph is an empty graph. 2) let n=p p , then Γ(R) contains two disjoint subgraph Γ(p ) and Γ(p ). 1 2 1 2 Proof. Each subgraph Γ(P ), has vertics set &lt; p &gt; and is a con- i i nectedsubgraph. Ontheotherhandwehavep p =n=0, andforeach 1 2 x ∈ W∗(R), we have x ∈/ p p R = 0, therefore tow subgraph Γ(R ) are 1 2 i not connected. Now, if p ,p ≤ 3, thus each subgraph has not any cycle and so 1 2 girth(Γ(R))=diam(Γ(R))=∞. ∗ Speaker. Emailaddress: sazare66@gmail.com 327</t>
+          <t>cozero-divisor graph, dual of cozero-divisor graph</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Binary decision (hyper) diagram, Binary decision (hyper) tree.. MSC(2020): 05C65, 94C10, 05C05. 1. Introduction Definition 1.1. [1] Let V be a finite set, m ∈ N, and for each 1 ≤ i ≤ m, F ⊆ V is an arbitrary subset of V. Then, we call H = (V,F = {F }m ) as a i i i=1 Pseudo hypergraph that each x∈V, is a hyper vertex (for simplicity, we call it a vertex) and for each 1≤i≤m, we call F hyperedges, and for simplicity we show i it as H =(V,{F }m ). i i=1 APseudohypergraphH =(V,{F }m )iscalledahypergraphifforeach1≤i≤m, i i=1 ∅≠ F and (cid:83)m F =V. i i=1 i Definition 1.2. [3]Abinarydecisiontree(BDT)forthevariableorderx &lt; i1 x &lt; ... &lt; x , It has the attached properties: (1), all end vertices are marked i2 in with 0 or 1, (2), all other nodes are labeled by a variable and they have precisely two subtree(children), the 0-child and the 1-child. The edges leading to these children are labeled by 0 respectively by 1, (3), if the root is not a leave, then it is labeled by x ,(4) if a node is labeled by x then, its two children are leaves, i1 in (5), if a node is labeled by x and j &lt; n, then its two children are labeled by ij x . Every path of a decision tree determines an assignment of the variables ij+1 x ,x ,...,x . The Boolean function f(x ,x ,...,x ) represented by a decision i1 i2 in 1 2 n tree T is defined by as f(x ,x ,...,x ) = label of the leaf reached by the path 1 2 n corresponding to the assignment x ,x ,...,x . i1 i2 in ∗ Speaker. Emailaddress: M.Rahmati@pnu.ac.ir 331</t>
+          <t>Binary decision (hyper) diagram, Binary decision (hyper) tree</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(m,n)-super hyper operation, (m,n)-super hyper G-subalgebra.. MSC(2020): 17A70, 17C70. 1. Introduction Definition 1.1. [1] A G-algebra is a non-empty set X with a constant 0 and a binary operation ∗ satisfying the following axioms: (I) x∗x=0, (II) x∗(x∗y)=y for all x,y ∈X. Definition 1.2. [5] Let X ̸= ∅. Then f∗ : Xm → Pn(X) is called an (m,n) ∗ (m,n)-super hyperoperation, where m ≥ 2,n ≥ 0, Pn(X) is the nth-powerset of ∗ the set X, ∅ ̸∈ Pn(X) and Xm = X×X×...×X. Also (X,f∗ ) is called an ∗ (m,n) (cid:124) (cid:123)(cid:122) (cid:125) m times (m,n)-super hyperalgebra. Let f∗ be an (m,n)-super hyperoperation on X and B ,...,B subsets of X. (m,n) 1 m We define (cid:91) f∗ (B ,...,B )= f∗ (x ,...,x ). (m,n) 1 m (m,n) 1 m xi∈Bi If B ⊆Pn(X), then we identify {B} with B. ∗ 2. Super hyper G-subalgebra In this section, we make the concept of super hyper G-subalgebras as an extension of G-subalgebras and seek some of their properties ∗ Speaker. Emailaddress: M.Rahmati@pnu.ac.ir 336</t>
+          <t>(m,n)-super hyper operation, (m,n)-super hyper G-subalgebra</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>compact graph, vertex degree, neighborhood, cut vertex. MSC(2020): 05C07, 05C38, 05C75. 1. Introduction Webeginwithrecallingsomedefinitionsandnotationsongraphs. Throughout thispaper,agraphGisanundirectedsimplegraphwiththevertexsetV =V(G) and the edge set E =E(G). A graph is said to be connected if there exists a path between any two distinct vertices. Maximal connected subgraphs of G are called theconnected componentsofGandthenumberofthemisdenotedbyc(G). Acut vertex is a vertex whose deletion increases the number of components. Moreover, inthispaper,weusethenotationω(G)fortheclique number. Acyclewithlength n is denoted by C . Every graph with no cycle is called a forest. Moreovere, we n denote the induced subgraph on X ⊂V(G), by G[X]. A bipartite graph is a graph whose vertex set can be divided into two disjoint parts X and Y such that both of the induced subgraphs G[X] and G[Y] have no edges. Moreover, a complete bipartite graph is a bipartite graph in which every vertex of one part is joined to every vertex of the other part. If the size of one of the parts is 1, then it is said to beastargraph. LetGbeagraph. TheneighbourhoodanddegreeofavertexxofG aredenotedbyN(x)=N (x)andd(x)=d (x),respectively. Also,themaximum G G (minimum) degree of vertices of G is denoted by ∆(G) (δ). An end vertex is a vertex withh degree one. A clique of a graph is its complete subgraph and the number of vertices in the largest clique of graph G, denoted by ω(G), is called the clique number of G. The complete graph of order, denoted by K , is a graph in n whichanytwodistinctverticesareadjacent. Thediameter ofaconnectedgraphG, denotedbydiam(G), isthemaximumdistancebetweenanypairoftheverticesof ∗ Speaker. f.shaveisi@razi.ac.ir 341</t>
+          <t>compact graph, vertex degree, neighborhood, cut vertex</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Energy of graph, domination number, perfect matching. . MSC(2020): 05C50, 05C69, 05C70. 1. Introduction Let G be a simple graph with n vertices, m edges and having eigenvalues λ ,...,λ . The energy of the graph G denoted by E(G) is defined as the sum of 1 n the absolute values of its eigenvalues. Hence, n (cid:80) E(G)= |λ |. i i=1 The domination number of G, denoted by γ(G), is the minimum cardinality of a dominating set of G. The total domination number of G, denoted by γ (G) is t the minimum cardinality of a total dominating set. The matching number of G, denoted by µ(G), is the size of a maximum matching. A maximum matching is a matching that contains the largest possible number of edges. If a matching covers all vertices of G, then it is called a perfect matching. 2. Main results Lemma 2.1. [4, Thm. 1.1]. Let G be a graph. Then E(G)≥2µ(G). Lemma 2.2. [3]. If G is a graph without any isolated vertex, then µ(G) ≥ γ(G). Lemma 2.3. If H is a proper subgraph of a graph G, then E(H)&lt;E(G). Lemma 2.4. [2, Thm. 3]. A connected graph G of order 2n has γ(G) = n if and only if either G = C or the vertices of G can be partitioned into two sets 4 V and V with a matching between them and satisfying G[V ]=K and G[V ] is 1 2 1 n 2 connected. ∗ Speaker. Emailaddress: sorouhani435@gmail.com 346</t>
+          <t>Energy of graph, domination number, perfect matching</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Random graphs, Expectation, Zagreb indices. MSC(2020): 05C07, 05C80, 60B20. 1. Introduction LetGbeagraphwiththevertexsetV(G)andtheedgesetE(G). Weconsider simple graphs with no loops or multiple edges. The degree of a vertex v ∈ V(G) is denoted by d(v). The Zagreb index, named after the capital of Croatia, is one of the earli- est chemical topological indices to be defined. Chemical graph theory serves as a bridge between mathematics, chemistry, and graph theory, exploring the rela- tionship between molecular diagrams and numerical quantities known as graph parameters. The first Zagreb index, denoted as M (G), and the second Zagreb 1 index, denoted as M (G), were introduced by Gutman and Trinajstic in 1975 [2]. 2 ∗ Speaker. Emailaddress: sara.samaie1981@gmail.com 350</t>
+          <t>Random graphs, Expectation, Zagreb indices</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Soft sets, soft graphs, soft coloring of soft graphs, total soft coloring of soft graphs.. MSC(2020): 03E75, 03E72, 05C15. 1. Introduction Graph coloring problem is one of the most studied and well known subjects in discrete and combinatorial optimization domain. There are many practical applications that can be modeled and analyzed by graph coloring problems. Soft set theory [5], firstly initiated by Molodtsov, is a new mathematical tool for dealing with uncertainties. It is shown that the soft sets have applications in severalfieldssuchasthesmoothnessoffunctions,operationresearch,gametheory, measurement and probability theory. The applications of soft sets are progressing rapidly and many researchers are focusing on real and practical problems. Many researchersstudiedapplicationsofsoftsetsinvariousalgebraicstructures. Thum- bakara and George [7] applied soft sets in graphs and presented the concept of soft graphs in the specific way. Akram and Nawas in [1] and [2] introduced the concept of soft graph in the broad spectrum and investigated some properties of this structure. Further study of the concept has been done in [3, 6]. In this paper, we introduce the notions of soft coloring and soft chromatic number of soft graph and show that these concepts are generalizations of the proper vertex, edge coloring and chromatic number of graphs. Also, the notion of soft coloring can unify the concepts of vertex and edge coloring of graphs, and coloring of hypergraphs. ∗ Speaker. Emailaddress: r.manaviyat@pnu.ac.ir 354</t>
+          <t>Soft sets, soft graphs, soft coloring of soft graphs, total soft coloring of soft graphs</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Legendre multiwavelet, Galerkin method, condition number.. MSC(2020): 65L20, 65N30, 42C40. 1. Introduction We consider the boundary value problem with Dirichlet condition (cid:40) −(p(x)u′)′ =f(x), x∈[0,1] (1) u(0)=u(1)=0. Wesupposef isacontinuousfunctionandp(x)isapositivefunctionwithcontin- uous derivative on I = [0,1]. Using the finite difference method, the problem (1) can be discretized as [2] p u −(p +p )u +p u =h2f , i=1,...,N, i−1 i−1 i−1 i+1 i i+1 i+1 i 2 2 2 2 where u =u(x ), p =p(x ), f =f(x ), x =ih, u =u =0. i i i+1 i+1 i i i 0 N+1 2 2 In summery, above equations can be written in matrix form Lu=f, where   −(p +p ) p 0 ··· 0 0 0 1 3 3 2 2 2  p −(p +p ) p ··· 0 0 0   3 2 3 2 5 2 5 2   . . . . . .  L= . . . . . . . . . . . .     0 0 0 ··· p −(p +p ) p   N−3 N−3 N−1 N−1  2 2 2 2 0 0 0 ··· 0 p −(p +p ) N−1 N−1 N+1 2 2 2 ∗ Speaker. Emailaddress: htabrizidooz@kashanu.ac.ir 361</t>
+          <t>Legendre multiwavelet, Galerkin method, condition number</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Generalized Jacobi polynomials, Lan-Emden equation , Petro-Galerkin method, Error estimate.. MSC(2020): 18A32, 18F20, 05C65. 1. Introduction In astrophysics, the Lane–Emden equation is a dimensionless form of Pois- son’s equation for the gravitational potential of a Newtonian self-gravitating. In this article, we consider the ODE form of this equation including Riesz fractional derivatives with variable coefficients in the following form [3] ∂αu(x) k ∂βu(x) 1 (1) + + u(x)=f(x), ∂|x|α xα−β ∂|x|β xα−2 where −1 ⩽ x ⩽ 1 , 1 &lt; α ⩽ 2 and 0 &lt; β ⩽ 1 and boundary conditions are u(−1) = u(1) = 0. We give a brief introduction of fractional derivatives [1]. For α∈[k−1,k)inwhichk ∈N,theleft-sidedRiemann-Liouvillefractionalderivative of order α is defined as 1 dk (cid:90) x v(y) (2) RDαv(x)= dy, x∈[a,b], x Γ(k−α)dxk (x−y)α−k+1 a andtheright-sidedRiemann-Liouvillefractionalderivativeoforderαisdefinedas (−1)k dk (cid:90) b v(y) (3) RDαv(x)= dy, x∈[a,b]. x Γ(k−α)dxk (y−x)α−k+1 x ∗ Speaker. Emailaddress: hoorihfakhari@yahoo.com 367</t>
+          <t>Generalized Jacobi polynomials, Lan-Emden equation , Petro-Galerkin method, Error estimate</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fuzzy multi-dimensional mappings; g-(linear continuous) function; g-differentiability; Directional g-derivative. MSC(2020): 34A07. 1. Introduction Since Zadeh [5] began to study the basic concepts and principles of fuzzy theory,manystudieshavefocusedonthetheoreticalandpracticalaspectsoffuzzy numbers. In 1987, Kaleva [6] discussed fuzzy differentiability and considered the necessary and sufficient conditions for H-differentiability of fuzzy mappings from [a,b] into E. In 2003, Wang and Wu [2] proposed fuzzy mappings from Rn into E by using H-difference, directional derivative, differentiability, and subdifferential. However,theH-differencebetweentwofuzzynumbersoccursonlyinveryrestricted conditions[6]andtheH-differencebetweentwofuzzynumberscannotalwayscome into existence [3]. Then the gH-difference between two fuzzy numbers is defined under less restrictive conditions, although the gH-difference is not always existed. As a result, the generalized difference proposed in [1, 3], by Gomes and Barros, eliminates all the short-comes discussed in the above differences so that the g- difference of two fuzzy numbers always exists [1]. In 2013, Bede and Stefanini studiedandintroducedtheconceptofgeneralizeddifferentiabilityforfuzzy-valued functions by using the new generalization of gH-difference. We introduce the concept of g-differentiability for fuzzy multi-dimensional mappings based on the concept of g-differentiability [1], so that it exists for a larger class of fuzzy multi- dimensional mappings. In this article, characterization is appointed for Fr´echet and Gˆateaux g-differentiability; based on level-set and through differentiability of endpoints real-valued functions a characterization is also offered and explored for directional and partial g-differentiability. The sufficient condition for Fr´echet and ∗ Speaker. Emailaddress: sedaghatfar@yahoo.com 373</t>
+          <t>Fuzzy multi-dimensional mappings; g-(linear continuous) function; g-differentiability; Directional g-derivative</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dickson polynomials, neural networks, system identification. MSC(2020): 12D05, 68T07, 93B30. 1. Introduction Systemidentificationisanactivefieldofcontroltheorywithwideapplications. In this field, the inputs and outputs of underlying system is measured and the modelingiscarriedoutusingthem. Duetothedifficultiesinmodelingofnonlinear systems using the first principles, the importance of this context is obvious. Applyingtheartificialneuralnetworksisoneofthemostimportantapproaches in the identification of nonlinear systems. On the basis of polynomial sets, some neural networks have been designed in the literature [4, 1]. In this work, a neu- ral network based on the Dickson polynomials is designed, and utilized for the identification of nonlinear dynamical systems. The rest of this work is continued as follow. In Section 2, the Dickson poly- nomials are introduced. On the basis of Dickson polynomials, a neural network is designed and explained in Section 3. In Section 4, the proposed model is utilized forsystemidentification. InSection5,anexampleisexplained,andtheconclusion is stated in Section 6. ∗ Speaker. Emailaddress: g.ahmadi@pnu.ac.ir 378</t>
+          <t>Dickson polynomials, neural networks, system identification</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Information measure, uncertainty, entropy, fuzzy set.. MSC(2020): 94A17 , 62A86 , 60A86. 1. Introduction Fuzzy theory and information theory have many applications in other fields. Fuzzy theory is useful in modeling imprecise systems and systems that require decisions to control the system. Information theory is also used in many branches suchasprobabilitytheory,statistics,financialmathematics,computerscienceand engineering. Statistical theory and fuzzy set theory have both been developed to study patterns involving uncertainty. The first one is suitable for studying pat- terns based on statistical uncertainty (due to random events) and the second one is suitable for studying patterns based on possibilistic (caused by ambiguity and impreciseness). The theory of fuzzy sets was proposed in 1965 by an Iranian sci- entist named Zadeh, but studies and researches in statistics and fuzzy probability started in the eighties. One of the important and fundamental concepts in information theory is en- tropy, which is used as a measure to compare different uncertain systems and was created by Boltzmann to evaluate the degree of disorder of a gas in a closed container. This concept was later used by Shannon in the field of information theory and penetrated the field of fuzzy sets. Information theory quantifies infor- mation, for example, the amount of information transmitted in an event from the sigma field depends on the probability of that event occurring. A mea- sure to quantify the information of an event A from the sigma field is equal to I(A) = −logP(A) and the average information over all the events from the sigma field (the expected value of uncertainty, associated with an experiment ∗ Speaker. Emailaddress: mehdishams@kashanu.ac.ir 384</t>
+          <t>Information measure, uncertainty, entropy, fuzzy set</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>linear regression, correlated covariance structure, time series regression, autoregressive moving average (ARMA) model. MSC(2020): 62J05,62M10, 91B84. 1. Introduction Multiple regression is a tool that allows one to model the linear relationship between a response variable and some explanatory variables [5]. The matrix form of the multiple regression model can be written as: (1) Y =Xβ+ϵ, where Y is n × 1 vector of the response variable, X is n × (k + 1) matrix of k explanatory variables, β is p×1 vector of the unknown regression coefficients (p=k+1),andϵdenotesthen×1vectorsoftheerrorterms. Itisusuallyassumed thatϵ∼ N(0,σ2I ). Iftheseassumptionsaremet,thetheordinary-least-squares n (OLS), in that it find estimate βˆ that minimize the error sum of squares SSE = (cid:80)n ϵ2, provides the best linear unbiased estimate of β. Statistical inference for i=1 i model (1) fitted to data using OLS method, needs to fulfill several assumptions about the random errors, including the assumption of the uncorrelated errors. For the situations, where the data are collected over time or space, it is common for the errors to have a correlated structure, since adjacent observations tend to be similar in both temporal and spatial dimensions. Serial correlation will not affect the unbiasedness or consistency of the OLS estimators, but it does affect theirefficiency. Withpositiveserialcorrelation,theOLSestimatesofthestandard errorswillbesmallerthanthetruestandarderrors. Thiswillleadtotheconclusion that the parameter estimates are more precise than they really are. There will be a tendency to reject the null hypothesis when it should not be rejected [1]. ∗ Speaker. Emailaddress: hamidghorbani@kashanu.ac.ir 390</t>
+          <t>linear regression, correlated covariance structure, time series regression, autoregressive moving average (ARMA) model</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>random graph models, network structure . MSC(2020): 05C80, 05C90. 1. Introduction Network data or graphs, a collection of nodes with edges connecting them, appear everywhere in today life. For example, disease-transmission networks, hu- manbrainnetworks,terroristnetworks,ecologicalfoodnetworks(foodweb),social networks, financial transaction networks, academic paper coauthor ships and ci- tations, protein interaction patterns and much more, [3]. Such network data can be modeled as a stochastic graph, see [6]. The nodes of random networks are randomly distributed on the plane and randomly connected to each other using a specific rules. The aim of entering the randomness in their construction is to increase their ability to mimic the observable behavior in real systems. Under- standing the behavior and properties of real-world networks is crucial for various fields, as it can help in designing efficient communication networks, studying the spreadofdiseases,analyzingsocialinteractions,anddevelopingalgorithmsfornet- work analysis. The random graph theory is a multidisciplinary field that applies probabilisticconceptstomodelandanalyzereal-worldnetworks. Thisfieldiscon- cerned with understanding the structure, complexity, and connectivity of various networks, including social networks, biological networks, and the Internet. The ∗ Speaker. Emailaddress: hamidghorbani@kashanu.ac.ir 395</t>
+          <t>random graph models, network structure</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECM-algorithm, linear mixed models, the canonical fundamental skew normal, heavy-tail distribution.. MSC(2020): 62H12, 62F10. 1. Introduction Linear mixed models (LMM) [1] have played important role in analyzing lon- gitudinal data that this data is measured repeatedly. The introduction of LMM paved a broad way to the development of applied statistics for analyzing data in a large variety of fields, specially medicine and bio-statistic. The key feature of LMM is to use multivariate normal distribution for each sample that has been repeat tests. In the case that the sample has participated in all periodic tests, for a set of random vectors Y ,...,Y , the generic form of an LMM model can 1 n theoretically be defined by a linear combination of random effects as iid iid (1) Y =X β+Z B +ϵ , B ∼ N (0,D), ϵ ∼ N (0,Ψ), B ⊥ε , j j j j j j q j p j j whereY ∈Rp,β isag-dimensionalconstanteffectsvectorandp×gknownmatrix j X . Basedonmodel(1),p×q knownmatrixZ describesrelationbetweenY and j j j B for j =1,...,n. j When faced with frequently measures, the problem of missing data should be addressed appropriately before engaging learning algorithms. However, many researchers have proposed the maximum likelihood approach to deal with missing information. TheGaussianLinearmixedmodelslacksrobustnessagainstskewness and kurtesis and may seriously distort the estimates and results. In asymmetric ∗ Speaker. Emailaddress: saeed darijani@yahoo.com 401</t>
+          <t>ECM-algorithm, linear mixed models, the canonical fundamental skew normal, heavy-tail distribution</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Finite mixture, canonical fundamental skew normal, outliers, missing information. MSC(2020): 62H12, 62F10. 1. Introduction Unsupervised classification have played important role in analyzing pattern recognition. The introduction of finite mixture model clear a broad way to the development of applied statistics for analyzing data in a large variety of fields, for example,factoranalysisandbio-statistic. Thekeyfeatureoffinitemixtureistouse multivariate normal distribution for each component. The finite mixture models based on normal distribution lacks robustness against skewness and kurtesis and may seriously distort the estimates and results. Missing data is an ubiquitous challenge in multivariate analysis and in finite mixture the problem of missing data cannot be neglected. Multivariate distributions with incomplete data has been considered in the paper, consisting the work by [1]. Severaldifferentasymmetricfinitemixturemodelwithusingtheclassofskew distribution have been suggested in the papers, for example, [3]. Specifically, a random variable Y is said to have a the canonical fundamental skew normal distribution, denoted by CFUSN (µ,Σ,Λ), if it can theoretically be defined by a p linear representation (1) Y =µ+ΛU +U , 0 where,µisalocationparameter,Λisap×q matrix,U isap-dimensionN (µ,Σ), 0 p U is a q-variate standard half-normal random vector, independent of U , and = 0 denotes the equality in distribution. ∗ Speaker. Emailaddress: farzane.hashemi1367@yahoo.com 407</t>
+          <t>Finite mixture, canonical fundamental skew normal, outliers, missing information</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ordered random variables, test of fit, contingency tables. MSC(2020): 62H17, 65C10. 1. Introduction Analysisofcontingencytablesisoneofthebestwaystoanswermanyquestions in the area of medicine, human, management and economics researches, etc.. [5] introduced an R or C association model and [6] presented a proportional odds modelastwomainapproachesformodelingthesedata. Whenthedataareordinal, the assignment of scores to the categories and the modelling of the empirical distribution are two well -known analysis models. Since, it is necessary to draw a suitable graph before performing statistical analysis, we have used the idea in [2] to draw new graph for ordered categorical data. This paper has the following structure. In section 2, a new chart was proposed for ordered data set in the contingency tables. Section 3 contains two examples to interpret the proposed chart. 2. The new plot Suppose that CT = {n } where i = 1,··· ,I and j = 1,··· ,J be a two-way ij contingency table, which the column variable be an ordinal variable and the rows represent different types of groups or some categorized explanatory variables. In this content, the column variable is a specified score whereas the row variable need not be a score. Let n = (cid:80)J n be a sum of ith row, p(j|i) = nij and i. j=1 ij ni. P(j|i) = (cid:80)j p(k|i) are the conditional percentage of the jth column category k=1 given the ith row and the conditional cumulative percentage function given the ith column. Similarity, n = (cid:80)I n be a sum of jth column, p(i|j) = nij .j i=1 ij n.j ∗ Speaker. Emailaddress: salmanpour@kashanu.ac.ir 413</t>
+          <t>ordered random variables, test of fit, contingency tables</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vibrating system, Cost minimization, Hamilton-Jacobi-Bellman equation. MSC(2020): 93-08. 1. Introduction Vibrating systems are one of the most important structures in engineering that has attracted considerable attention in the past decade. Optimization of these systems has been considered by researchers from different aspects such as cost optimization, size optimization, topology optimization [1]. In this paper, we are going to consider the problem of cost optimization for a harmonic oscillator which is described by the following equation of motion: (1) My¨(t)+Dy˙(t)+Ky(t)=u(t) where y(t) shows displacement, M is mass, D is damping, K is stiffness and u(t) is the force acting on the system. Thevibratingsystem(1)isaccompaniedwithacostfunctionofthefollowingform that should be minimized: 1(cid:90) T (2) J = g(t,y(t),u(t))dt 2 0 In this paper, we are going to consider the problem of minimizing (2) subject to (1) by calculating a suitable input force u(t). In what follows, we will clarify our proposed procedure for solving this minimization problem. ∗ Speaker. Emailaddress: m ayatollahi@pnu.ac.ir 419</t>
+          <t>Vibrating system, Cost minimization, Hamilton-Jacobi-Bellman equation</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Quasi-equilibrium problem, Hadamar space, Strictly monotone mapping, Proximal point method.. MSC(2020): 65K15, 90C33, 47H09. 1. Introduction Let(X,d)beametricspace. Forx,y∈X,amappingc:[0,l]→X,wherel≥0,is calledageodesicwithendpointsx,y,ifc(0)=x,c(l)=y,andd(c(t),c(t′))=|t−t′|for all t,t′∈[0,l]. If, for every x,y∈X, a geodesic with endpoints x,y exists, then we call (X,d) a geodesic metric space. Furthermore if there exists a unique geodesic for each x,y ∈ X, then (X,d) is said to be uniquely geodesic. A subset C of a uniquely geodesic space X is said to be convex when for any two points x,y∈C, the geodesic joining x and y is contained in C. For each x,y∈X, the image of a geodesic c with endpoints x,y is called a geodesic segment joining x and y and is denoted by [x,y]. Let X be a uniquely geodesic metric space. For each x,y ∈ X andforeacht∈[0,1],thereexistsauniquepointz∈[x,y]suchthatd(x,z)=td(x,y) and d(y,z)=(1−t)d(x,y). We will use the notation (1−t)x⊕ty for denoting the unique point z satisfying the above statement. Definition 1.1. [1] A geodesic space X is called CAT(0) space if for all x,y,z∈X and t∈[0,1] it holds that d2(tx⊕(1−t)y,z)≤td2(x,z)+(1−t)d2(y,z)−t(1−t)d2(x,y). A complete CAT(0) space is called an Hadamard space. ∗ Speaker. Emailaddress: r.lotfikar@ilam.ac.ir 424</t>
+          <t>Quasi-equilibrium problem, Hadamar space, Strictly monotone mapping, Proximal point method</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prey-predator model, Cross-diffusion, Hopf bifurcation, Turing instability. MSC(2020): 92B05, 92D25. 1. Introduction In a prey-predator system, a group defense is a strategy used by the prey to protect themselves from predators instead of escape[7]. The group defense behavior of species in the predator-prey system is modeled by a nonmonotonic functional response [1, 6]. As examples of functional responses describing the group defense mechanism we can mention Holling-type IV [5], simplified Monod- Haldane [6], Ivlev-type, and Ivlev-like [2]. Also, the functional response mu (1) g(u)= , p&gt;1, up+c discussed in [3], describes the group defense behavior in prey species. In[4],Patraetal. introducedaprey-predatorsystemwiththefunctionalresponse (1). The authors studied the local asymptotic stability of the interior equilibrium point and the Hopf bifurcation. ∗ Speaker. Emailaddress: y.jalilian@razi.ac.ir 429</t>
+          <t>Prey-predator model, Cross-diffusion, Hopf bifurcation, Turing instability</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wireless Sensor Network, WSN, network coding, multicast,optimization problem.. MSC(2020): 18A32, 05C50. 1. Introduction Thenetworkencodingtechniqueworkssothatnetworknodesstoretheirinput packets for a period in memory to combine with other packets and create a new encoded package. Regardless all the benefits and advantages of using network encoding technology, the time constraint for wireless sensor network nodes is a disadvantage for this technique. In this paper, the limited time of sensor nodes in ∗ Speaker. Emailaddress: askari@kashanu.ac.ir 434</t>
+          <t>Wireless Sensor Network, WSN, network coding, multicast,optimization problem</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>distributed convex optimization, consensus, gradient descent method. MSC(2020): 46N10, 93D05, 93D50. 1. Introduction Multi-agentsystemshave attractedinterest fromresearchers overthe lastfew yearsbecauseagentscanagreeonavalueusinginteractionsbetweenthem. Reach- inganagreementonavalueusingcommunicationbetweenagentsiscalledconsen- sus[5]. Duetothewidespreaduseofmulti-agentsystems, thedesignandanalysis of distributed algorithms have become an important research topic. Distributed algorithms use only local calculations and the information exchange of each agent with its neighbors to achieve the specified goals. The consensus-based algorithm is the most widely used distributed algorithm. Distributed consensus-based al- gorithms are extensively applied to solve the distributed optimization problem. The purpose of the distributed optimization problem is to calculate the optimal solution of the cost function by using distributed algorithms. The distributed convex optimization problem has been frequently solved by gradient-based methods [2]-[4]. In [4], an algorithm has been suggested for the distributed convex optimization problem, and it has been considered the commu- nicationnetworktobeundirected. Inaddition,ithasbeenprovedtheexponential convergence of the suggested algorithm by applying the Lyapunov theory. According to the above-mentioned explanations, in this article, the proposed algorithm is designed by combining the gradient method with the consensus algo- rithm of the multi-agent system. A theorem for the convergence of the proposed ∗ Speaker. Emailaddress: ehsan.nzm74@gmail.com 439</t>
+          <t>distributed convex optimization, consensus, gradient descent method</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>stochastic gradient descent, decay step size, convergence rate.. MSC(2020): 90C06, 90C15, 90C26. 1. Introduction Stochastic gradient descent (SGD) is a popular optimization algorithm for training machine learning models. It efficiently optimizes high-dimensional ob- jective functions by updating model parameters using gradients computed from subsets of training samples. The effectiveness of SGD depends on selecting the right step size, or learning rate. Afixedstepsizecanleadtoslowconvergenceorovershooting,whileanoverly adaptive step size can introduce instability. Researchers have explored adaptive strategies for adjusting the step size during training. One common approach is using decay step sizes, which gradually reduce the step size over time [1, 2]. This helpsbalanceexplorationandexploitation,enablingquickexplorationinitiallyand fine-tuning later for convergence. The cosine step length is widely used among decay step lengths due to its favorable performance in terms of accuracy and loss function [2]. However, it has a drawback in the initial iterations where it does not yield satisfactory results ∗ Speaker. Emailsoheilshamaee@kashanu.ac.ir 445</t>
+          <t>stochastic gradient descent, decay step size, convergence rate</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Blind Watermarking, Official Letters, Letter Body Detection, Cryptography. MSC(2020): 11T71. 1. Introduction Watermarking is a crucial technique for establishing copyright ownership and authenticity of digital files. Since 1990, digital image watermarking has been in use. However, in 1993, it was introduced as electronic watermarking by Tirkel et al.[1]. Withadvancementsintechnology,moderntechniquessuchasdeeplearning are now commonly used for watermarking [2]. Several studies have investigated watermarking techniques for documents in different languages such as Chinese [3], English [4], etc. In this article, we will focus on the watermarking of official documents in organizations, irrespective of the language used. In [5], a blind watermarking algorithm for images is presented. In this paper, weintroduceablindalgorithmspecificallydesignedforconcealingpersonnelcodes and administrative information associated with official document circulation. Theremainderofthepaperisorganizedasfollows. Insection2,wepresentthe watermarking and extraction algorithms. In section 3, we evaluate the effective- ness of the presented algorithms by examining the results of their implementation on a sample image. Finally, section 4 concludes the paper by highlighting its achievements. 2. Watermarking Algorithm In this section, we present a blind watermarking algorithm for embedding a watermark into a document and an algorithm for extracting the watermark. We ∗ Speaker. Emailaddress: asaeedi@kashanu.ac.ir 451</t>
+          <t>Blind Watermarking, Official Letters, Letter Body Detection, Cryptography</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inverse eigenvalue problem, Bordered diagonal matrix, Leading principal submatrix. MSC(2020): 15xx-15A29. 1. Introduction Inverse eigenvalue problems arise in several applications, including system and control theory, neural networks, physics, vibration analysis, and so on [2, 3]. Withrespecttothespectralinformationarisefromtheproblemathandandwhich kind of matrix we are looking for, there are various methods in inverse eigenvalue problems. Here we consider the problem of constructing a symmetric bordered diagonal matrix of the following form from special spectral data:   a b b ··· b 1 1 2 n−1  b 1 ma 1 0 ··· 0    (1) A= b 2 0 ma 1 ··· 0  , a ∈R , b &gt;0 , m∈R.    . . . . . . . . . ... . . .    1 j b 0 0 ··· ma n−1 1 This class of matrices appear in certain symmetric inverse eigenvalue and inverse Sturm Liouville problems, for instance, in the movement equation with some per- turbations in regulation systems in control theory [1, 4, 5] Throughout this paper, we denote the j×j leading principal submatrix of A by A , the characteristic polynomial of A by ϕ (λ) and the eigenvalues of A by j j j j λ(j) ≤ λ(j) ≤ ··· ≤ λ(j) for j = 1,...,n. This work is motivated by the results 1 2 j ∗ Speaker. Emailaddress: s-mashayekhi@araku.ac.ir 457</t>
+          <t>Inverse eigenvalue problem, Bordered diagonal matrix, Leading principal submatrix</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Robust set-valued optimization problem, Asymptotic function. MSC(2020): 49J10, 49K10, 90C26. ∗ Speaker. Emailaddress: z.soltani@kashanu.ac.ir 464</t>
+          <t>Robust set-valued optimization problem, Asymptotic function</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minimax Theorem, Asymptotic function. MSC(2020): 49J10, 49K10, 90C26. ∗ Speaker. Emailaddress: z.soltani@kashanu.ac.ir 466</t>
+          <t>Minimax Theorem, Asymptotic function</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Enhanced power graph, power graph, nilpotent groups, forbidden subgraphs.. MSC(2020): 05C25. References 1. G. Aalipour, S. Akbari, P. J. Cameron, R. Nikandish, and F. Shaveisi. On the structure of the power graph and the enhanced power graph of a group. Electron. J. Combin. 24 (3) (2017)16-18. 2. S.Biswas,P.J.Cameron,A.Das,andH.K.Dey.Ondifferenceofenhancedpowergraphand power graph of a finite group,(2022) arXiv:2206.12422. ∗ JitenderKumar. Emailaddress: jitenderarora09@gmail.com 468</t>
+          <t>Enhanced power graph, power graph, nilpotent groups, forbidden subgraphs</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Shifted Vieta-Lucas polynomials, Caputo derivative, Fractional-order Ricatti differential equations, Operational matices. MSC(2020): 65L60, 65L05, 33C45. ∗ Speaker. Emailaddress: zabihi@kashanu.ac.ir 470</t>
+          <t>Shifted Vieta-Lucas polynomials, Caputo derivative, Fractional-order Ricatti differential equations, Operational matices</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Shifted Legendre polynomials, Legendre wavelets, Water pollution, Pollution of system of lakes.. MSC(2020): 65L05, 33C45. ∗ Speaker. Emailaddress: zabihi@kashanu.ac.ir 472</t>
+          <t>Shifted Legendre polynomials, Legendre wavelets, Water pollution, Pollution of system of lakes</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gyrogroup, Cayley graph, Algorithm. MSC(2020): 20N05, 05C40, 05C85. References 1. L.Bussaban,A.Kaewkhao,S.Suantai,Cayleygraphsofgyrogroups,QuasigroupsandRelated Systems,27(2019)25-32. 2. R. Maungchang, P. Khachorncharoenkul, K. Prathom,T. Suksumran, On transitivity and connectedness of Cayley graphs of gyrogroups,Heliyon,7(2021)e07049. ∗ Speaker. Emailaddress: neda.moradi@grade.kashanu.ac.ir 474</t>
+          <t>Gyrogroup, Cayley graph, Algorithm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Non-local ring, genus and crosscap of a graph, graph classes. MSC(2020): 05C25. References 1. M. Saha, A. Das, E. Y. C¸elikel, and C. Abdio˘glu, Prime ideal sum graph of a commutative ring,J.AlgebraAppl.22(2023)no.6,2350121. 2. Z.S.Pucanovi´candZ.Z.Petrovi´c,Toroidalityofintersectiongraphsofidealsofcommutative rings,GraphsCombin.30(2014)no.3,707–716. 3. Z. S. Pucanovi´c, M. Radovanovi´c, and A. L. Eri´c, On the genus of the intersection graph of ideals of a commutative ring,J.AlgebraAppl.13(2014)no.5,1350155. 4. V.Ramanathan,On projective intersection graph of ideals of commutative rings,J.Algebra Appl.20(2021)no.2,2150017. ∗ Speaker. Emailaddress: maithilpraveen@gmail.com 477</t>
+          <t>Non-local ring, genus and crosscap of a graph, graph classes</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Graph, Eigenvalues, Spectrum. MSC(2020): 18A32, 18F20, 05C65 . References 1. Y. Hou and W.-C. Shiu, The spectrum of the edge corona of two graphs, Electronic Journal ofLinearAlgebra,20(2010),586–594. 2. M. Javarsineh and G.H. Fath-Tabar, The Main Eigenvalues of the Undirected Power Graph of a Group,JournalofAlgebraicStructuresandTheirApplications,4(1)(2017)19-32. 3. I.Gopalapillai,Thespectrumofneighborhoodcoronaofgraphs,KragujevacJ.Math,35(2011) 493–500. ∗ Speaker. Emailaddress: khani@shaiau.ac.ir 479</t>
+          <t>Graph, Eigenvalues, Spectrum</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Class preserving automorphism group, central automorphism group, normal automorphism group, generalized dihedral group. MSC(2020): 20D99, 20F99. References 1. V. Bardakov, A. Vesnin and M.K. Yadav, Class preserving automorphisms of unitian- gular groups, International Journal of Algebra and Computation, 22 (3) (2012) 1250023, https://doi.org/10.1142/S02181967125002. 2. The GAP Team, Group, GAP - Groups, Algorithms, and Programming, 2012, http://www.gap-system.org. 3. M.K.Yadav,Classpreservingautomorphismsoffinitep-groups,JournaloftheLondonMath- ematicalSociety,Ser.2,75(3)(2007)755–772,https://doi.org/10.1112/jlms/jdm025. 4. M.K. Yadav, Class preserving automorphisms of finite p-groups II, Israel Journal of Mathe- matics,209(2015)355–396,10.1007/s11856-015-1222-4. ∗ Speaker. Emailaddress: momoeysfn@gmail.com 481</t>
+          <t>Class preserving automorphism group, central automorphism group, normal automorphism group, generalized dihedral group</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary: 16W20; Secondary: 13C60.. References 1. F.W. Anderson, K.R. Fuller, Rings and categories of modules, (Vol. 13) Springer Science &amp; BusinessMedia,2012. 2. B.Amini,M.ErshadandH.Sharif,Coretractable modules,JournaloftheAustralianMathe- maticalSociety,86(3)(2009)289-304. 3. S.Asgari,A.HaghanyandY.Tolooei,T-semisimplemodulesandT-semisimplerings,Com- municationsinAlgebra,41(5)(2013)1882-1902. 4. P. Neishabouri, Y. Tolooei, S. Bagheri, On modules in which every finitely generated sub- module is a kernel of an endomorphism,CommunicationsinAlgebra,51(2)(2023)841-858. 5. A.A.Tuganbaev,Ringsclosetoregular,(Vol.545)SpringerScience&amp;BusinessMedia,2013. 6. A. Ghorbani, Co-epi-retractable modules and co-pri rings, Communications in Algebra, 38 (10)(2010)3589-3596. 7. R.Wisbauer,Foundations of module and ring theory,Routledge,2018. ∗Speaker. Emailaddress: pegahneishabori96@gmail.com 483</t>
+          <t>Co-finite-retractable, Co-retractable</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Class preserving automorphism group, central automorphism group, normal automorphism group, generalized dicyclic group. MSC(2020): 20D99, 20F99. References 1. V. Bardakov, A. Vesnin and M.K. Yadav, Class preserving automorphisms of unitian- gular groups, International Journal of Algebra and Computation, 22 (3) (2012) 1250023, https://doi.org/10.1142/S02181967125002. 2. TheGAP Team, Group, GAP -Groups, Algorithms, and Programming,Version4.5.5,2012, http://www.gap-system.org. 3. M.K. Yadav, Class preserving automorphisms of finite p-groups, Journal of the London Mathematical Society, Ser. 2, 75 (3) (2007) 755–772; available at https://doi.org/10.1112/jlms/jdm025. 4. M.K.Yadav,Class preserving automorphisms of finite p-groups II,Israel Journal of Mathe- matics,209(2015)355–396,10.1007/s11856-015-1222-4. ∗ Speaker. Emailaddress: bardia.jahangiri@yahoo.com 485</t>
+          <t>Class preserving automorphism group, central automorphism group, normal automorphism group, generalized dicyclic group</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Neural Networks, Systems Biology, Modules of Genes. MSC(2020): 62P10, 68T07, 92C42. ∗ Speaker. Emailaddress: mahdevar@kashanu.ac.ir 487</t>
+          <t>Neural Networks, Systems Biology, Modules of Genes</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Co-finite-retractable, Co-retractable.. MSC(2020): Primary 16D10; secondary 16D40. . References 1. F.W. Anderson, K.R.Fuller, Rings and categories of modules, (Vol. 13) Springer Science &amp; BusinessMedia,2012. 2. B.Amini,M.ErshadandH.Sharif,Coretractable modules,JournaloftheAustralianMathe- maticalSociety,86(3)(2009)289-304. 3. S.Asgari,A.Haghany,Y.Tolooei,T-semisimple modules and T-semisimple rings. Commu- nications in Algebra,41(5)(2013)1882-1902. 4. P.Neishabouri,Y.Tolooei,S.Bagheri,Onmodulesinwhicheveryfinitelygeneratedsubmod- ule is a kernel of an endomorphism,CommunicationsinAlgebra,51(2)(2023)841-858. 5. A. Ghorbani, Co-epi-retractable modules and co-pri rings, Communications in Algebra, 38 (10)(2010)3589-3596. ∗Speaker. Emailaddress: Y.toloei@razi.ac.ir 489</t>
+          <t>Co-finite-retractable, Co-retractable</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>lexicographic product, connectivity, super connectivity. MSC(2020): 05C40. ∗ Speaker. Emailaddress: zeinabghasemi39@gmail.com 491</t>
+          <t>lexicographic product, connectivity, super connectivity</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
